--- a/VISA_CHECK.xlsx
+++ b/VISA_CHECK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianaRodriguezBelt\Downloads\DEFENSE_VIEWER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FFEB1B9-D61B-4626-AC22-8F93C3CFA829}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A2EC8C-DE9A-41E4-A057-2354EA4213B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="941" firstSheet="2" activeTab="6" xr2:uid="{65CF5D28-24F6-4E6D-B37B-A691AC3C8BFA}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18448" uniqueCount="1316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18452" uniqueCount="1316">
   <si>
     <t>country_code</t>
   </si>
@@ -51900,7 +51900,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E885E9E-B9D0-4AB2-985A-25954D52BD4C}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:I1155"/>
@@ -51941,7 +51941,7 @@
       </c>
       <c r="G1" s="24"/>
     </row>
-    <row r="2" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1075</v>
       </c>
@@ -51961,7 +51961,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1075</v>
       </c>
@@ -51981,7 +51981,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52001,7 +52001,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52021,7 +52021,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52041,7 +52041,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52061,7 +52061,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52081,7 +52081,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52101,7 +52101,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52121,7 +52121,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52141,7 +52141,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52161,7 +52161,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52181,7 +52181,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52199,7 +52199,7 @@
       </c>
       <c r="F14"/>
     </row>
-    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52217,7 +52217,7 @@
       </c>
       <c r="F15"/>
     </row>
-    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52235,7 +52235,7 @@
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52253,7 +52253,7 @@
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52271,7 +52271,7 @@
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52290,7 +52290,7 @@
       <c r="F19"/>
       <c r="I19" s="24"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52308,7 +52308,7 @@
       </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52326,7 +52326,7 @@
       </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52344,7 +52344,7 @@
       </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52362,7 +52362,7 @@
       </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52380,7 +52380,7 @@
       </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52398,7 +52398,7 @@
       </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52416,7 +52416,7 @@
       </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52434,7 +52434,7 @@
       </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52452,7 +52452,7 @@
       </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52470,7 +52470,7 @@
       </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52488,7 +52488,7 @@
       </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52506,7 +52506,7 @@
       </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52524,7 +52524,7 @@
       </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52542,7 +52542,7 @@
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52560,7 +52560,7 @@
       </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52578,7 +52578,7 @@
       </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52704,7 +52704,7 @@
       </c>
       <c r="F42"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52722,7 +52722,7 @@
       </c>
       <c r="F43"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52740,7 +52740,7 @@
       </c>
       <c r="F44"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52758,7 +52758,7 @@
       </c>
       <c r="F45"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52776,7 +52776,7 @@
       </c>
       <c r="F46"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="F47"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52812,7 +52812,7 @@
       </c>
       <c r="F48"/>
     </row>
-    <row r="49" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52830,7 +52830,7 @@
       </c>
       <c r="F49"/>
     </row>
-    <row r="50" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52848,7 +52848,7 @@
       </c>
       <c r="F50"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52866,7 +52866,7 @@
       </c>
       <c r="F51"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52884,7 +52884,7 @@
       </c>
       <c r="F52"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52902,7 +52902,7 @@
       </c>
       <c r="F53"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52920,7 +52920,7 @@
       </c>
       <c r="F54"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52938,7 +52938,7 @@
       </c>
       <c r="F55"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52956,7 +52956,7 @@
       </c>
       <c r="F56"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52974,7 +52974,7 @@
       </c>
       <c r="F57"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52992,7 +52992,7 @@
       </c>
       <c r="F58"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53010,7 +53010,7 @@
       </c>
       <c r="F59"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53028,7 +53028,7 @@
       </c>
       <c r="F60"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53046,7 +53046,7 @@
       </c>
       <c r="F61"/>
     </row>
-    <row r="62" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53064,7 +53064,7 @@
       </c>
       <c r="F62"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53082,7 +53082,7 @@
       </c>
       <c r="F63"/>
     </row>
-    <row r="64" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53100,7 +53100,7 @@
       </c>
       <c r="F64"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53118,7 +53118,7 @@
       </c>
       <c r="F65"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53136,7 +53136,7 @@
       </c>
       <c r="F66"/>
     </row>
-    <row r="67" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53154,7 +53154,7 @@
       </c>
       <c r="F67"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53172,7 +53172,7 @@
       </c>
       <c r="F68"/>
     </row>
-    <row r="69" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53190,7 +53190,7 @@
       </c>
       <c r="F69"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53208,7 +53208,7 @@
       </c>
       <c r="F70"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53226,7 +53226,7 @@
       </c>
       <c r="F71"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53244,7 +53244,7 @@
       </c>
       <c r="F72"/>
     </row>
-    <row r="73" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53262,7 +53262,7 @@
       </c>
       <c r="F73"/>
     </row>
-    <row r="74" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53280,7 +53280,7 @@
       </c>
       <c r="F74"/>
     </row>
-    <row r="75" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53298,7 +53298,7 @@
       </c>
       <c r="F75"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53316,7 +53316,7 @@
       </c>
       <c r="F76"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53334,7 +53334,7 @@
       </c>
       <c r="F77"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53352,7 +53352,7 @@
       </c>
       <c r="F78"/>
     </row>
-    <row r="79" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53370,7 +53370,7 @@
       </c>
       <c r="F79"/>
     </row>
-    <row r="80" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53388,7 +53388,7 @@
       </c>
       <c r="F80"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53406,7 +53406,7 @@
       </c>
       <c r="F81"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53424,7 +53424,7 @@
       </c>
       <c r="F82"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53442,7 +53442,7 @@
       </c>
       <c r="F83"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53460,7 +53460,7 @@
       </c>
       <c r="F84"/>
     </row>
-    <row r="85" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53478,7 +53478,7 @@
       </c>
       <c r="F85"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53496,7 +53496,7 @@
       </c>
       <c r="F86"/>
     </row>
-    <row r="87" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53514,7 +53514,7 @@
       </c>
       <c r="F87"/>
     </row>
-    <row r="88" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53532,7 +53532,7 @@
       </c>
       <c r="F88"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53550,7 +53550,7 @@
       </c>
       <c r="F89"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53568,7 +53568,7 @@
       </c>
       <c r="F90"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53586,7 +53586,7 @@
       </c>
       <c r="F91"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53604,7 +53604,7 @@
       </c>
       <c r="F92"/>
     </row>
-    <row r="93" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53624,7 +53624,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53644,7 +53644,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53664,7 +53664,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53684,7 +53684,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53704,7 +53704,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53724,7 +53724,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53744,7 +53744,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53764,7 +53764,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53784,7 +53784,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53804,7 +53804,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53824,7 +53824,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53844,7 +53844,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53862,7 +53862,7 @@
       </c>
       <c r="F105"/>
     </row>
-    <row r="106" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53880,7 +53880,7 @@
       </c>
       <c r="F106"/>
     </row>
-    <row r="107" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53898,7 +53898,7 @@
       </c>
       <c r="F107"/>
     </row>
-    <row r="108" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53916,7 +53916,7 @@
       </c>
       <c r="F108"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53934,7 +53934,7 @@
       </c>
       <c r="F109"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53952,7 +53952,7 @@
       </c>
       <c r="F110"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53970,7 +53970,7 @@
       </c>
       <c r="F111"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53988,7 +53988,7 @@
       </c>
       <c r="F112"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54006,7 +54006,7 @@
       </c>
       <c r="F113"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54024,7 +54024,7 @@
       </c>
       <c r="F114"/>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54042,7 +54042,7 @@
       </c>
       <c r="F115"/>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54060,7 +54060,7 @@
       </c>
       <c r="F116"/>
     </row>
-    <row r="117" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54078,7 +54078,7 @@
       </c>
       <c r="F117"/>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54096,7 +54096,7 @@
       </c>
       <c r="F118"/>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54114,7 +54114,7 @@
       </c>
       <c r="F119"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54132,7 +54132,7 @@
       </c>
       <c r="F120"/>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54150,7 +54150,7 @@
       </c>
       <c r="F121"/>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54168,7 +54168,7 @@
       </c>
       <c r="F122"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54186,7 +54186,7 @@
       </c>
       <c r="F123"/>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54204,7 +54204,7 @@
       </c>
       <c r="F124"/>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54222,7 +54222,7 @@
       </c>
       <c r="F125"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54240,7 +54240,7 @@
       </c>
       <c r="F126"/>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54366,7 +54366,7 @@
       </c>
       <c r="F133"/>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54384,7 +54384,7 @@
       </c>
       <c r="F134"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54402,7 +54402,7 @@
       </c>
       <c r="F135"/>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54420,7 +54420,7 @@
       </c>
       <c r="F136"/>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54438,7 +54438,7 @@
       </c>
       <c r="F137"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54456,7 +54456,7 @@
       </c>
       <c r="F138"/>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54474,7 +54474,7 @@
       </c>
       <c r="F139"/>
     </row>
-    <row r="140" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54492,7 +54492,7 @@
       </c>
       <c r="F140"/>
     </row>
-    <row r="141" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54510,7 +54510,7 @@
       </c>
       <c r="F141"/>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54528,7 +54528,7 @@
       </c>
       <c r="F142"/>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54546,7 +54546,7 @@
       </c>
       <c r="F143"/>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54564,7 +54564,7 @@
       </c>
       <c r="F144"/>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54582,7 +54582,7 @@
       </c>
       <c r="F145"/>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54600,7 +54600,7 @@
       </c>
       <c r="F146"/>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54618,7 +54618,7 @@
       </c>
       <c r="F147"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54636,7 +54636,7 @@
       </c>
       <c r="F148"/>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54654,7 +54654,7 @@
       </c>
       <c r="F149"/>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54672,7 +54672,7 @@
       </c>
       <c r="F150"/>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54690,7 +54690,7 @@
       </c>
       <c r="F151"/>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54708,7 +54708,7 @@
       </c>
       <c r="F152"/>
     </row>
-    <row r="153" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54726,7 +54726,7 @@
       </c>
       <c r="F153"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54744,7 +54744,7 @@
       </c>
       <c r="F154"/>
     </row>
-    <row r="155" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54762,7 +54762,7 @@
       </c>
       <c r="F155"/>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54780,7 +54780,7 @@
       </c>
       <c r="F156"/>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54798,7 +54798,7 @@
       </c>
       <c r="F157"/>
     </row>
-    <row r="158" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54816,7 +54816,7 @@
       </c>
       <c r="F158"/>
     </row>
-    <row r="159" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54834,7 +54834,7 @@
       </c>
       <c r="F159"/>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54852,7 +54852,7 @@
       </c>
       <c r="F160"/>
     </row>
-    <row r="161" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54870,7 +54870,7 @@
       </c>
       <c r="F161"/>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54888,7 +54888,7 @@
       </c>
       <c r="F162"/>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54906,7 +54906,7 @@
       </c>
       <c r="F163"/>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54924,7 +54924,7 @@
       </c>
       <c r="F164"/>
     </row>
-    <row r="165" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54942,7 +54942,7 @@
       </c>
       <c r="F165"/>
     </row>
-    <row r="166" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54960,7 +54960,7 @@
       </c>
       <c r="F166"/>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="F167"/>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54996,7 +54996,7 @@
       </c>
       <c r="F168"/>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55014,7 +55014,7 @@
       </c>
       <c r="F169"/>
     </row>
-    <row r="170" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55032,7 +55032,7 @@
       </c>
       <c r="F170"/>
     </row>
-    <row r="171" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55050,7 +55050,7 @@
       </c>
       <c r="F171"/>
     </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55068,7 +55068,7 @@
       </c>
       <c r="F172"/>
     </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55086,7 +55086,7 @@
       </c>
       <c r="F173"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55104,7 +55104,7 @@
       </c>
       <c r="F174"/>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55122,7 +55122,7 @@
       </c>
       <c r="F175"/>
     </row>
-    <row r="176" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55140,7 +55140,7 @@
       </c>
       <c r="F176"/>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55158,7 +55158,7 @@
       </c>
       <c r="F177"/>
     </row>
-    <row r="178" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55176,7 +55176,7 @@
       </c>
       <c r="F178"/>
     </row>
-    <row r="179" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55194,7 +55194,7 @@
       </c>
       <c r="F179"/>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55212,7 +55212,7 @@
       </c>
       <c r="F180"/>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55230,7 +55230,7 @@
       </c>
       <c r="F181"/>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55248,7 +55248,7 @@
       </c>
       <c r="F182"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55266,7 +55266,7 @@
       </c>
       <c r="F183"/>
     </row>
-    <row r="184" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55286,7 +55286,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55306,7 +55306,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55326,7 +55326,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55346,7 +55346,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55366,7 +55366,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55386,7 +55386,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55406,7 +55406,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55426,7 +55426,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55446,7 +55446,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55466,7 +55466,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55486,7 +55486,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55506,7 +55506,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="F196"/>
     </row>
-    <row r="197" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55542,7 +55542,7 @@
       </c>
       <c r="F197"/>
     </row>
-    <row r="198" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55560,7 +55560,7 @@
       </c>
       <c r="F198"/>
     </row>
-    <row r="199" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55578,7 +55578,7 @@
       </c>
       <c r="F199"/>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55596,7 +55596,7 @@
       </c>
       <c r="F200"/>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55614,7 +55614,7 @@
       </c>
       <c r="F201"/>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55632,7 +55632,7 @@
       </c>
       <c r="F202"/>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55650,7 +55650,7 @@
       </c>
       <c r="F203"/>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55668,7 +55668,7 @@
       </c>
       <c r="F204"/>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55686,7 +55686,7 @@
       </c>
       <c r="F205"/>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55704,7 +55704,7 @@
       </c>
       <c r="F206"/>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55722,7 +55722,7 @@
       </c>
       <c r="F207"/>
     </row>
-    <row r="208" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55740,7 +55740,7 @@
       </c>
       <c r="F208"/>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55758,7 +55758,7 @@
       </c>
       <c r="F209"/>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55776,7 +55776,7 @@
       </c>
       <c r="F210"/>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55794,7 +55794,7 @@
       </c>
       <c r="F211"/>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55812,7 +55812,7 @@
       </c>
       <c r="F212"/>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55830,7 +55830,7 @@
       </c>
       <c r="F213"/>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55848,7 +55848,7 @@
       </c>
       <c r="F214"/>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55866,7 +55866,7 @@
       </c>
       <c r="F215"/>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55884,7 +55884,7 @@
       </c>
       <c r="F216"/>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55902,7 +55902,7 @@
       </c>
       <c r="F217"/>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56028,7 +56028,7 @@
       </c>
       <c r="F224"/>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56046,7 +56046,7 @@
       </c>
       <c r="F225"/>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56064,7 +56064,7 @@
       </c>
       <c r="F226"/>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56082,7 +56082,7 @@
       </c>
       <c r="F227"/>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56100,7 +56100,7 @@
       </c>
       <c r="F228"/>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56118,7 +56118,7 @@
       </c>
       <c r="F229"/>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56136,7 +56136,7 @@
       </c>
       <c r="F230"/>
     </row>
-    <row r="231" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56154,7 +56154,7 @@
       </c>
       <c r="F231"/>
     </row>
-    <row r="232" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56172,7 +56172,7 @@
       </c>
       <c r="F232"/>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56190,7 +56190,7 @@
       </c>
       <c r="F233"/>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56208,7 +56208,7 @@
       </c>
       <c r="F234"/>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56226,7 +56226,7 @@
       </c>
       <c r="F235"/>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56244,7 +56244,7 @@
       </c>
       <c r="F236"/>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56262,7 +56262,7 @@
       </c>
       <c r="F237"/>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56280,7 +56280,7 @@
       </c>
       <c r="F238"/>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56298,7 +56298,7 @@
       </c>
       <c r="F239"/>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56316,7 +56316,7 @@
       </c>
       <c r="F240"/>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56334,7 +56334,7 @@
       </c>
       <c r="F241"/>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56352,7 +56352,7 @@
       </c>
       <c r="F242"/>
     </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56370,7 +56370,7 @@
       </c>
       <c r="F243"/>
     </row>
-    <row r="244" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56388,7 +56388,7 @@
       </c>
       <c r="F244"/>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56406,7 +56406,7 @@
       </c>
       <c r="F245"/>
     </row>
-    <row r="246" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56424,7 +56424,7 @@
       </c>
       <c r="F246"/>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56442,7 +56442,7 @@
       </c>
       <c r="F247"/>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56460,7 +56460,7 @@
       </c>
       <c r="F248"/>
     </row>
-    <row r="249" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56478,7 +56478,7 @@
       </c>
       <c r="F249"/>
     </row>
-    <row r="250" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56496,7 +56496,7 @@
       </c>
       <c r="F250"/>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56514,7 +56514,7 @@
       </c>
       <c r="F251"/>
     </row>
-    <row r="252" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56532,7 +56532,7 @@
       </c>
       <c r="F252"/>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56550,7 +56550,7 @@
       </c>
       <c r="F253"/>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56568,7 +56568,7 @@
       </c>
       <c r="F254"/>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56586,7 +56586,7 @@
       </c>
       <c r="F255"/>
     </row>
-    <row r="256" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56604,7 +56604,7 @@
       </c>
       <c r="F256"/>
     </row>
-    <row r="257" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56622,7 +56622,7 @@
       </c>
       <c r="F257"/>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56640,7 +56640,7 @@
       </c>
       <c r="F258"/>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56658,7 +56658,7 @@
       </c>
       <c r="F259"/>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56676,7 +56676,7 @@
       </c>
       <c r="F260"/>
     </row>
-    <row r="261" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56694,7 +56694,7 @@
       </c>
       <c r="F261"/>
     </row>
-    <row r="262" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56712,7 +56712,7 @@
       </c>
       <c r="F262"/>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56730,7 +56730,7 @@
       </c>
       <c r="F263"/>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56748,7 +56748,7 @@
       </c>
       <c r="F264"/>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56766,7 +56766,7 @@
       </c>
       <c r="F265"/>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56784,7 +56784,7 @@
       </c>
       <c r="F266"/>
     </row>
-    <row r="267" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56802,7 +56802,7 @@
       </c>
       <c r="F267"/>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56820,7 +56820,7 @@
       </c>
       <c r="F268"/>
     </row>
-    <row r="269" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56838,7 +56838,7 @@
       </c>
       <c r="F269"/>
     </row>
-    <row r="270" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56856,7 +56856,7 @@
       </c>
       <c r="F270"/>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56874,7 +56874,7 @@
       </c>
       <c r="F271"/>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56892,7 +56892,7 @@
       </c>
       <c r="F272"/>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56910,7 +56910,7 @@
       </c>
       <c r="F273"/>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56928,7 +56928,7 @@
       </c>
       <c r="F274"/>
     </row>
-    <row r="275" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>1119</v>
       </c>
@@ -56948,7 +56948,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>1119</v>
       </c>
@@ -56968,7 +56968,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>1119</v>
       </c>
@@ -56988,7 +56988,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57008,7 +57008,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="279" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57028,7 +57028,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57048,7 +57048,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57068,7 +57068,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57088,7 +57088,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="283" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57108,7 +57108,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="284" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57128,7 +57128,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57148,7 +57148,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57168,7 +57168,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="287" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57188,7 +57188,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="288" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57208,7 +57208,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57226,7 +57226,7 @@
       </c>
       <c r="F289"/>
     </row>
-    <row r="290" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57244,7 +57244,7 @@
       </c>
       <c r="F290"/>
     </row>
-    <row r="291" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57262,7 +57262,7 @@
       </c>
       <c r="F291"/>
     </row>
-    <row r="292" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57280,7 +57280,7 @@
       </c>
       <c r="F292"/>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57298,7 +57298,7 @@
       </c>
       <c r="F293"/>
     </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57316,7 +57316,7 @@
       </c>
       <c r="F294"/>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57334,7 +57334,7 @@
       </c>
       <c r="F295"/>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57352,7 +57352,7 @@
       </c>
       <c r="F296"/>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57370,7 +57370,7 @@
       </c>
       <c r="F297"/>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57388,7 +57388,7 @@
       </c>
       <c r="F298"/>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57406,7 +57406,7 @@
       </c>
       <c r="F299"/>
     </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57424,7 +57424,7 @@
       </c>
       <c r="F300"/>
     </row>
-    <row r="301" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57442,7 +57442,7 @@
       </c>
       <c r="F301"/>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57460,7 +57460,7 @@
       </c>
       <c r="F302"/>
     </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57478,7 +57478,7 @@
       </c>
       <c r="F303"/>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57496,7 +57496,7 @@
       </c>
       <c r="F304"/>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57514,7 +57514,7 @@
       </c>
       <c r="F305"/>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57532,7 +57532,7 @@
       </c>
       <c r="F306"/>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57550,7 +57550,7 @@
       </c>
       <c r="F307"/>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57568,7 +57568,7 @@
       </c>
       <c r="F308"/>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57586,7 +57586,7 @@
       </c>
       <c r="F309"/>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57604,7 +57604,7 @@
       </c>
       <c r="F310"/>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57730,7 +57730,7 @@
       </c>
       <c r="F317"/>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57748,7 +57748,7 @@
       </c>
       <c r="F318"/>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57766,7 +57766,7 @@
       </c>
       <c r="F319"/>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57784,7 +57784,7 @@
       </c>
       <c r="F320"/>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57802,7 +57802,7 @@
       </c>
       <c r="F321"/>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57820,7 +57820,7 @@
       </c>
       <c r="F322"/>
     </row>
-    <row r="323" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57838,7 +57838,7 @@
       </c>
       <c r="F323"/>
     </row>
-    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57856,7 +57856,7 @@
       </c>
       <c r="F324"/>
     </row>
-    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57874,7 +57874,7 @@
       </c>
       <c r="F325"/>
     </row>
-    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57892,7 +57892,7 @@
       </c>
       <c r="F326"/>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57910,7 +57910,7 @@
       </c>
       <c r="F327"/>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57928,7 +57928,7 @@
       </c>
       <c r="F328"/>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57946,7 +57946,7 @@
       </c>
       <c r="F329"/>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57964,7 +57964,7 @@
       </c>
       <c r="F330"/>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57982,7 +57982,7 @@
       </c>
       <c r="F331"/>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58000,7 +58000,7 @@
       </c>
       <c r="F332"/>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58018,7 +58018,7 @@
       </c>
       <c r="F333"/>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58036,7 +58036,7 @@
       </c>
       <c r="F334"/>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58054,7 +58054,7 @@
       </c>
       <c r="F335"/>
     </row>
-    <row r="336" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="F336"/>
     </row>
-    <row r="337" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58090,7 +58090,7 @@
       </c>
       <c r="F337"/>
     </row>
-    <row r="338" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58108,7 +58108,7 @@
       </c>
       <c r="F338"/>
     </row>
-    <row r="339" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58126,7 +58126,7 @@
       </c>
       <c r="F339"/>
     </row>
-    <row r="340" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58144,7 +58144,7 @@
       </c>
       <c r="F340"/>
     </row>
-    <row r="341" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58162,7 +58162,7 @@
       </c>
       <c r="F341"/>
     </row>
-    <row r="342" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58180,7 +58180,7 @@
       </c>
       <c r="F342"/>
     </row>
-    <row r="343" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58198,7 +58198,7 @@
       </c>
       <c r="F343"/>
     </row>
-    <row r="344" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58216,7 +58216,7 @@
       </c>
       <c r="F344"/>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58234,7 +58234,7 @@
       </c>
       <c r="F345"/>
     </row>
-    <row r="346" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58252,7 +58252,7 @@
       </c>
       <c r="F346"/>
     </row>
-    <row r="347" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58270,7 +58270,7 @@
       </c>
       <c r="F347"/>
     </row>
-    <row r="348" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58288,7 +58288,7 @@
       </c>
       <c r="F348"/>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58306,7 +58306,7 @@
       </c>
       <c r="F349"/>
     </row>
-    <row r="350" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58324,7 +58324,7 @@
       </c>
       <c r="F350"/>
     </row>
-    <row r="351" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58342,7 +58342,7 @@
       </c>
       <c r="F351"/>
     </row>
-    <row r="352" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58360,7 +58360,7 @@
       </c>
       <c r="F352"/>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58378,7 +58378,7 @@
       </c>
       <c r="F353"/>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58396,7 +58396,7 @@
       </c>
       <c r="F354"/>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58414,7 +58414,7 @@
       </c>
       <c r="F355"/>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58432,7 +58432,7 @@
       </c>
       <c r="F356"/>
     </row>
-    <row r="357" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58450,7 +58450,7 @@
       </c>
       <c r="F357"/>
     </row>
-    <row r="358" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58468,7 +58468,7 @@
       </c>
       <c r="F358"/>
     </row>
-    <row r="359" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58486,7 +58486,7 @@
       </c>
       <c r="F359"/>
     </row>
-    <row r="360" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58504,7 +58504,7 @@
       </c>
       <c r="F360"/>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58522,7 +58522,7 @@
       </c>
       <c r="F361"/>
     </row>
-    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58540,7 +58540,7 @@
       </c>
       <c r="F362"/>
     </row>
-    <row r="363" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58558,7 +58558,7 @@
       </c>
       <c r="F363"/>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58576,7 +58576,7 @@
       </c>
       <c r="F364"/>
     </row>
-    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58594,7 +58594,7 @@
       </c>
       <c r="F365"/>
     </row>
-    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58612,7 +58612,7 @@
       </c>
       <c r="F366"/>
     </row>
-    <row r="367" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58632,7 +58632,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58652,7 +58652,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58672,7 +58672,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58692,7 +58692,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="371" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58712,7 +58712,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58732,7 +58732,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58752,7 +58752,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58772,7 +58772,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="375" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58792,7 +58792,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="376" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58812,7 +58812,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58832,7 +58832,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58852,7 +58852,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58872,7 +58872,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="380" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58892,7 +58892,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="381" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58910,7 +58910,7 @@
       </c>
       <c r="F381"/>
     </row>
-    <row r="382" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58928,7 +58928,7 @@
       </c>
       <c r="F382"/>
     </row>
-    <row r="383" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58946,7 +58946,7 @@
       </c>
       <c r="F383"/>
     </row>
-    <row r="384" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58964,7 +58964,7 @@
       </c>
       <c r="F384"/>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="F385"/>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59000,7 +59000,7 @@
       </c>
       <c r="F386"/>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59018,7 +59018,7 @@
       </c>
       <c r="F387"/>
     </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59036,7 +59036,7 @@
       </c>
       <c r="F388"/>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59054,7 +59054,7 @@
       </c>
       <c r="F389"/>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59072,7 +59072,7 @@
       </c>
       <c r="F390"/>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59090,7 +59090,7 @@
       </c>
       <c r="F391"/>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59108,7 +59108,7 @@
       </c>
       <c r="F392"/>
     </row>
-    <row r="393" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59126,7 +59126,7 @@
       </c>
       <c r="F393"/>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59144,7 +59144,7 @@
       </c>
       <c r="F394"/>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59162,7 +59162,7 @@
       </c>
       <c r="F395"/>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59180,7 +59180,7 @@
       </c>
       <c r="F396"/>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59198,7 +59198,7 @@
       </c>
       <c r="F397"/>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59216,7 +59216,7 @@
       </c>
       <c r="F398"/>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59234,7 +59234,7 @@
       </c>
       <c r="F399"/>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59252,7 +59252,7 @@
       </c>
       <c r="F400"/>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59270,7 +59270,7 @@
       </c>
       <c r="F401"/>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59288,7 +59288,7 @@
       </c>
       <c r="F402"/>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59414,7 +59414,7 @@
       </c>
       <c r="F409"/>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59432,7 +59432,7 @@
       </c>
       <c r="F410"/>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59450,7 +59450,7 @@
       </c>
       <c r="F411"/>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59468,7 +59468,7 @@
       </c>
       <c r="F412"/>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59486,7 +59486,7 @@
       </c>
       <c r="F413"/>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59504,7 +59504,7 @@
       </c>
       <c r="F414"/>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59522,7 +59522,7 @@
       </c>
       <c r="F415"/>
     </row>
-    <row r="416" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59540,7 +59540,7 @@
       </c>
       <c r="F416"/>
     </row>
-    <row r="417" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59558,7 +59558,7 @@
       </c>
       <c r="F417"/>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59576,7 +59576,7 @@
       </c>
       <c r="F418"/>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59594,7 +59594,7 @@
       </c>
       <c r="F419"/>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59612,7 +59612,7 @@
       </c>
       <c r="F420"/>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59630,7 +59630,7 @@
       </c>
       <c r="F421"/>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59648,7 +59648,7 @@
       </c>
       <c r="F422"/>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59666,7 +59666,7 @@
       </c>
       <c r="F423"/>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59684,7 +59684,7 @@
       </c>
       <c r="F424"/>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59702,7 +59702,7 @@
       </c>
       <c r="F425"/>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59720,7 +59720,7 @@
       </c>
       <c r="F426"/>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59738,7 +59738,7 @@
       </c>
       <c r="F427"/>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59756,7 +59756,7 @@
       </c>
       <c r="F428"/>
     </row>
-    <row r="429" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59774,7 +59774,7 @@
       </c>
       <c r="F429"/>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59792,7 +59792,7 @@
       </c>
       <c r="F430"/>
     </row>
-    <row r="431" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59810,7 +59810,7 @@
       </c>
       <c r="F431"/>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59828,7 +59828,7 @@
       </c>
       <c r="F432"/>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59846,7 +59846,7 @@
       </c>
       <c r="F433"/>
     </row>
-    <row r="434" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59864,7 +59864,7 @@
       </c>
       <c r="F434"/>
     </row>
-    <row r="435" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59882,7 +59882,7 @@
       </c>
       <c r="F435"/>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59900,7 +59900,7 @@
       </c>
       <c r="F436"/>
     </row>
-    <row r="437" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59918,7 +59918,7 @@
       </c>
       <c r="F437"/>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59936,7 +59936,7 @@
       </c>
       <c r="F438"/>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59954,7 +59954,7 @@
       </c>
       <c r="F439"/>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59972,7 +59972,7 @@
       </c>
       <c r="F440"/>
     </row>
-    <row r="441" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59990,7 +59990,7 @@
       </c>
       <c r="F441"/>
     </row>
-    <row r="442" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60008,7 +60008,7 @@
       </c>
       <c r="F442"/>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60026,7 +60026,7 @@
       </c>
       <c r="F443"/>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60044,7 +60044,7 @@
       </c>
       <c r="F444"/>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60062,7 +60062,7 @@
       </c>
       <c r="F445"/>
     </row>
-    <row r="446" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60080,7 +60080,7 @@
       </c>
       <c r="F446"/>
     </row>
-    <row r="447" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60098,7 +60098,7 @@
       </c>
       <c r="F447"/>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60116,7 +60116,7 @@
       </c>
       <c r="F448"/>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60134,7 +60134,7 @@
       </c>
       <c r="F449"/>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60152,7 +60152,7 @@
       </c>
       <c r="F450"/>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60170,7 +60170,7 @@
       </c>
       <c r="F451"/>
     </row>
-    <row r="452" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60188,7 +60188,7 @@
       </c>
       <c r="F452"/>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60206,7 +60206,7 @@
       </c>
       <c r="F453"/>
     </row>
-    <row r="454" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60224,7 +60224,7 @@
       </c>
       <c r="F454"/>
     </row>
-    <row r="455" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60242,7 +60242,7 @@
       </c>
       <c r="F455"/>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60260,7 +60260,7 @@
       </c>
       <c r="F456"/>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60278,7 +60278,7 @@
       </c>
       <c r="F457"/>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60296,7 +60296,7 @@
       </c>
       <c r="F458"/>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60314,7 +60314,7 @@
       </c>
       <c r="F459"/>
     </row>
-    <row r="460" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60334,7 +60334,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60354,7 +60354,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60374,7 +60374,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60394,7 +60394,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="464" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60414,7 +60414,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60434,7 +60434,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60454,7 +60454,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60474,7 +60474,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="468" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60494,7 +60494,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="469" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60514,7 +60514,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60534,7 +60534,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60554,7 +60554,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="472" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60574,7 +60574,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="473" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60594,7 +60594,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="474" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60612,7 +60612,7 @@
       </c>
       <c r="F474"/>
     </row>
-    <row r="475" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60630,7 +60630,7 @@
       </c>
       <c r="F475"/>
     </row>
-    <row r="476" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60648,7 +60648,7 @@
       </c>
       <c r="F476"/>
     </row>
-    <row r="477" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60666,7 +60666,7 @@
       </c>
       <c r="F477"/>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60684,7 +60684,7 @@
       </c>
       <c r="F478"/>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60702,7 +60702,7 @@
       </c>
       <c r="F479"/>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60720,7 +60720,7 @@
       </c>
       <c r="F480"/>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60738,7 +60738,7 @@
       </c>
       <c r="F481"/>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60756,7 +60756,7 @@
       </c>
       <c r="F482"/>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60774,7 +60774,7 @@
       </c>
       <c r="F483"/>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60792,7 +60792,7 @@
       </c>
       <c r="F484"/>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60810,7 +60810,7 @@
       </c>
       <c r="F485"/>
     </row>
-    <row r="486" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60828,7 +60828,7 @@
       </c>
       <c r="F486"/>
     </row>
-    <row r="487" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60846,7 +60846,7 @@
       </c>
       <c r="F487"/>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60864,7 +60864,7 @@
       </c>
       <c r="F488"/>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60882,7 +60882,7 @@
       </c>
       <c r="F489"/>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60900,7 +60900,7 @@
       </c>
       <c r="F490"/>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60918,7 +60918,7 @@
       </c>
       <c r="F491"/>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60936,7 +60936,7 @@
       </c>
       <c r="F492"/>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60954,7 +60954,7 @@
       </c>
       <c r="F493"/>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60972,7 +60972,7 @@
       </c>
       <c r="F494"/>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60990,7 +60990,7 @@
       </c>
       <c r="F495"/>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61116,7 +61116,7 @@
       </c>
       <c r="F502"/>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61134,7 +61134,7 @@
       </c>
       <c r="F503"/>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61152,7 +61152,7 @@
       </c>
       <c r="F504"/>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61170,7 +61170,7 @@
       </c>
       <c r="F505"/>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61188,7 +61188,7 @@
       </c>
       <c r="F506"/>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61206,7 +61206,7 @@
       </c>
       <c r="F507"/>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61224,7 +61224,7 @@
       </c>
       <c r="F508"/>
     </row>
-    <row r="509" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61242,7 +61242,7 @@
       </c>
       <c r="F509"/>
     </row>
-    <row r="510" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61260,7 +61260,7 @@
       </c>
       <c r="F510"/>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61278,7 +61278,7 @@
       </c>
       <c r="F511"/>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61296,7 +61296,7 @@
       </c>
       <c r="F512"/>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61314,7 +61314,7 @@
       </c>
       <c r="F513"/>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61332,7 +61332,7 @@
       </c>
       <c r="F514"/>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61350,7 +61350,7 @@
       </c>
       <c r="F515"/>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61368,7 +61368,7 @@
       </c>
       <c r="F516"/>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61386,7 +61386,7 @@
       </c>
       <c r="F517"/>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61404,7 +61404,7 @@
       </c>
       <c r="F518"/>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61422,7 +61422,7 @@
       </c>
       <c r="F519"/>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61440,7 +61440,7 @@
       </c>
       <c r="F520"/>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61458,7 +61458,7 @@
       </c>
       <c r="F521"/>
     </row>
-    <row r="522" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61476,7 +61476,7 @@
       </c>
       <c r="F522"/>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61494,7 +61494,7 @@
       </c>
       <c r="F523"/>
     </row>
-    <row r="524" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61512,7 +61512,7 @@
       </c>
       <c r="F524"/>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61530,7 +61530,7 @@
       </c>
       <c r="F525"/>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61548,7 +61548,7 @@
       </c>
       <c r="F526"/>
     </row>
-    <row r="527" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61566,7 +61566,7 @@
       </c>
       <c r="F527"/>
     </row>
-    <row r="528" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61584,7 +61584,7 @@
       </c>
       <c r="F528"/>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61602,7 +61602,7 @@
       </c>
       <c r="F529"/>
     </row>
-    <row r="530" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61620,7 +61620,7 @@
       </c>
       <c r="F530"/>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61638,7 +61638,7 @@
       </c>
       <c r="F531"/>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61656,7 +61656,7 @@
       </c>
       <c r="F532"/>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61674,7 +61674,7 @@
       </c>
       <c r="F533"/>
     </row>
-    <row r="534" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61692,7 +61692,7 @@
       </c>
       <c r="F534"/>
     </row>
-    <row r="535" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61710,7 +61710,7 @@
       </c>
       <c r="F535"/>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61728,7 +61728,7 @@
       </c>
       <c r="F536"/>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61746,7 +61746,7 @@
       </c>
       <c r="F537"/>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61764,7 +61764,7 @@
       </c>
       <c r="F538"/>
     </row>
-    <row r="539" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61782,7 +61782,7 @@
       </c>
       <c r="F539"/>
     </row>
-    <row r="540" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61800,7 +61800,7 @@
       </c>
       <c r="F540"/>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61818,7 +61818,7 @@
       </c>
       <c r="F541"/>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A542" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61836,7 +61836,7 @@
       </c>
       <c r="F542"/>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61854,7 +61854,7 @@
       </c>
       <c r="F543"/>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61872,7 +61872,7 @@
       </c>
       <c r="F544"/>
     </row>
-    <row r="545" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61890,7 +61890,7 @@
       </c>
       <c r="F545"/>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61908,7 +61908,7 @@
       </c>
       <c r="F546"/>
     </row>
-    <row r="547" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61926,7 +61926,7 @@
       </c>
       <c r="F547"/>
     </row>
-    <row r="548" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61944,7 +61944,7 @@
       </c>
       <c r="F548"/>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61962,7 +61962,7 @@
       </c>
       <c r="F549"/>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61980,7 +61980,7 @@
       </c>
       <c r="F550"/>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61998,7 +61998,7 @@
       </c>
       <c r="F551"/>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" s="4" t="s">
         <v>1121</v>
       </c>
@@ -62016,7 +62016,7 @@
       </c>
       <c r="F552"/>
     </row>
-    <row r="553" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62036,7 +62036,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62056,7 +62056,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62076,7 +62076,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62096,7 +62096,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="557" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62116,7 +62116,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A558" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62136,7 +62136,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A559" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62156,7 +62156,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62176,7 +62176,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="561" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A561" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62196,7 +62196,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="562" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62216,7 +62216,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62236,7 +62236,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62256,7 +62256,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="565" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62276,7 +62276,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="566" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A566" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62296,7 +62296,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="567" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A567" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62314,7 +62314,7 @@
       </c>
       <c r="F567"/>
     </row>
-    <row r="568" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62332,7 +62332,7 @@
       </c>
       <c r="F568"/>
     </row>
-    <row r="569" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62350,7 +62350,7 @@
       </c>
       <c r="F569"/>
     </row>
-    <row r="570" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62368,7 +62368,7 @@
       </c>
       <c r="F570"/>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62386,7 +62386,7 @@
       </c>
       <c r="F571"/>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62404,7 +62404,7 @@
       </c>
       <c r="F572"/>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62422,7 +62422,7 @@
       </c>
       <c r="F573"/>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62440,7 +62440,7 @@
       </c>
       <c r="F574"/>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62458,7 +62458,7 @@
       </c>
       <c r="F575"/>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A576" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62476,7 +62476,7 @@
       </c>
       <c r="F576"/>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62494,7 +62494,7 @@
       </c>
       <c r="F577"/>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62512,7 +62512,7 @@
       </c>
       <c r="F578"/>
     </row>
-    <row r="579" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62530,7 +62530,7 @@
       </c>
       <c r="F579"/>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62548,7 +62548,7 @@
       </c>
       <c r="F580"/>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A581" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62566,7 +62566,7 @@
       </c>
       <c r="F581"/>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62584,7 +62584,7 @@
       </c>
       <c r="F582"/>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62602,7 +62602,7 @@
       </c>
       <c r="F583"/>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62620,7 +62620,7 @@
       </c>
       <c r="F584"/>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62638,7 +62638,7 @@
       </c>
       <c r="F585"/>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62656,7 +62656,7 @@
       </c>
       <c r="F586"/>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62674,7 +62674,7 @@
       </c>
       <c r="F587"/>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62692,7 +62692,7 @@
       </c>
       <c r="F588"/>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62818,7 +62818,7 @@
       </c>
       <c r="F595"/>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62836,7 +62836,7 @@
       </c>
       <c r="F596"/>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62854,7 +62854,7 @@
       </c>
       <c r="F597"/>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62872,7 +62872,7 @@
       </c>
       <c r="F598"/>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62890,7 +62890,7 @@
       </c>
       <c r="F599"/>
     </row>
-    <row r="600" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62908,7 +62908,7 @@
       </c>
       <c r="F600"/>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A601" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62926,7 +62926,7 @@
       </c>
       <c r="F601"/>
     </row>
-    <row r="602" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62944,7 +62944,7 @@
       </c>
       <c r="F602"/>
     </row>
-    <row r="603" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62962,7 +62962,7 @@
       </c>
       <c r="F603"/>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A604" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62980,7 +62980,7 @@
       </c>
       <c r="F604"/>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62998,7 +62998,7 @@
       </c>
       <c r="F605"/>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63016,7 +63016,7 @@
       </c>
       <c r="F606"/>
     </row>
-    <row r="607" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63034,7 +63034,7 @@
       </c>
       <c r="F607"/>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63052,7 +63052,7 @@
       </c>
       <c r="F608"/>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A609" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63070,7 +63070,7 @@
       </c>
       <c r="F609"/>
     </row>
-    <row r="610" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63088,7 +63088,7 @@
       </c>
       <c r="F610"/>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A611" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63106,7 +63106,7 @@
       </c>
       <c r="F611"/>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63124,7 +63124,7 @@
       </c>
       <c r="F612"/>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A613" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63142,7 +63142,7 @@
       </c>
       <c r="F613"/>
     </row>
-    <row r="614" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63160,7 +63160,7 @@
       </c>
       <c r="F614"/>
     </row>
-    <row r="615" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A615" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63178,7 +63178,7 @@
       </c>
       <c r="F615"/>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A616" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63196,7 +63196,7 @@
       </c>
       <c r="F616"/>
     </row>
-    <row r="617" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63214,7 +63214,7 @@
       </c>
       <c r="F617"/>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A618" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63232,7 +63232,7 @@
       </c>
       <c r="F618"/>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A619" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63250,7 +63250,7 @@
       </c>
       <c r="F619"/>
     </row>
-    <row r="620" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A620" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63268,7 +63268,7 @@
       </c>
       <c r="F620"/>
     </row>
-    <row r="621" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A621" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63286,7 +63286,7 @@
       </c>
       <c r="F621"/>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A622" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63304,7 +63304,7 @@
       </c>
       <c r="F622"/>
     </row>
-    <row r="623" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A623" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63322,7 +63322,7 @@
       </c>
       <c r="F623"/>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A624" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63340,7 +63340,7 @@
       </c>
       <c r="F624"/>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A625" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63358,7 +63358,7 @@
       </c>
       <c r="F625"/>
     </row>
-    <row r="626" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A626" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63376,7 +63376,7 @@
       </c>
       <c r="F626"/>
     </row>
-    <row r="627" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A627" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63394,7 +63394,7 @@
       </c>
       <c r="F627"/>
     </row>
-    <row r="628" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A628" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63412,7 +63412,7 @@
       </c>
       <c r="F628"/>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A629" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63430,7 +63430,7 @@
       </c>
       <c r="F629"/>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A630" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63448,7 +63448,7 @@
       </c>
       <c r="F630"/>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A631" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63466,7 +63466,7 @@
       </c>
       <c r="F631"/>
     </row>
-    <row r="632" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A632" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63484,7 +63484,7 @@
       </c>
       <c r="F632"/>
     </row>
-    <row r="633" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A633" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63502,7 +63502,7 @@
       </c>
       <c r="F633"/>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A634" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63520,7 +63520,7 @@
       </c>
       <c r="F634"/>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A635" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63538,7 +63538,7 @@
       </c>
       <c r="F635"/>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A636" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63556,7 +63556,7 @@
       </c>
       <c r="F636"/>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A637" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63574,7 +63574,7 @@
       </c>
       <c r="F637"/>
     </row>
-    <row r="638" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A638" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63592,7 +63592,7 @@
       </c>
       <c r="F638"/>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A639" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63610,7 +63610,7 @@
       </c>
       <c r="F639"/>
     </row>
-    <row r="640" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A640" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63628,7 +63628,7 @@
       </c>
       <c r="F640"/>
     </row>
-    <row r="641" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A641" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63646,7 +63646,7 @@
       </c>
       <c r="F641"/>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A642" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63664,7 +63664,7 @@
       </c>
       <c r="F642"/>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A643" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63682,7 +63682,7 @@
       </c>
       <c r="F643"/>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A644" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63700,7 +63700,7 @@
       </c>
       <c r="F644"/>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A645" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63718,7 +63718,7 @@
       </c>
       <c r="F645"/>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A646" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63738,7 +63738,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A647" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63758,7 +63758,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="648" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A648" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63778,7 +63778,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A649" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63795,7 +63795,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A650" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63815,7 +63815,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A651" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63835,7 +63835,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A652" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63855,7 +63855,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A653" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63875,7 +63875,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="654" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A654" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63895,7 +63895,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="655" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A655" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63915,7 +63915,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="656" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A656" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63933,7 +63933,7 @@
       </c>
       <c r="F656"/>
     </row>
-    <row r="657" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A657" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63951,7 +63951,7 @@
       </c>
       <c r="F657"/>
     </row>
-    <row r="658" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A658" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63969,7 +63969,7 @@
       </c>
       <c r="F658"/>
     </row>
-    <row r="659" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A659" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63987,7 +63987,7 @@
       </c>
       <c r="F659"/>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A660" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64005,7 +64005,7 @@
       </c>
       <c r="F660"/>
     </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A661" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64023,7 +64023,7 @@
       </c>
       <c r="F661"/>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A662" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64041,7 +64041,7 @@
       </c>
       <c r="F662"/>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A663" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64059,7 +64059,7 @@
       </c>
       <c r="F663"/>
     </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A664" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64077,7 +64077,7 @@
       </c>
       <c r="F664"/>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A665" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64095,7 +64095,7 @@
       </c>
       <c r="F665"/>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A666" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64113,7 +64113,7 @@
       </c>
       <c r="F666"/>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A667" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64131,7 +64131,7 @@
       </c>
       <c r="F667"/>
     </row>
-    <row r="668" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A668" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64149,7 +64149,7 @@
       </c>
       <c r="F668"/>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A669" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64167,7 +64167,7 @@
       </c>
       <c r="F669"/>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A670" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64185,7 +64185,7 @@
       </c>
       <c r="F670"/>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A671" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64203,7 +64203,7 @@
       </c>
       <c r="F671"/>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A672" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64221,7 +64221,7 @@
       </c>
       <c r="F672"/>
     </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A673" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64239,7 +64239,7 @@
       </c>
       <c r="F673"/>
     </row>
-    <row r="674" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A674" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64257,7 +64257,7 @@
       </c>
       <c r="F674"/>
     </row>
-    <row r="675" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A675" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64275,7 +64275,7 @@
       </c>
       <c r="F675"/>
     </row>
-    <row r="676" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A676" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64293,7 +64293,7 @@
       </c>
       <c r="F676"/>
     </row>
-    <row r="677" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A677" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64311,7 +64311,7 @@
       </c>
       <c r="F677"/>
     </row>
-    <row r="678" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A678" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64437,7 +64437,7 @@
       </c>
       <c r="F684"/>
     </row>
-    <row r="685" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A685" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64455,7 +64455,7 @@
       </c>
       <c r="F685"/>
     </row>
-    <row r="686" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A686" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64473,7 +64473,7 @@
       </c>
       <c r="F686"/>
     </row>
-    <row r="687" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A687" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64491,7 +64491,7 @@
       </c>
       <c r="F687"/>
     </row>
-    <row r="688" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A688" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64509,7 +64509,7 @@
       </c>
       <c r="F688"/>
     </row>
-    <row r="689" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A689" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64527,7 +64527,7 @@
       </c>
       <c r="F689"/>
     </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A690" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64545,7 +64545,7 @@
       </c>
       <c r="F690"/>
     </row>
-    <row r="691" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A691" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64563,7 +64563,7 @@
       </c>
       <c r="F691"/>
     </row>
-    <row r="692" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A692" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64581,7 +64581,7 @@
       </c>
       <c r="F692"/>
     </row>
-    <row r="693" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A693" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64599,7 +64599,7 @@
       </c>
       <c r="F693"/>
     </row>
-    <row r="694" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A694" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64617,7 +64617,7 @@
       </c>
       <c r="F694"/>
     </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A695" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64635,7 +64635,7 @@
       </c>
       <c r="F695"/>
     </row>
-    <row r="696" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A696" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64653,7 +64653,7 @@
       </c>
       <c r="F696"/>
     </row>
-    <row r="697" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A697" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64671,7 +64671,7 @@
       </c>
       <c r="F697"/>
     </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A698" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64689,7 +64689,7 @@
       </c>
       <c r="F698"/>
     </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A699" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64707,7 +64707,7 @@
       </c>
       <c r="F699"/>
     </row>
-    <row r="700" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A700" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64725,7 +64725,7 @@
       </c>
       <c r="F700"/>
     </row>
-    <row r="701" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A701" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64743,7 +64743,7 @@
       </c>
       <c r="F701"/>
     </row>
-    <row r="702" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A702" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64761,7 +64761,7 @@
       </c>
       <c r="F702"/>
     </row>
-    <row r="703" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A703" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64779,7 +64779,7 @@
       </c>
       <c r="F703"/>
     </row>
-    <row r="704" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A704" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64797,7 +64797,7 @@
       </c>
       <c r="F704"/>
     </row>
-    <row r="705" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A705" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64815,7 +64815,7 @@
       </c>
       <c r="F705"/>
     </row>
-    <row r="706" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A706" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64833,7 +64833,7 @@
       </c>
       <c r="F706"/>
     </row>
-    <row r="707" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A707" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64851,7 +64851,7 @@
       </c>
       <c r="F707"/>
     </row>
-    <row r="708" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A708" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64869,7 +64869,7 @@
       </c>
       <c r="F708"/>
     </row>
-    <row r="709" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A709" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64887,7 +64887,7 @@
       </c>
       <c r="F709"/>
     </row>
-    <row r="710" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A710" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64905,7 +64905,7 @@
       </c>
       <c r="F710"/>
     </row>
-    <row r="711" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A711" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64923,7 +64923,7 @@
       </c>
       <c r="F711"/>
     </row>
-    <row r="712" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A712" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64941,7 +64941,7 @@
       </c>
       <c r="F712"/>
     </row>
-    <row r="713" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A713" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64959,7 +64959,7 @@
       </c>
       <c r="F713"/>
     </row>
-    <row r="714" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A714" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64977,7 +64977,7 @@
       </c>
       <c r="F714"/>
     </row>
-    <row r="715" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A715" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64995,7 +64995,7 @@
       </c>
       <c r="F715"/>
     </row>
-    <row r="716" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A716" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65013,7 +65013,7 @@
       </c>
       <c r="F716"/>
     </row>
-    <row r="717" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A717" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65031,7 +65031,7 @@
       </c>
       <c r="F717"/>
     </row>
-    <row r="718" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A718" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65049,7 +65049,7 @@
       </c>
       <c r="F718"/>
     </row>
-    <row r="719" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A719" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65067,7 +65067,7 @@
       </c>
       <c r="F719"/>
     </row>
-    <row r="720" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A720" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65085,7 +65085,7 @@
       </c>
       <c r="F720"/>
     </row>
-    <row r="721" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A721" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65103,7 +65103,7 @@
       </c>
       <c r="F721"/>
     </row>
-    <row r="722" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A722" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65121,7 +65121,7 @@
       </c>
       <c r="F722"/>
     </row>
-    <row r="723" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A723" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65139,7 +65139,7 @@
       </c>
       <c r="F723"/>
     </row>
-    <row r="724" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A724" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65157,7 +65157,7 @@
       </c>
       <c r="F724"/>
     </row>
-    <row r="725" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A725" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65175,7 +65175,7 @@
       </c>
       <c r="F725"/>
     </row>
-    <row r="726" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A726" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65193,7 +65193,7 @@
       </c>
       <c r="F726"/>
     </row>
-    <row r="727" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A727" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65211,7 +65211,7 @@
       </c>
       <c r="F727"/>
     </row>
-    <row r="728" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A728" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65229,7 +65229,7 @@
       </c>
       <c r="F728"/>
     </row>
-    <row r="729" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A729" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65247,7 +65247,7 @@
       </c>
       <c r="F729"/>
     </row>
-    <row r="730" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A730" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65265,7 +65265,7 @@
       </c>
       <c r="F730"/>
     </row>
-    <row r="731" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A731" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65283,7 +65283,7 @@
       </c>
       <c r="F731"/>
     </row>
-    <row r="732" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A732" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65301,7 +65301,7 @@
       </c>
       <c r="F732"/>
     </row>
-    <row r="733" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A733" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65319,7 +65319,7 @@
       </c>
       <c r="F733"/>
     </row>
-    <row r="734" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A734" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65337,7 +65337,7 @@
       </c>
       <c r="F734"/>
     </row>
-    <row r="735" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A735" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65357,7 +65357,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="736" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A736" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65377,7 +65377,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A737" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65397,7 +65397,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A738" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65417,7 +65417,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="739" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A739" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65437,7 +65437,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A740" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65457,7 +65457,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A741" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65477,7 +65477,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="742" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A742" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65497,7 +65497,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A743" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65517,7 +65517,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A744" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65537,7 +65537,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="745" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A745" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65557,7 +65557,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="746" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A746" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65577,7 +65577,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="747" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A747" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65595,7 +65595,7 @@
       </c>
       <c r="F747"/>
     </row>
-    <row r="748" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A748" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65613,7 +65613,7 @@
       </c>
       <c r="F748"/>
     </row>
-    <row r="749" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A749" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65631,7 +65631,7 @@
       </c>
       <c r="F749"/>
     </row>
-    <row r="750" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A750" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65649,7 +65649,7 @@
       </c>
       <c r="F750"/>
     </row>
-    <row r="751" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A751" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65667,7 +65667,7 @@
       </c>
       <c r="F751"/>
     </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A752" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65685,7 +65685,7 @@
       </c>
       <c r="F752"/>
     </row>
-    <row r="753" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A753" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65703,7 +65703,7 @@
       </c>
       <c r="F753"/>
     </row>
-    <row r="754" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A754" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65721,7 +65721,7 @@
       </c>
       <c r="F754"/>
     </row>
-    <row r="755" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A755" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65739,7 +65739,7 @@
       </c>
       <c r="F755"/>
     </row>
-    <row r="756" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A756" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65757,7 +65757,7 @@
       </c>
       <c r="F756"/>
     </row>
-    <row r="757" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A757" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65775,7 +65775,7 @@
       </c>
       <c r="F757"/>
     </row>
-    <row r="758" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A758" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65793,7 +65793,7 @@
       </c>
       <c r="F758"/>
     </row>
-    <row r="759" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A759" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65811,7 +65811,7 @@
       </c>
       <c r="F759"/>
     </row>
-    <row r="760" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A760" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65829,7 +65829,7 @@
       </c>
       <c r="F760"/>
     </row>
-    <row r="761" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A761" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65847,7 +65847,7 @@
       </c>
       <c r="F761"/>
     </row>
-    <row r="762" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A762" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65865,7 +65865,7 @@
       </c>
       <c r="F762"/>
     </row>
-    <row r="763" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A763" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65883,7 +65883,7 @@
       </c>
       <c r="F763"/>
     </row>
-    <row r="764" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A764" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65901,7 +65901,7 @@
       </c>
       <c r="F764"/>
     </row>
-    <row r="765" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A765" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65919,7 +65919,7 @@
       </c>
       <c r="F765"/>
     </row>
-    <row r="766" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A766" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65937,7 +65937,7 @@
       </c>
       <c r="F766"/>
     </row>
-    <row r="767" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A767" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65955,7 +65955,7 @@
       </c>
       <c r="F767"/>
     </row>
-    <row r="768" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A768" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65973,7 +65973,7 @@
       </c>
       <c r="F768"/>
     </row>
-    <row r="769" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A769" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66099,7 +66099,7 @@
       </c>
       <c r="F775"/>
     </row>
-    <row r="776" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A776" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66117,7 +66117,7 @@
       </c>
       <c r="F776"/>
     </row>
-    <row r="777" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A777" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66135,7 +66135,7 @@
       </c>
       <c r="F777"/>
     </row>
-    <row r="778" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A778" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66153,7 +66153,7 @@
       </c>
       <c r="F778"/>
     </row>
-    <row r="779" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A779" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66171,7 +66171,7 @@
       </c>
       <c r="F779"/>
     </row>
-    <row r="780" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A780" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66189,7 +66189,7 @@
       </c>
       <c r="F780"/>
     </row>
-    <row r="781" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A781" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66207,7 +66207,7 @@
       </c>
       <c r="F781"/>
     </row>
-    <row r="782" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A782" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66225,7 +66225,7 @@
       </c>
       <c r="F782"/>
     </row>
-    <row r="783" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A783" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66243,7 +66243,7 @@
       </c>
       <c r="F783"/>
     </row>
-    <row r="784" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A784" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66261,7 +66261,7 @@
       </c>
       <c r="F784"/>
     </row>
-    <row r="785" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A785" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66279,7 +66279,7 @@
       </c>
       <c r="F785"/>
     </row>
-    <row r="786" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A786" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66297,7 +66297,7 @@
       </c>
       <c r="F786"/>
     </row>
-    <row r="787" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A787" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66315,7 +66315,7 @@
       </c>
       <c r="F787"/>
     </row>
-    <row r="788" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A788" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66333,7 +66333,7 @@
       </c>
       <c r="F788"/>
     </row>
-    <row r="789" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A789" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66351,7 +66351,7 @@
       </c>
       <c r="F789"/>
     </row>
-    <row r="790" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A790" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66369,7 +66369,7 @@
       </c>
       <c r="F790"/>
     </row>
-    <row r="791" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A791" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66387,7 +66387,7 @@
       </c>
       <c r="F791"/>
     </row>
-    <row r="792" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A792" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66405,7 +66405,7 @@
       </c>
       <c r="F792"/>
     </row>
-    <row r="793" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A793" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66423,7 +66423,7 @@
       </c>
       <c r="F793"/>
     </row>
-    <row r="794" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A794" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66441,7 +66441,7 @@
       </c>
       <c r="F794"/>
     </row>
-    <row r="795" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A795" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66459,7 +66459,7 @@
       </c>
       <c r="F795"/>
     </row>
-    <row r="796" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A796" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66477,7 +66477,7 @@
       </c>
       <c r="F796"/>
     </row>
-    <row r="797" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A797" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66495,7 +66495,7 @@
       </c>
       <c r="F797"/>
     </row>
-    <row r="798" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A798" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66513,7 +66513,7 @@
       </c>
       <c r="F798"/>
     </row>
-    <row r="799" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A799" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66531,7 +66531,7 @@
       </c>
       <c r="F799"/>
     </row>
-    <row r="800" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A800" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66549,7 +66549,7 @@
       </c>
       <c r="F800"/>
     </row>
-    <row r="801" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A801" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66567,7 +66567,7 @@
       </c>
       <c r="F801"/>
     </row>
-    <row r="802" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A802" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66585,7 +66585,7 @@
       </c>
       <c r="F802"/>
     </row>
-    <row r="803" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A803" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66603,7 +66603,7 @@
       </c>
       <c r="F803"/>
     </row>
-    <row r="804" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A804" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66621,7 +66621,7 @@
       </c>
       <c r="F804"/>
     </row>
-    <row r="805" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A805" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66639,7 +66639,7 @@
       </c>
       <c r="F805"/>
     </row>
-    <row r="806" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A806" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66657,7 +66657,7 @@
       </c>
       <c r="F806"/>
     </row>
-    <row r="807" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A807" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66675,7 +66675,7 @@
       </c>
       <c r="F807"/>
     </row>
-    <row r="808" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A808" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66693,7 +66693,7 @@
       </c>
       <c r="F808"/>
     </row>
-    <row r="809" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A809" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66711,7 +66711,7 @@
       </c>
       <c r="F809"/>
     </row>
-    <row r="810" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A810" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66729,7 +66729,7 @@
       </c>
       <c r="F810"/>
     </row>
-    <row r="811" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A811" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66747,7 +66747,7 @@
       </c>
       <c r="F811"/>
     </row>
-    <row r="812" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A812" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66765,7 +66765,7 @@
       </c>
       <c r="F812"/>
     </row>
-    <row r="813" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A813" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66783,7 +66783,7 @@
       </c>
       <c r="F813"/>
     </row>
-    <row r="814" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A814" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66801,7 +66801,7 @@
       </c>
       <c r="F814"/>
     </row>
-    <row r="815" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A815" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66819,7 +66819,7 @@
       </c>
       <c r="F815"/>
     </row>
-    <row r="816" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A816" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66837,7 +66837,7 @@
       </c>
       <c r="F816"/>
     </row>
-    <row r="817" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A817" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66855,7 +66855,7 @@
       </c>
       <c r="F817"/>
     </row>
-    <row r="818" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A818" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66873,7 +66873,7 @@
       </c>
       <c r="F818"/>
     </row>
-    <row r="819" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A819" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66891,7 +66891,7 @@
       </c>
       <c r="F819"/>
     </row>
-    <row r="820" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A820" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66909,7 +66909,7 @@
       </c>
       <c r="F820"/>
     </row>
-    <row r="821" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A821" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66927,7 +66927,7 @@
       </c>
       <c r="F821"/>
     </row>
-    <row r="822" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A822" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66945,7 +66945,7 @@
       </c>
       <c r="F822"/>
     </row>
-    <row r="823" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A823" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66963,7 +66963,7 @@
       </c>
       <c r="F823"/>
     </row>
-    <row r="824" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A824" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66981,7 +66981,7 @@
       </c>
       <c r="F824"/>
     </row>
-    <row r="825" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A825" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66999,7 +66999,7 @@
       </c>
       <c r="F825"/>
     </row>
-    <row r="826" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A826" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67019,7 +67019,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="827" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A827" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67039,7 +67039,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A828" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67059,7 +67059,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="829" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A829" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67079,7 +67079,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="830" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A830" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67099,7 +67099,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="831" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A831" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67119,7 +67119,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="832" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A832" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67139,7 +67139,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="833" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A833" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67159,7 +67159,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="834" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A834" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67179,7 +67179,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="835" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A835" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67199,7 +67199,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="836" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A836" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67219,7 +67219,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="837" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A837" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67239,7 +67239,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="838" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A838" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67257,7 +67257,7 @@
       </c>
       <c r="F838"/>
     </row>
-    <row r="839" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A839" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67275,7 +67275,7 @@
       </c>
       <c r="F839"/>
     </row>
-    <row r="840" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A840" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67293,7 +67293,7 @@
       </c>
       <c r="F840"/>
     </row>
-    <row r="841" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A841" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67311,7 +67311,7 @@
       </c>
       <c r="F841"/>
     </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A842" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67329,7 +67329,7 @@
       </c>
       <c r="F842"/>
     </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A843" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67347,7 +67347,7 @@
       </c>
       <c r="F843"/>
     </row>
-    <row r="844" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A844" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67365,7 +67365,7 @@
       </c>
       <c r="F844"/>
     </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A845" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67383,7 +67383,7 @@
       </c>
       <c r="F845"/>
     </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A846" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67401,7 +67401,7 @@
       </c>
       <c r="F846"/>
     </row>
-    <row r="847" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A847" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67419,7 +67419,7 @@
       </c>
       <c r="F847"/>
     </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A848" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67437,7 +67437,7 @@
       </c>
       <c r="F848"/>
     </row>
-    <row r="849" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A849" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67455,7 +67455,7 @@
       </c>
       <c r="F849"/>
     </row>
-    <row r="850" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A850" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67473,7 +67473,7 @@
       </c>
       <c r="F850"/>
     </row>
-    <row r="851" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A851" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67491,7 +67491,7 @@
       </c>
       <c r="F851"/>
     </row>
-    <row r="852" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A852" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67509,7 +67509,7 @@
       </c>
       <c r="F852"/>
     </row>
-    <row r="853" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A853" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67527,7 +67527,7 @@
       </c>
       <c r="F853"/>
     </row>
-    <row r="854" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A854" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67545,7 +67545,7 @@
       </c>
       <c r="F854"/>
     </row>
-    <row r="855" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A855" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67563,7 +67563,7 @@
       </c>
       <c r="F855"/>
     </row>
-    <row r="856" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A856" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67581,7 +67581,7 @@
       </c>
       <c r="F856"/>
     </row>
-    <row r="857" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A857" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67599,7 +67599,7 @@
       </c>
       <c r="F857"/>
     </row>
-    <row r="858" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A858" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67617,7 +67617,7 @@
       </c>
       <c r="F858"/>
     </row>
-    <row r="859" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A859" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67635,7 +67635,7 @@
       </c>
       <c r="F859"/>
     </row>
-    <row r="860" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A860" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67761,7 +67761,7 @@
       </c>
       <c r="F866"/>
     </row>
-    <row r="867" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A867" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67779,7 +67779,7 @@
       </c>
       <c r="F867"/>
     </row>
-    <row r="868" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A868" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67797,7 +67797,7 @@
       </c>
       <c r="F868"/>
     </row>
-    <row r="869" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A869" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67815,7 +67815,7 @@
       </c>
       <c r="F869"/>
     </row>
-    <row r="870" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A870" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67833,7 +67833,7 @@
       </c>
       <c r="F870"/>
     </row>
-    <row r="871" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A871" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67851,7 +67851,7 @@
       </c>
       <c r="F871"/>
     </row>
-    <row r="872" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A872" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67869,7 +67869,7 @@
       </c>
       <c r="F872"/>
     </row>
-    <row r="873" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A873" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67887,7 +67887,7 @@
       </c>
       <c r="F873"/>
     </row>
-    <row r="874" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A874" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67905,7 +67905,7 @@
       </c>
       <c r="F874"/>
     </row>
-    <row r="875" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A875" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67923,7 +67923,7 @@
       </c>
       <c r="F875"/>
     </row>
-    <row r="876" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A876" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67941,7 +67941,7 @@
       </c>
       <c r="F876"/>
     </row>
-    <row r="877" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A877" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67959,7 +67959,7 @@
       </c>
       <c r="F877"/>
     </row>
-    <row r="878" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A878" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67977,7 +67977,7 @@
       </c>
       <c r="F878"/>
     </row>
-    <row r="879" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A879" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67995,7 +67995,7 @@
       </c>
       <c r="F879"/>
     </row>
-    <row r="880" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A880" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68013,7 +68013,7 @@
       </c>
       <c r="F880"/>
     </row>
-    <row r="881" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A881" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68031,7 +68031,7 @@
       </c>
       <c r="F881"/>
     </row>
-    <row r="882" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A882" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68049,7 +68049,7 @@
       </c>
       <c r="F882"/>
     </row>
-    <row r="883" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A883" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68067,7 +68067,7 @@
       </c>
       <c r="F883"/>
     </row>
-    <row r="884" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A884" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68085,7 +68085,7 @@
       </c>
       <c r="F884"/>
     </row>
-    <row r="885" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A885" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68103,7 +68103,7 @@
       </c>
       <c r="F885"/>
     </row>
-    <row r="886" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A886" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68121,7 +68121,7 @@
       </c>
       <c r="F886"/>
     </row>
-    <row r="887" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A887" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68139,7 +68139,7 @@
       </c>
       <c r="F887"/>
     </row>
-    <row r="888" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A888" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68157,7 +68157,7 @@
       </c>
       <c r="F888"/>
     </row>
-    <row r="889" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A889" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68175,7 +68175,7 @@
       </c>
       <c r="F889"/>
     </row>
-    <row r="890" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A890" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68193,7 +68193,7 @@
       </c>
       <c r="F890"/>
     </row>
-    <row r="891" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A891" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68211,7 +68211,7 @@
       </c>
       <c r="F891"/>
     </row>
-    <row r="892" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A892" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68229,7 +68229,7 @@
       </c>
       <c r="F892"/>
     </row>
-    <row r="893" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A893" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68247,17 +68247,25 @@
       </c>
       <c r="F893"/>
     </row>
-    <row r="894" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A894" s="4"/>
-      <c r="B894" s="4"/>
-      <c r="C894" s="4"/>
-      <c r="D894" s="4"/>
+    <row r="894" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A894" s="4" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B894" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="C894" s="4" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D894" s="4" t="s">
+        <v>389</v>
+      </c>
       <c r="E894" s="24" t="s">
         <v>1189</v>
       </c>
       <c r="F894"/>
     </row>
-    <row r="895" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A895" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68275,7 +68283,7 @@
       </c>
       <c r="F895"/>
     </row>
-    <row r="896" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A896" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68293,7 +68301,7 @@
       </c>
       <c r="F896"/>
     </row>
-    <row r="897" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A897" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68311,7 +68319,7 @@
       </c>
       <c r="F897"/>
     </row>
-    <row r="898" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A898" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68329,7 +68337,7 @@
       </c>
       <c r="F898"/>
     </row>
-    <row r="899" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A899" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68347,7 +68355,7 @@
       </c>
       <c r="F899"/>
     </row>
-    <row r="900" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A900" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68365,7 +68373,7 @@
       </c>
       <c r="F900"/>
     </row>
-    <row r="901" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A901" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68383,7 +68391,7 @@
       </c>
       <c r="F901"/>
     </row>
-    <row r="902" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A902" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68401,7 +68409,7 @@
       </c>
       <c r="F902"/>
     </row>
-    <row r="903" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A903" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68419,7 +68427,7 @@
       </c>
       <c r="F903"/>
     </row>
-    <row r="904" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A904" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68437,7 +68445,7 @@
       </c>
       <c r="F904"/>
     </row>
-    <row r="905" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A905" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68455,7 +68463,7 @@
       </c>
       <c r="F905"/>
     </row>
-    <row r="906" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A906" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68473,7 +68481,7 @@
       </c>
       <c r="F906"/>
     </row>
-    <row r="907" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A907" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68491,7 +68499,7 @@
       </c>
       <c r="F907"/>
     </row>
-    <row r="908" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A908" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68509,7 +68517,7 @@
       </c>
       <c r="F908"/>
     </row>
-    <row r="909" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A909" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68527,7 +68535,7 @@
       </c>
       <c r="F909"/>
     </row>
-    <row r="910" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A910" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68545,7 +68553,7 @@
       </c>
       <c r="F910"/>
     </row>
-    <row r="911" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A911" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68563,7 +68571,7 @@
       </c>
       <c r="F911"/>
     </row>
-    <row r="912" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A912" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68583,7 +68591,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="913" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A913" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68603,7 +68611,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="914" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A914" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68623,7 +68631,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="915" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A915" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68643,7 +68651,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="916" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A916" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68663,7 +68671,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="917" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A917" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68683,7 +68691,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="918" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A918" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68703,7 +68711,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="919" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A919" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68723,7 +68731,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="920" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A920" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68743,7 +68751,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="921" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A921" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68763,7 +68771,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="922" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A922" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68781,7 +68789,7 @@
       </c>
       <c r="F922"/>
     </row>
-    <row r="923" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A923" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68799,7 +68807,7 @@
       </c>
       <c r="F923"/>
     </row>
-    <row r="924" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A924" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68817,7 +68825,7 @@
       </c>
       <c r="F924"/>
     </row>
-    <row r="925" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A925" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68835,7 +68843,7 @@
       </c>
       <c r="F925"/>
     </row>
-    <row r="926" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A926" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68853,7 +68861,7 @@
       </c>
       <c r="F926"/>
     </row>
-    <row r="927" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A927" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68871,7 +68879,7 @@
       </c>
       <c r="F927"/>
     </row>
-    <row r="928" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A928" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68889,7 +68897,7 @@
       </c>
       <c r="F928"/>
     </row>
-    <row r="929" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A929" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68907,7 +68915,7 @@
       </c>
       <c r="F929"/>
     </row>
-    <row r="930" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A930" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68925,7 +68933,7 @@
       </c>
       <c r="F930"/>
     </row>
-    <row r="931" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A931" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68943,7 +68951,7 @@
       </c>
       <c r="F931"/>
     </row>
-    <row r="932" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A932" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68961,7 +68969,7 @@
       </c>
       <c r="F932"/>
     </row>
-    <row r="933" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A933" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68979,7 +68987,7 @@
       </c>
       <c r="F933"/>
     </row>
-    <row r="934" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A934" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68997,7 +69005,7 @@
       </c>
       <c r="F934"/>
     </row>
-    <row r="935" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A935" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69015,7 +69023,7 @@
       </c>
       <c r="F935"/>
     </row>
-    <row r="936" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A936" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69033,7 +69041,7 @@
       </c>
       <c r="F936"/>
     </row>
-    <row r="937" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A937" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69051,7 +69059,7 @@
       </c>
       <c r="F937"/>
     </row>
-    <row r="938" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A938" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69069,7 +69077,7 @@
       </c>
       <c r="F938"/>
     </row>
-    <row r="939" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A939" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69087,7 +69095,7 @@
       </c>
       <c r="F939"/>
     </row>
-    <row r="940" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A940" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69105,7 +69113,7 @@
       </c>
       <c r="F940"/>
     </row>
-    <row r="941" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A941" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69123,7 +69131,7 @@
       </c>
       <c r="F941"/>
     </row>
-    <row r="942" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A942" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69141,7 +69149,7 @@
       </c>
       <c r="F942"/>
     </row>
-    <row r="943" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A943" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69159,7 +69167,7 @@
       </c>
       <c r="F943"/>
     </row>
-    <row r="944" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A944" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69285,7 +69293,7 @@
       </c>
       <c r="F950"/>
     </row>
-    <row r="951" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A951" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69303,7 +69311,7 @@
       </c>
       <c r="F951"/>
     </row>
-    <row r="952" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A952" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69321,7 +69329,7 @@
       </c>
       <c r="F952"/>
     </row>
-    <row r="953" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A953" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69339,7 +69347,7 @@
       </c>
       <c r="F953"/>
     </row>
-    <row r="954" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A954" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69357,7 +69365,7 @@
       </c>
       <c r="F954"/>
     </row>
-    <row r="955" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A955" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69375,7 +69383,7 @@
       </c>
       <c r="F955"/>
     </row>
-    <row r="956" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A956" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69393,7 +69401,7 @@
       </c>
       <c r="F956"/>
     </row>
-    <row r="957" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A957" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69411,7 +69419,7 @@
       </c>
       <c r="F957"/>
     </row>
-    <row r="958" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A958" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69429,7 +69437,7 @@
       </c>
       <c r="F958"/>
     </row>
-    <row r="959" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A959" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69447,7 +69455,7 @@
       </c>
       <c r="F959"/>
     </row>
-    <row r="960" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A960" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69465,7 +69473,7 @@
       </c>
       <c r="F960"/>
     </row>
-    <row r="961" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A961" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69483,7 +69491,7 @@
       </c>
       <c r="F961"/>
     </row>
-    <row r="962" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A962" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69501,7 +69509,7 @@
       </c>
       <c r="F962"/>
     </row>
-    <row r="963" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A963" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69519,7 +69527,7 @@
       </c>
       <c r="F963"/>
     </row>
-    <row r="964" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A964" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69537,7 +69545,7 @@
       </c>
       <c r="F964"/>
     </row>
-    <row r="965" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A965" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69555,7 +69563,7 @@
       </c>
       <c r="F965"/>
     </row>
-    <row r="966" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A966" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69573,7 +69581,7 @@
       </c>
       <c r="F966"/>
     </row>
-    <row r="967" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A967" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69591,7 +69599,7 @@
       </c>
       <c r="F967"/>
     </row>
-    <row r="968" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A968" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69609,7 +69617,7 @@
       </c>
       <c r="F968"/>
     </row>
-    <row r="969" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A969" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69627,7 +69635,7 @@
       </c>
       <c r="F969"/>
     </row>
-    <row r="970" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A970" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69645,7 +69653,7 @@
       </c>
       <c r="F970"/>
     </row>
-    <row r="971" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A971" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69663,7 +69671,7 @@
       </c>
       <c r="F971"/>
     </row>
-    <row r="972" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A972" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69681,7 +69689,7 @@
       </c>
       <c r="F972"/>
     </row>
-    <row r="973" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A973" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69699,7 +69707,7 @@
       </c>
       <c r="F973"/>
     </row>
-    <row r="974" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A974" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69717,7 +69725,7 @@
       </c>
       <c r="F974"/>
     </row>
-    <row r="975" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A975" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69735,7 +69743,7 @@
       </c>
       <c r="F975"/>
     </row>
-    <row r="976" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A976" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69753,7 +69761,7 @@
       </c>
       <c r="F976"/>
     </row>
-    <row r="977" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A977" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69771,7 +69779,7 @@
       </c>
       <c r="F977"/>
     </row>
-    <row r="978" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A978" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69789,7 +69797,7 @@
       </c>
       <c r="F978"/>
     </row>
-    <row r="979" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A979" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69807,7 +69815,7 @@
       </c>
       <c r="F979"/>
     </row>
-    <row r="980" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A980" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69825,7 +69833,7 @@
       </c>
       <c r="F980"/>
     </row>
-    <row r="981" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A981" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69843,7 +69851,7 @@
       </c>
       <c r="F981"/>
     </row>
-    <row r="982" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A982" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69861,7 +69869,7 @@
       </c>
       <c r="F982"/>
     </row>
-    <row r="983" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A983" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69879,7 +69887,7 @@
       </c>
       <c r="F983"/>
     </row>
-    <row r="984" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A984" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69897,7 +69905,7 @@
       </c>
       <c r="F984"/>
     </row>
-    <row r="985" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A985" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69915,7 +69923,7 @@
       </c>
       <c r="F985"/>
     </row>
-    <row r="986" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A986" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69933,7 +69941,7 @@
       </c>
       <c r="F986"/>
     </row>
-    <row r="987" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A987" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69951,7 +69959,7 @@
       </c>
       <c r="F987"/>
     </row>
-    <row r="988" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A988" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69969,7 +69977,7 @@
       </c>
       <c r="F988"/>
     </row>
-    <row r="989" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A989" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69987,7 +69995,7 @@
       </c>
       <c r="F989"/>
     </row>
-    <row r="990" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A990" s="4" t="s">
         <v>1113</v>
       </c>
@@ -70005,7 +70013,7 @@
       </c>
       <c r="F990"/>
     </row>
-    <row r="991" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A991" s="4" t="s">
         <v>1113</v>
       </c>
@@ -70023,7 +70031,7 @@
       </c>
       <c r="F991"/>
     </row>
-    <row r="992" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A992" s="4" t="s">
         <v>1113</v>
       </c>
@@ -70041,7 +70049,7 @@
       </c>
       <c r="F992"/>
     </row>
-    <row r="993" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A993" s="4" t="s">
         <v>1113</v>
       </c>
@@ -70059,7 +70067,7 @@
       </c>
       <c r="F993"/>
     </row>
-    <row r="994" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A994" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70079,7 +70087,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="995" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A995" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70099,7 +70107,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="996" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A996" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70119,7 +70127,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="997" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A997" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70139,7 +70147,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="998" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A998" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70159,7 +70167,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="999" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A999" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70179,7 +70187,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1000" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1000" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70199,7 +70207,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1001" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1001" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1001" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70219,7 +70227,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1002" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="1002" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1002" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70239,7 +70247,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1003" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1003" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1003" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70257,7 +70265,7 @@
       </c>
       <c r="F1003"/>
     </row>
-    <row r="1004" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1004" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1004" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70275,7 +70283,7 @@
       </c>
       <c r="F1004"/>
     </row>
-    <row r="1005" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1005" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1005" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70293,7 +70301,7 @@
       </c>
       <c r="F1005"/>
     </row>
-    <row r="1006" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1006" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1006" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70311,7 +70319,7 @@
       </c>
       <c r="F1006"/>
     </row>
-    <row r="1007" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1007" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1007" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70329,7 +70337,7 @@
       </c>
       <c r="F1007"/>
     </row>
-    <row r="1008" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1008" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1008" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70347,7 +70355,7 @@
       </c>
       <c r="F1008"/>
     </row>
-    <row r="1009" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1009" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1009" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70365,7 +70373,7 @@
       </c>
       <c r="F1009"/>
     </row>
-    <row r="1010" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1010" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1010" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70383,7 +70391,7 @@
       </c>
       <c r="F1010"/>
     </row>
-    <row r="1011" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1011" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1011" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70401,7 +70409,7 @@
       </c>
       <c r="F1011"/>
     </row>
-    <row r="1012" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1012" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1012" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70419,7 +70427,7 @@
       </c>
       <c r="F1012"/>
     </row>
-    <row r="1013" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1013" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1013" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70437,7 +70445,7 @@
       </c>
       <c r="F1013"/>
     </row>
-    <row r="1014" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1014" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1014" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70455,7 +70463,7 @@
       </c>
       <c r="F1014"/>
     </row>
-    <row r="1015" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1015" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1015" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70473,7 +70481,7 @@
       </c>
       <c r="F1015"/>
     </row>
-    <row r="1016" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1016" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1016" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70491,7 +70499,7 @@
       </c>
       <c r="F1016"/>
     </row>
-    <row r="1017" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1017" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1017" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70509,7 +70517,7 @@
       </c>
       <c r="F1017"/>
     </row>
-    <row r="1018" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1018" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1018" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70527,7 +70535,7 @@
       </c>
       <c r="F1018"/>
     </row>
-    <row r="1019" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1019" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1019" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70545,7 +70553,7 @@
       </c>
       <c r="F1019"/>
     </row>
-    <row r="1020" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1020" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1020" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70563,7 +70571,7 @@
       </c>
       <c r="F1020"/>
     </row>
-    <row r="1021" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1021" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1021" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70581,7 +70589,7 @@
       </c>
       <c r="F1021"/>
     </row>
-    <row r="1022" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1022" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1022" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70599,7 +70607,7 @@
       </c>
       <c r="F1022"/>
     </row>
-    <row r="1023" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1023" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1023" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70617,7 +70625,7 @@
       </c>
       <c r="F1023"/>
     </row>
-    <row r="1024" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1024" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1024" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70635,7 +70643,7 @@
       </c>
       <c r="F1024"/>
     </row>
-    <row r="1025" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1025" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1025" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70761,7 +70769,7 @@
       </c>
       <c r="F1031"/>
     </row>
-    <row r="1032" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1032" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1032" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70779,7 +70787,7 @@
       </c>
       <c r="F1032"/>
     </row>
-    <row r="1033" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1033" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1033" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70797,7 +70805,7 @@
       </c>
       <c r="F1033"/>
     </row>
-    <row r="1034" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1034" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1034" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70815,7 +70823,7 @@
       </c>
       <c r="F1034"/>
     </row>
-    <row r="1035" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1035" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1035" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70833,7 +70841,7 @@
       </c>
       <c r="F1035"/>
     </row>
-    <row r="1036" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1036" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1036" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70851,7 +70859,7 @@
       </c>
       <c r="F1036"/>
     </row>
-    <row r="1037" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1037" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1037" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70869,7 +70877,7 @@
       </c>
       <c r="F1037"/>
     </row>
-    <row r="1038" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1038" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1038" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70887,7 +70895,7 @@
       </c>
       <c r="F1038"/>
     </row>
-    <row r="1039" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1039" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1039" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70905,7 +70913,7 @@
       </c>
       <c r="F1039"/>
     </row>
-    <row r="1040" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1040" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1040" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70923,7 +70931,7 @@
       </c>
       <c r="F1040"/>
     </row>
-    <row r="1041" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1041" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1041" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70941,7 +70949,7 @@
       </c>
       <c r="F1041"/>
     </row>
-    <row r="1042" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1042" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1042" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70959,7 +70967,7 @@
       </c>
       <c r="F1042"/>
     </row>
-    <row r="1043" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1043" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1043" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70977,7 +70985,7 @@
       </c>
       <c r="F1043"/>
     </row>
-    <row r="1044" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1044" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1044" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70995,7 +71003,7 @@
       </c>
       <c r="F1044"/>
     </row>
-    <row r="1045" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1045" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1045" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71013,7 +71021,7 @@
       </c>
       <c r="F1045"/>
     </row>
-    <row r="1046" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1046" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1046" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71031,7 +71039,7 @@
       </c>
       <c r="F1046"/>
     </row>
-    <row r="1047" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1047" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1047" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71049,7 +71057,7 @@
       </c>
       <c r="F1047"/>
     </row>
-    <row r="1048" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1048" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1048" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71067,7 +71075,7 @@
       </c>
       <c r="F1048"/>
     </row>
-    <row r="1049" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1049" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1049" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71085,7 +71093,7 @@
       </c>
       <c r="F1049"/>
     </row>
-    <row r="1050" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1050" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1050" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71103,7 +71111,7 @@
       </c>
       <c r="F1050"/>
     </row>
-    <row r="1051" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1051" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1051" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71121,7 +71129,7 @@
       </c>
       <c r="F1051"/>
     </row>
-    <row r="1052" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1052" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1052" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71139,7 +71147,7 @@
       </c>
       <c r="F1052"/>
     </row>
-    <row r="1053" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1053" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1053" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71157,7 +71165,7 @@
       </c>
       <c r="F1053"/>
     </row>
-    <row r="1054" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1054" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1054" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71175,7 +71183,7 @@
       </c>
       <c r="F1054"/>
     </row>
-    <row r="1055" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1055" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1055" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71193,7 +71201,7 @@
       </c>
       <c r="F1055"/>
     </row>
-    <row r="1056" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1056" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1056" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71211,7 +71219,7 @@
       </c>
       <c r="F1056"/>
     </row>
-    <row r="1057" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1057" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1057" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71229,7 +71237,7 @@
       </c>
       <c r="F1057"/>
     </row>
-    <row r="1058" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1058" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1058" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71247,7 +71255,7 @@
       </c>
       <c r="F1058"/>
     </row>
-    <row r="1059" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1059" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1059" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71265,7 +71273,7 @@
       </c>
       <c r="F1059"/>
     </row>
-    <row r="1060" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1060" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1060" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71283,7 +71291,7 @@
       </c>
       <c r="F1060"/>
     </row>
-    <row r="1061" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="1061" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1061" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71301,7 +71309,7 @@
       </c>
       <c r="F1061"/>
     </row>
-    <row r="1062" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1062" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1062" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71319,7 +71327,7 @@
       </c>
       <c r="F1062"/>
     </row>
-    <row r="1063" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1063" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1063" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71337,7 +71345,7 @@
       </c>
       <c r="F1063"/>
     </row>
-    <row r="1064" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1064" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1064" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71355,7 +71363,7 @@
       </c>
       <c r="F1064"/>
     </row>
-    <row r="1065" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1065" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1065" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71373,7 +71381,7 @@
       </c>
       <c r="F1065"/>
     </row>
-    <row r="1066" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1066" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1066" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71391,7 +71399,7 @@
       </c>
       <c r="F1066"/>
     </row>
-    <row r="1067" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1067" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1067" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71409,7 +71417,7 @@
       </c>
       <c r="F1067"/>
     </row>
-    <row r="1068" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1068" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1068" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71427,7 +71435,7 @@
       </c>
       <c r="F1068"/>
     </row>
-    <row r="1069" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1069" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1069" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71445,7 +71453,7 @@
       </c>
       <c r="F1069"/>
     </row>
-    <row r="1070" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1070" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1070" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71463,7 +71471,7 @@
       </c>
       <c r="F1070"/>
     </row>
-    <row r="1071" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1071" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1071" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71481,7 +71489,7 @@
       </c>
       <c r="F1071"/>
     </row>
-    <row r="1072" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1072" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1072" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71499,7 +71507,7 @@
       </c>
       <c r="F1072"/>
     </row>
-    <row r="1073" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1073" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1073" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71517,7 +71525,7 @@
       </c>
       <c r="F1073"/>
     </row>
-    <row r="1074" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1074" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1074" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71535,7 +71543,7 @@
       </c>
       <c r="F1074"/>
     </row>
-    <row r="1075" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1075" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1075" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71555,7 +71563,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1076" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1076" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1076" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71575,7 +71583,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="1077" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1077" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1077" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71595,7 +71603,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1078" spans="1:6" ht="58" x14ac:dyDescent="0.35">
+    <row r="1078" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1078" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71615,7 +71623,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1079" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1079" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1079" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71635,7 +71643,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1080" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1080" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1080" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71655,7 +71663,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1081" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1081" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1081" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71675,7 +71683,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1082" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1082" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1082" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71695,7 +71703,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1083" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="1083" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1083" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71715,7 +71723,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1084" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1084" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1084" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71733,7 +71741,7 @@
       </c>
       <c r="F1084"/>
     </row>
-    <row r="1085" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1085" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1085" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71751,7 +71759,7 @@
       </c>
       <c r="F1085"/>
     </row>
-    <row r="1086" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1086" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1086" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71769,7 +71777,7 @@
       </c>
       <c r="F1086"/>
     </row>
-    <row r="1087" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1087" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1087" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71787,7 +71795,7 @@
       </c>
       <c r="F1087"/>
     </row>
-    <row r="1088" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1088" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1088" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71805,7 +71813,7 @@
       </c>
       <c r="F1088"/>
     </row>
-    <row r="1089" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1089" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1089" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71823,7 +71831,7 @@
       </c>
       <c r="F1089"/>
     </row>
-    <row r="1090" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1090" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1090" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71841,7 +71849,7 @@
       </c>
       <c r="F1090"/>
     </row>
-    <row r="1091" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1091" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1091" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71859,7 +71867,7 @@
       </c>
       <c r="F1091"/>
     </row>
-    <row r="1092" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1092" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1092" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71877,7 +71885,7 @@
       </c>
       <c r="F1092"/>
     </row>
-    <row r="1093" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1093" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1093" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71895,7 +71903,7 @@
       </c>
       <c r="F1093"/>
     </row>
-    <row r="1094" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1094" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1094" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71913,7 +71921,7 @@
       </c>
       <c r="F1094"/>
     </row>
-    <row r="1095" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1095" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1095" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71931,7 +71939,7 @@
       </c>
       <c r="F1095"/>
     </row>
-    <row r="1096" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1096" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1096" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71949,7 +71957,7 @@
       </c>
       <c r="F1096"/>
     </row>
-    <row r="1097" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1097" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1097" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71967,7 +71975,7 @@
       </c>
       <c r="F1097"/>
     </row>
-    <row r="1098" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1098" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1098" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71985,7 +71993,7 @@
       </c>
       <c r="F1098"/>
     </row>
-    <row r="1099" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1099" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1099" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72003,7 +72011,7 @@
       </c>
       <c r="F1099"/>
     </row>
-    <row r="1100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1100" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72021,7 +72029,7 @@
       </c>
       <c r="F1100"/>
     </row>
-    <row r="1101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1101" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72039,7 +72047,7 @@
       </c>
       <c r="F1101"/>
     </row>
-    <row r="1102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1102" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72057,7 +72065,7 @@
       </c>
       <c r="F1102"/>
     </row>
-    <row r="1103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1103" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1103" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72075,7 +72083,7 @@
       </c>
       <c r="F1103"/>
     </row>
-    <row r="1104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1104" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1104" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72093,7 +72101,7 @@
       </c>
       <c r="F1104"/>
     </row>
-    <row r="1105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1105" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1105" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72111,7 +72119,7 @@
       </c>
       <c r="F1105"/>
     </row>
-    <row r="1106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1106" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1106" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72237,7 +72245,7 @@
       </c>
       <c r="F1112"/>
     </row>
-    <row r="1113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1113" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1113" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72255,7 +72263,7 @@
       </c>
       <c r="F1113"/>
     </row>
-    <row r="1114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1114" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1114" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72273,7 +72281,7 @@
       </c>
       <c r="F1114"/>
     </row>
-    <row r="1115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1115" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1115" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72291,7 +72299,7 @@
       </c>
       <c r="F1115"/>
     </row>
-    <row r="1116" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1116" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1116" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72309,7 +72317,7 @@
       </c>
       <c r="F1116"/>
     </row>
-    <row r="1117" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1117" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1117" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72327,7 +72335,7 @@
       </c>
       <c r="F1117"/>
     </row>
-    <row r="1118" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1118" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1118" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72345,7 +72353,7 @@
       </c>
       <c r="F1118"/>
     </row>
-    <row r="1119" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1119" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1119" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72363,7 +72371,7 @@
       </c>
       <c r="F1119"/>
     </row>
-    <row r="1120" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1120" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1120" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72381,7 +72389,7 @@
       </c>
       <c r="F1120"/>
     </row>
-    <row r="1121" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1121" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1121" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72399,7 +72407,7 @@
       </c>
       <c r="F1121"/>
     </row>
-    <row r="1122" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1122" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1122" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72417,7 +72425,7 @@
       </c>
       <c r="F1122"/>
     </row>
-    <row r="1123" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1123" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1123" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72435,7 +72443,7 @@
       </c>
       <c r="F1123"/>
     </row>
-    <row r="1124" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1124" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1124" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72453,7 +72461,7 @@
       </c>
       <c r="F1124"/>
     </row>
-    <row r="1125" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1125" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1125" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72471,7 +72479,7 @@
       </c>
       <c r="F1125"/>
     </row>
-    <row r="1126" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1126" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1126" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72489,7 +72497,7 @@
       </c>
       <c r="F1126"/>
     </row>
-    <row r="1127" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1127" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1127" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72507,7 +72515,7 @@
       </c>
       <c r="F1127"/>
     </row>
-    <row r="1128" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1128" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1128" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72525,7 +72533,7 @@
       </c>
       <c r="F1128"/>
     </row>
-    <row r="1129" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1129" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1129" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72543,7 +72551,7 @@
       </c>
       <c r="F1129"/>
     </row>
-    <row r="1130" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1130" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1130" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72561,7 +72569,7 @@
       </c>
       <c r="F1130"/>
     </row>
-    <row r="1131" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1131" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1131" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72579,7 +72587,7 @@
       </c>
       <c r="F1131"/>
     </row>
-    <row r="1132" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1132" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1132" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72597,7 +72605,7 @@
       </c>
       <c r="F1132"/>
     </row>
-    <row r="1133" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1133" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1133" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72615,7 +72623,7 @@
       </c>
       <c r="F1133"/>
     </row>
-    <row r="1134" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1134" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1134" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72633,7 +72641,7 @@
       </c>
       <c r="F1134"/>
     </row>
-    <row r="1135" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1135" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1135" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72651,7 +72659,7 @@
       </c>
       <c r="F1135"/>
     </row>
-    <row r="1136" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1136" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1136" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72669,7 +72677,7 @@
       </c>
       <c r="F1136"/>
     </row>
-    <row r="1137" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1137" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1137" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72687,7 +72695,7 @@
       </c>
       <c r="F1137"/>
     </row>
-    <row r="1138" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1138" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1138" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72705,7 +72713,7 @@
       </c>
       <c r="F1138"/>
     </row>
-    <row r="1139" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1139" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1139" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72723,7 +72731,7 @@
       </c>
       <c r="F1139"/>
     </row>
-    <row r="1140" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1140" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1140" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72741,7 +72749,7 @@
       </c>
       <c r="F1140"/>
     </row>
-    <row r="1141" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1141" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1141" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72759,7 +72767,7 @@
       </c>
       <c r="F1141"/>
     </row>
-    <row r="1142" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="1142" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1142" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72777,7 +72785,7 @@
       </c>
       <c r="F1142"/>
     </row>
-    <row r="1143" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1143" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1143" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72795,7 +72803,7 @@
       </c>
       <c r="F1143"/>
     </row>
-    <row r="1144" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1144" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1144" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72813,7 +72821,7 @@
       </c>
       <c r="F1144"/>
     </row>
-    <row r="1145" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1145" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1145" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72831,7 +72839,7 @@
       </c>
       <c r="F1145"/>
     </row>
-    <row r="1146" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1146" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1146" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72849,7 +72857,7 @@
       </c>
       <c r="F1146"/>
     </row>
-    <row r="1147" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1147" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1147" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72867,7 +72875,7 @@
       </c>
       <c r="F1147"/>
     </row>
-    <row r="1148" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1148" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1148" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72885,7 +72893,7 @@
       </c>
       <c r="F1148"/>
     </row>
-    <row r="1149" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1149" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1149" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72903,7 +72911,7 @@
       </c>
       <c r="F1149"/>
     </row>
-    <row r="1150" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1150" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1150" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72921,7 +72929,7 @@
       </c>
       <c r="F1150"/>
     </row>
-    <row r="1151" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1151" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1151" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72939,7 +72947,7 @@
       </c>
       <c r="F1151"/>
     </row>
-    <row r="1152" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1152" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1152" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72957,7 +72965,7 @@
       </c>
       <c r="F1152"/>
     </row>
-    <row r="1153" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="1153" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1153" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72975,7 +72983,7 @@
       </c>
       <c r="F1153"/>
     </row>
-    <row r="1154" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1154" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1154" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72993,7 +73001,7 @@
       </c>
       <c r="F1154"/>
     </row>
-    <row r="1155" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1155" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1155" s="4" t="s">
         <v>1115</v>
       </c>
@@ -73012,7 +73020,13 @@
       <c r="F1155"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1155" xr:uid="{7E885E9E-B9D0-4AB2-985A-25954D52BD4C}"/>
+  <autoFilter ref="A1:I1155" xr:uid="{7E885E9E-B9D0-4AB2-985A-25954D52BD4C}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="12.6 Duplicate Processing"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/VISA_CHECK.xlsx
+++ b/VISA_CHECK.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianaRodriguezBelt\Downloads\DEFENSE_VIEWER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianaRodriguezBelt\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A2EC8C-DE9A-41E4-A057-2354EA4213B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A79104-3902-4D9D-9520-93F4E73E392A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="941" firstSheet="2" activeTab="6" xr2:uid="{65CF5D28-24F6-4E6D-B37B-A691AC3C8BFA}"/>
   </bookViews>
@@ -51900,7 +51900,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E885E9E-B9D0-4AB2-985A-25954D52BD4C}">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:I1155"/>
@@ -51941,7 +51941,7 @@
       </c>
       <c r="G1" s="24"/>
     </row>
-    <row r="2" spans="1:7" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>1075</v>
       </c>
@@ -51961,7 +51961,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>1075</v>
       </c>
@@ -51981,7 +51981,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52001,7 +52001,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52021,7 +52021,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52041,7 +52041,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52061,7 +52061,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52081,7 +52081,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52101,7 +52101,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52121,7 +52121,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52141,7 +52141,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52161,7 +52161,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52181,7 +52181,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52199,7 +52199,7 @@
       </c>
       <c r="F14"/>
     </row>
-    <row r="15" spans="1:7" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52217,7 +52217,7 @@
       </c>
       <c r="F15"/>
     </row>
-    <row r="16" spans="1:7" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52235,7 +52235,7 @@
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52253,7 +52253,7 @@
       </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52271,7 +52271,7 @@
       </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52290,7 +52290,7 @@
       <c r="F19"/>
       <c r="I19" s="24"/>
     </row>
-    <row r="20" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A20" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52308,7 +52308,7 @@
       </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52326,7 +52326,7 @@
       </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A22" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52344,7 +52344,7 @@
       </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52362,7 +52362,7 @@
       </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52380,7 +52380,7 @@
       </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A25" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52398,7 +52398,7 @@
       </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="1:9" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52416,7 +52416,7 @@
       </c>
       <c r="F26"/>
     </row>
-    <row r="27" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A27" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52434,7 +52434,7 @@
       </c>
       <c r="F27"/>
     </row>
-    <row r="28" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A28" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52452,7 +52452,7 @@
       </c>
       <c r="F28"/>
     </row>
-    <row r="29" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A29" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52470,7 +52470,7 @@
       </c>
       <c r="F29"/>
     </row>
-    <row r="30" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A30" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52488,7 +52488,7 @@
       </c>
       <c r="F30"/>
     </row>
-    <row r="31" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52506,7 +52506,7 @@
       </c>
       <c r="F31"/>
     </row>
-    <row r="32" spans="1:9" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52524,7 +52524,7 @@
       </c>
       <c r="F32"/>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52542,7 +52542,7 @@
       </c>
       <c r="F33"/>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52560,7 +52560,7 @@
       </c>
       <c r="F34"/>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52578,7 +52578,7 @@
       </c>
       <c r="F35"/>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52704,7 +52704,7 @@
       </c>
       <c r="F42"/>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52722,7 +52722,7 @@
       </c>
       <c r="F43"/>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52740,7 +52740,7 @@
       </c>
       <c r="F44"/>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52758,7 +52758,7 @@
       </c>
       <c r="F45"/>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52776,7 +52776,7 @@
       </c>
       <c r="F46"/>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52794,7 +52794,7 @@
       </c>
       <c r="F47"/>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52812,7 +52812,7 @@
       </c>
       <c r="F48"/>
     </row>
-    <row r="49" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52830,7 +52830,7 @@
       </c>
       <c r="F49"/>
     </row>
-    <row r="50" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A50" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52848,7 +52848,7 @@
       </c>
       <c r="F50"/>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52866,7 +52866,7 @@
       </c>
       <c r="F51"/>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52884,7 +52884,7 @@
       </c>
       <c r="F52"/>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52902,7 +52902,7 @@
       </c>
       <c r="F53"/>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52920,7 +52920,7 @@
       </c>
       <c r="F54"/>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52938,7 +52938,7 @@
       </c>
       <c r="F55"/>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52956,7 +52956,7 @@
       </c>
       <c r="F56"/>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52974,7 +52974,7 @@
       </c>
       <c r="F57"/>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="4" t="s">
         <v>1075</v>
       </c>
@@ -52992,7 +52992,7 @@
       </c>
       <c r="F58"/>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53010,7 +53010,7 @@
       </c>
       <c r="F59"/>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53028,7 +53028,7 @@
       </c>
       <c r="F60"/>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53046,7 +53046,7 @@
       </c>
       <c r="F61"/>
     </row>
-    <row r="62" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53064,7 +53064,7 @@
       </c>
       <c r="F62"/>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53082,7 +53082,7 @@
       </c>
       <c r="F63"/>
     </row>
-    <row r="64" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53100,7 +53100,7 @@
       </c>
       <c r="F64"/>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53118,7 +53118,7 @@
       </c>
       <c r="F65"/>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53136,7 +53136,7 @@
       </c>
       <c r="F66"/>
     </row>
-    <row r="67" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A67" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53154,7 +53154,7 @@
       </c>
       <c r="F67"/>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53172,7 +53172,7 @@
       </c>
       <c r="F68"/>
     </row>
-    <row r="69" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A69" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53190,7 +53190,7 @@
       </c>
       <c r="F69"/>
     </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53208,7 +53208,7 @@
       </c>
       <c r="F70"/>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53226,7 +53226,7 @@
       </c>
       <c r="F71"/>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53244,7 +53244,7 @@
       </c>
       <c r="F72"/>
     </row>
-    <row r="73" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A73" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53262,7 +53262,7 @@
       </c>
       <c r="F73"/>
     </row>
-    <row r="74" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53280,7 +53280,7 @@
       </c>
       <c r="F74"/>
     </row>
-    <row r="75" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53298,7 +53298,7 @@
       </c>
       <c r="F75"/>
     </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53316,7 +53316,7 @@
       </c>
       <c r="F76"/>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53334,7 +53334,7 @@
       </c>
       <c r="F77"/>
     </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53352,7 +53352,7 @@
       </c>
       <c r="F78"/>
     </row>
-    <row r="79" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A79" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53370,7 +53370,7 @@
       </c>
       <c r="F79"/>
     </row>
-    <row r="80" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A80" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53388,7 +53388,7 @@
       </c>
       <c r="F80"/>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53406,7 +53406,7 @@
       </c>
       <c r="F81"/>
     </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53424,7 +53424,7 @@
       </c>
       <c r="F82"/>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53442,7 +53442,7 @@
       </c>
       <c r="F83"/>
     </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53460,7 +53460,7 @@
       </c>
       <c r="F84"/>
     </row>
-    <row r="85" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53478,7 +53478,7 @@
       </c>
       <c r="F85"/>
     </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53496,7 +53496,7 @@
       </c>
       <c r="F86"/>
     </row>
-    <row r="87" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53514,7 +53514,7 @@
       </c>
       <c r="F87"/>
     </row>
-    <row r="88" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53532,7 +53532,7 @@
       </c>
       <c r="F88"/>
     </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53550,7 +53550,7 @@
       </c>
       <c r="F89"/>
     </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53568,7 +53568,7 @@
       </c>
       <c r="F90"/>
     </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53586,7 +53586,7 @@
       </c>
       <c r="F91"/>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="4" t="s">
         <v>1075</v>
       </c>
@@ -53604,7 +53604,7 @@
       </c>
       <c r="F92"/>
     </row>
-    <row r="93" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A93" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53624,7 +53624,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53644,7 +53644,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53664,7 +53664,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53684,7 +53684,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A97" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53704,7 +53704,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53724,7 +53724,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53744,7 +53744,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53764,7 +53764,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53784,7 +53784,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53804,7 +53804,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="103" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A103" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53824,7 +53824,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="104" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A104" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53844,7 +53844,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="105" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A105" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53862,7 +53862,7 @@
       </c>
       <c r="F105"/>
     </row>
-    <row r="106" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A106" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53880,7 +53880,7 @@
       </c>
       <c r="F106"/>
     </row>
-    <row r="107" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53898,7 +53898,7 @@
       </c>
       <c r="F107"/>
     </row>
-    <row r="108" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A108" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53916,7 +53916,7 @@
       </c>
       <c r="F108"/>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53934,7 +53934,7 @@
       </c>
       <c r="F109"/>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53952,7 +53952,7 @@
       </c>
       <c r="F110"/>
     </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53970,7 +53970,7 @@
       </c>
       <c r="F111"/>
     </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="4" t="s">
         <v>1111</v>
       </c>
@@ -53988,7 +53988,7 @@
       </c>
       <c r="F112"/>
     </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54006,7 +54006,7 @@
       </c>
       <c r="F113"/>
     </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54024,7 +54024,7 @@
       </c>
       <c r="F114"/>
     </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54042,7 +54042,7 @@
       </c>
       <c r="F115"/>
     </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54060,7 +54060,7 @@
       </c>
       <c r="F116"/>
     </row>
-    <row r="117" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A117" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54078,7 +54078,7 @@
       </c>
       <c r="F117"/>
     </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54096,7 +54096,7 @@
       </c>
       <c r="F118"/>
     </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54114,7 +54114,7 @@
       </c>
       <c r="F119"/>
     </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54132,7 +54132,7 @@
       </c>
       <c r="F120"/>
     </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54150,7 +54150,7 @@
       </c>
       <c r="F121"/>
     </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A122" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54168,7 +54168,7 @@
       </c>
       <c r="F122"/>
     </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54186,7 +54186,7 @@
       </c>
       <c r="F123"/>
     </row>
-    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54204,7 +54204,7 @@
       </c>
       <c r="F124"/>
     </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54222,7 +54222,7 @@
       </c>
       <c r="F125"/>
     </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54240,7 +54240,7 @@
       </c>
       <c r="F126"/>
     </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54366,7 +54366,7 @@
       </c>
       <c r="F133"/>
     </row>
-    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54384,7 +54384,7 @@
       </c>
       <c r="F134"/>
     </row>
-    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54402,7 +54402,7 @@
       </c>
       <c r="F135"/>
     </row>
-    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54420,7 +54420,7 @@
       </c>
       <c r="F136"/>
     </row>
-    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54438,7 +54438,7 @@
       </c>
       <c r="F137"/>
     </row>
-    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54456,7 +54456,7 @@
       </c>
       <c r="F138"/>
     </row>
-    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54474,7 +54474,7 @@
       </c>
       <c r="F139"/>
     </row>
-    <row r="140" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A140" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54492,7 +54492,7 @@
       </c>
       <c r="F140"/>
     </row>
-    <row r="141" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A141" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54510,7 +54510,7 @@
       </c>
       <c r="F141"/>
     </row>
-    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54528,7 +54528,7 @@
       </c>
       <c r="F142"/>
     </row>
-    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54546,7 +54546,7 @@
       </c>
       <c r="F143"/>
     </row>
-    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54564,7 +54564,7 @@
       </c>
       <c r="F144"/>
     </row>
-    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54582,7 +54582,7 @@
       </c>
       <c r="F145"/>
     </row>
-    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54600,7 +54600,7 @@
       </c>
       <c r="F146"/>
     </row>
-    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54618,7 +54618,7 @@
       </c>
       <c r="F147"/>
     </row>
-    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54636,7 +54636,7 @@
       </c>
       <c r="F148"/>
     </row>
-    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54654,7 +54654,7 @@
       </c>
       <c r="F149"/>
     </row>
-    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54672,7 +54672,7 @@
       </c>
       <c r="F150"/>
     </row>
-    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54690,7 +54690,7 @@
       </c>
       <c r="F151"/>
     </row>
-    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54708,7 +54708,7 @@
       </c>
       <c r="F152"/>
     </row>
-    <row r="153" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A153" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54726,7 +54726,7 @@
       </c>
       <c r="F153"/>
     </row>
-    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54744,7 +54744,7 @@
       </c>
       <c r="F154"/>
     </row>
-    <row r="155" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A155" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54762,7 +54762,7 @@
       </c>
       <c r="F155"/>
     </row>
-    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A156" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54780,7 +54780,7 @@
       </c>
       <c r="F156"/>
     </row>
-    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A157" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54798,7 +54798,7 @@
       </c>
       <c r="F157"/>
     </row>
-    <row r="158" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A158" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54816,7 +54816,7 @@
       </c>
       <c r="F158"/>
     </row>
-    <row r="159" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A159" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54834,7 +54834,7 @@
       </c>
       <c r="F159"/>
     </row>
-    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A160" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54852,7 +54852,7 @@
       </c>
       <c r="F160"/>
     </row>
-    <row r="161" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A161" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54870,7 +54870,7 @@
       </c>
       <c r="F161"/>
     </row>
-    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54888,7 +54888,7 @@
       </c>
       <c r="F162"/>
     </row>
-    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54906,7 +54906,7 @@
       </c>
       <c r="F163"/>
     </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A164" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54924,7 +54924,7 @@
       </c>
       <c r="F164"/>
     </row>
-    <row r="165" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A165" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54942,7 +54942,7 @@
       </c>
       <c r="F165"/>
     </row>
-    <row r="166" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A166" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54960,7 +54960,7 @@
       </c>
       <c r="F166"/>
     </row>
-    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54978,7 +54978,7 @@
       </c>
       <c r="F167"/>
     </row>
-    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="4" t="s">
         <v>1111</v>
       </c>
@@ -54996,7 +54996,7 @@
       </c>
       <c r="F168"/>
     </row>
-    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55014,7 +55014,7 @@
       </c>
       <c r="F169"/>
     </row>
-    <row r="170" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A170" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55032,7 +55032,7 @@
       </c>
       <c r="F170"/>
     </row>
-    <row r="171" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A171" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55050,7 +55050,7 @@
       </c>
       <c r="F171"/>
     </row>
-    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55068,7 +55068,7 @@
       </c>
       <c r="F172"/>
     </row>
-    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55086,7 +55086,7 @@
       </c>
       <c r="F173"/>
     </row>
-    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55104,7 +55104,7 @@
       </c>
       <c r="F174"/>
     </row>
-    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55122,7 +55122,7 @@
       </c>
       <c r="F175"/>
     </row>
-    <row r="176" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A176" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55140,7 +55140,7 @@
       </c>
       <c r="F176"/>
     </row>
-    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55158,7 +55158,7 @@
       </c>
       <c r="F177"/>
     </row>
-    <row r="178" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A178" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55176,7 +55176,7 @@
       </c>
       <c r="F178"/>
     </row>
-    <row r="179" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A179" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55194,7 +55194,7 @@
       </c>
       <c r="F179"/>
     </row>
-    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55212,7 +55212,7 @@
       </c>
       <c r="F180"/>
     </row>
-    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55230,7 +55230,7 @@
       </c>
       <c r="F181"/>
     </row>
-    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55248,7 +55248,7 @@
       </c>
       <c r="F182"/>
     </row>
-    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="4" t="s">
         <v>1111</v>
       </c>
@@ -55266,7 +55266,7 @@
       </c>
       <c r="F183"/>
     </row>
-    <row r="184" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A184" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55286,7 +55286,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55306,7 +55306,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55326,7 +55326,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55346,7 +55346,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A188" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55366,7 +55366,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55386,7 +55386,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55406,7 +55406,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55426,7 +55426,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55446,7 +55446,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55466,7 +55466,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="194" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A194" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55486,7 +55486,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="195" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A195" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55506,7 +55506,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="196" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A196" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55524,7 +55524,7 @@
       </c>
       <c r="F196"/>
     </row>
-    <row r="197" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A197" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55542,7 +55542,7 @@
       </c>
       <c r="F197"/>
     </row>
-    <row r="198" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A198" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55560,7 +55560,7 @@
       </c>
       <c r="F198"/>
     </row>
-    <row r="199" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A199" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55578,7 +55578,7 @@
       </c>
       <c r="F199"/>
     </row>
-    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55596,7 +55596,7 @@
       </c>
       <c r="F200"/>
     </row>
-    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55614,7 +55614,7 @@
       </c>
       <c r="F201"/>
     </row>
-    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55632,7 +55632,7 @@
       </c>
       <c r="F202"/>
     </row>
-    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55650,7 +55650,7 @@
       </c>
       <c r="F203"/>
     </row>
-    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55668,7 +55668,7 @@
       </c>
       <c r="F204"/>
     </row>
-    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A205" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55686,7 +55686,7 @@
       </c>
       <c r="F205"/>
     </row>
-    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A206" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55704,7 +55704,7 @@
       </c>
       <c r="F206"/>
     </row>
-    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A207" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55722,7 +55722,7 @@
       </c>
       <c r="F207"/>
     </row>
-    <row r="208" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A208" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55740,7 +55740,7 @@
       </c>
       <c r="F208"/>
     </row>
-    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A209" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55758,7 +55758,7 @@
       </c>
       <c r="F209"/>
     </row>
-    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A210" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55776,7 +55776,7 @@
       </c>
       <c r="F210"/>
     </row>
-    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A211" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55794,7 +55794,7 @@
       </c>
       <c r="F211"/>
     </row>
-    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A212" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55812,7 +55812,7 @@
       </c>
       <c r="F212"/>
     </row>
-    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A213" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55830,7 +55830,7 @@
       </c>
       <c r="F213"/>
     </row>
-    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A214" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55848,7 +55848,7 @@
       </c>
       <c r="F214"/>
     </row>
-    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A215" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55866,7 +55866,7 @@
       </c>
       <c r="F215"/>
     </row>
-    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A216" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55884,7 +55884,7 @@
       </c>
       <c r="F216"/>
     </row>
-    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A217" s="4" t="s">
         <v>1118</v>
       </c>
@@ -55902,7 +55902,7 @@
       </c>
       <c r="F217"/>
     </row>
-    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A218" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56028,7 +56028,7 @@
       </c>
       <c r="F224"/>
     </row>
-    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56046,7 +56046,7 @@
       </c>
       <c r="F225"/>
     </row>
-    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56064,7 +56064,7 @@
       </c>
       <c r="F226"/>
     </row>
-    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56082,7 +56082,7 @@
       </c>
       <c r="F227"/>
     </row>
-    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56100,7 +56100,7 @@
       </c>
       <c r="F228"/>
     </row>
-    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56118,7 +56118,7 @@
       </c>
       <c r="F229"/>
     </row>
-    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56136,7 +56136,7 @@
       </c>
       <c r="F230"/>
     </row>
-    <row r="231" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A231" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56154,7 +56154,7 @@
       </c>
       <c r="F231"/>
     </row>
-    <row r="232" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A232" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56172,7 +56172,7 @@
       </c>
       <c r="F232"/>
     </row>
-    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A233" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56190,7 +56190,7 @@
       </c>
       <c r="F233"/>
     </row>
-    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A234" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56208,7 +56208,7 @@
       </c>
       <c r="F234"/>
     </row>
-    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A235" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56226,7 +56226,7 @@
       </c>
       <c r="F235"/>
     </row>
-    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A236" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56244,7 +56244,7 @@
       </c>
       <c r="F236"/>
     </row>
-    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A237" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56262,7 +56262,7 @@
       </c>
       <c r="F237"/>
     </row>
-    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A238" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56280,7 +56280,7 @@
       </c>
       <c r="F238"/>
     </row>
-    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A239" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56298,7 +56298,7 @@
       </c>
       <c r="F239"/>
     </row>
-    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A240" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56316,7 +56316,7 @@
       </c>
       <c r="F240"/>
     </row>
-    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A241" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56334,7 +56334,7 @@
       </c>
       <c r="F241"/>
     </row>
-    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56352,7 +56352,7 @@
       </c>
       <c r="F242"/>
     </row>
-    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56370,7 +56370,7 @@
       </c>
       <c r="F243"/>
     </row>
-    <row r="244" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A244" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56388,7 +56388,7 @@
       </c>
       <c r="F244"/>
     </row>
-    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56406,7 +56406,7 @@
       </c>
       <c r="F245"/>
     </row>
-    <row r="246" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A246" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56424,7 +56424,7 @@
       </c>
       <c r="F246"/>
     </row>
-    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56442,7 +56442,7 @@
       </c>
       <c r="F247"/>
     </row>
-    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56460,7 +56460,7 @@
       </c>
       <c r="F248"/>
     </row>
-    <row r="249" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A249" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56478,7 +56478,7 @@
       </c>
       <c r="F249"/>
     </row>
-    <row r="250" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A250" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56496,7 +56496,7 @@
       </c>
       <c r="F250"/>
     </row>
-    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A251" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56514,7 +56514,7 @@
       </c>
       <c r="F251"/>
     </row>
-    <row r="252" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A252" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56532,7 +56532,7 @@
       </c>
       <c r="F252"/>
     </row>
-    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A253" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56550,7 +56550,7 @@
       </c>
       <c r="F253"/>
     </row>
-    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A254" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56568,7 +56568,7 @@
       </c>
       <c r="F254"/>
     </row>
-    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A255" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56586,7 +56586,7 @@
       </c>
       <c r="F255"/>
     </row>
-    <row r="256" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A256" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56604,7 +56604,7 @@
       </c>
       <c r="F256"/>
     </row>
-    <row r="257" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A257" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56622,7 +56622,7 @@
       </c>
       <c r="F257"/>
     </row>
-    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A258" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56640,7 +56640,7 @@
       </c>
       <c r="F258"/>
     </row>
-    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A259" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56658,7 +56658,7 @@
       </c>
       <c r="F259"/>
     </row>
-    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A260" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56676,7 +56676,7 @@
       </c>
       <c r="F260"/>
     </row>
-    <row r="261" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A261" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56694,7 +56694,7 @@
       </c>
       <c r="F261"/>
     </row>
-    <row r="262" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A262" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56712,7 +56712,7 @@
       </c>
       <c r="F262"/>
     </row>
-    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A263" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56730,7 +56730,7 @@
       </c>
       <c r="F263"/>
     </row>
-    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A264" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56748,7 +56748,7 @@
       </c>
       <c r="F264"/>
     </row>
-    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A265" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56766,7 +56766,7 @@
       </c>
       <c r="F265"/>
     </row>
-    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A266" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56784,7 +56784,7 @@
       </c>
       <c r="F266"/>
     </row>
-    <row r="267" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A267" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56802,7 +56802,7 @@
       </c>
       <c r="F267"/>
     </row>
-    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A268" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56820,7 +56820,7 @@
       </c>
       <c r="F268"/>
     </row>
-    <row r="269" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A269" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56838,7 +56838,7 @@
       </c>
       <c r="F269"/>
     </row>
-    <row r="270" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A270" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56856,7 +56856,7 @@
       </c>
       <c r="F270"/>
     </row>
-    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A271" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56874,7 +56874,7 @@
       </c>
       <c r="F271"/>
     </row>
-    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A272" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56892,7 +56892,7 @@
       </c>
       <c r="F272"/>
     </row>
-    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A273" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56910,7 +56910,7 @@
       </c>
       <c r="F273"/>
     </row>
-    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A274" s="4" t="s">
         <v>1118</v>
       </c>
@@ -56928,7 +56928,7 @@
       </c>
       <c r="F274"/>
     </row>
-    <row r="275" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A275" s="4" t="s">
         <v>1119</v>
       </c>
@@ -56948,7 +56948,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A276" s="4" t="s">
         <v>1119</v>
       </c>
@@ -56968,7 +56968,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A277" s="4" t="s">
         <v>1119</v>
       </c>
@@ -56988,7 +56988,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A278" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57008,7 +57008,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="279" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A279" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57028,7 +57028,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A280" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57048,7 +57048,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A281" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57068,7 +57068,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A282" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57088,7 +57088,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="283" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A283" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57108,7 +57108,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="284" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A284" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57128,7 +57128,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A285" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57148,7 +57148,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A286" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57168,7 +57168,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="287" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A287" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57188,7 +57188,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="288" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A288" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57208,7 +57208,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="289" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A289" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57226,7 +57226,7 @@
       </c>
       <c r="F289"/>
     </row>
-    <row r="290" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A290" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57244,7 +57244,7 @@
       </c>
       <c r="F290"/>
     </row>
-    <row r="291" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A291" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57262,7 +57262,7 @@
       </c>
       <c r="F291"/>
     </row>
-    <row r="292" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A292" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57280,7 +57280,7 @@
       </c>
       <c r="F292"/>
     </row>
-    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A293" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57298,7 +57298,7 @@
       </c>
       <c r="F293"/>
     </row>
-    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A294" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57316,7 +57316,7 @@
       </c>
       <c r="F294"/>
     </row>
-    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A295" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57334,7 +57334,7 @@
       </c>
       <c r="F295"/>
     </row>
-    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A296" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57352,7 +57352,7 @@
       </c>
       <c r="F296"/>
     </row>
-    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A297" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57370,7 +57370,7 @@
       </c>
       <c r="F297"/>
     </row>
-    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A298" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57388,7 +57388,7 @@
       </c>
       <c r="F298"/>
     </row>
-    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A299" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57406,7 +57406,7 @@
       </c>
       <c r="F299"/>
     </row>
-    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A300" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57424,7 +57424,7 @@
       </c>
       <c r="F300"/>
     </row>
-    <row r="301" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A301" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57442,7 +57442,7 @@
       </c>
       <c r="F301"/>
     </row>
-    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A302" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57460,7 +57460,7 @@
       </c>
       <c r="F302"/>
     </row>
-    <row r="303" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A303" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57478,7 +57478,7 @@
       </c>
       <c r="F303"/>
     </row>
-    <row r="304" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A304" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57496,7 +57496,7 @@
       </c>
       <c r="F304"/>
     </row>
-    <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A305" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57514,7 +57514,7 @@
       </c>
       <c r="F305"/>
     </row>
-    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A306" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57532,7 +57532,7 @@
       </c>
       <c r="F306"/>
     </row>
-    <row r="307" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A307" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57550,7 +57550,7 @@
       </c>
       <c r="F307"/>
     </row>
-    <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A308" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57568,7 +57568,7 @@
       </c>
       <c r="F308"/>
     </row>
-    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A309" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57586,7 +57586,7 @@
       </c>
       <c r="F309"/>
     </row>
-    <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A310" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57604,7 +57604,7 @@
       </c>
       <c r="F310"/>
     </row>
-    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A311" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57730,7 +57730,7 @@
       </c>
       <c r="F317"/>
     </row>
-    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A318" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57748,7 +57748,7 @@
       </c>
       <c r="F318"/>
     </row>
-    <row r="319" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A319" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57766,7 +57766,7 @@
       </c>
       <c r="F319"/>
     </row>
-    <row r="320" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A320" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57784,7 +57784,7 @@
       </c>
       <c r="F320"/>
     </row>
-    <row r="321" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57802,7 +57802,7 @@
       </c>
       <c r="F321"/>
     </row>
-    <row r="322" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A322" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57820,7 +57820,7 @@
       </c>
       <c r="F322"/>
     </row>
-    <row r="323" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A323" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57838,7 +57838,7 @@
       </c>
       <c r="F323"/>
     </row>
-    <row r="324" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A324" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57856,7 +57856,7 @@
       </c>
       <c r="F324"/>
     </row>
-    <row r="325" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A325" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57874,7 +57874,7 @@
       </c>
       <c r="F325"/>
     </row>
-    <row r="326" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57892,7 +57892,7 @@
       </c>
       <c r="F326"/>
     </row>
-    <row r="327" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57910,7 +57910,7 @@
       </c>
       <c r="F327"/>
     </row>
-    <row r="328" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57928,7 +57928,7 @@
       </c>
       <c r="F328"/>
     </row>
-    <row r="329" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A329" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57946,7 +57946,7 @@
       </c>
       <c r="F329"/>
     </row>
-    <row r="330" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57964,7 +57964,7 @@
       </c>
       <c r="F330"/>
     </row>
-    <row r="331" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" s="4" t="s">
         <v>1119</v>
       </c>
@@ -57982,7 +57982,7 @@
       </c>
       <c r="F331"/>
     </row>
-    <row r="332" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58000,7 +58000,7 @@
       </c>
       <c r="F332"/>
     </row>
-    <row r="333" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A333" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58018,7 +58018,7 @@
       </c>
       <c r="F333"/>
     </row>
-    <row r="334" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A334" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58036,7 +58036,7 @@
       </c>
       <c r="F334"/>
     </row>
-    <row r="335" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A335" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58054,7 +58054,7 @@
       </c>
       <c r="F335"/>
     </row>
-    <row r="336" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A336" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58072,7 +58072,7 @@
       </c>
       <c r="F336"/>
     </row>
-    <row r="337" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A337" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58090,7 +58090,7 @@
       </c>
       <c r="F337"/>
     </row>
-    <row r="338" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A338" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58108,7 +58108,7 @@
       </c>
       <c r="F338"/>
     </row>
-    <row r="339" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A339" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58126,7 +58126,7 @@
       </c>
       <c r="F339"/>
     </row>
-    <row r="340" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A340" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58144,7 +58144,7 @@
       </c>
       <c r="F340"/>
     </row>
-    <row r="341" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A341" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58162,7 +58162,7 @@
       </c>
       <c r="F341"/>
     </row>
-    <row r="342" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58180,7 +58180,7 @@
       </c>
       <c r="F342"/>
     </row>
-    <row r="343" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A343" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58198,7 +58198,7 @@
       </c>
       <c r="F343"/>
     </row>
-    <row r="344" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A344" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58216,7 +58216,7 @@
       </c>
       <c r="F344"/>
     </row>
-    <row r="345" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A345" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58234,7 +58234,7 @@
       </c>
       <c r="F345"/>
     </row>
-    <row r="346" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A346" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58252,7 +58252,7 @@
       </c>
       <c r="F346"/>
     </row>
-    <row r="347" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A347" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58270,7 +58270,7 @@
       </c>
       <c r="F347"/>
     </row>
-    <row r="348" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A348" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58288,7 +58288,7 @@
       </c>
       <c r="F348"/>
     </row>
-    <row r="349" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A349" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58306,7 +58306,7 @@
       </c>
       <c r="F349"/>
     </row>
-    <row r="350" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A350" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58324,7 +58324,7 @@
       </c>
       <c r="F350"/>
     </row>
-    <row r="351" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A351" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58342,7 +58342,7 @@
       </c>
       <c r="F351"/>
     </row>
-    <row r="352" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A352" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58360,7 +58360,7 @@
       </c>
       <c r="F352"/>
     </row>
-    <row r="353" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A353" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58378,7 +58378,7 @@
       </c>
       <c r="F353"/>
     </row>
-    <row r="354" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A354" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58396,7 +58396,7 @@
       </c>
       <c r="F354"/>
     </row>
-    <row r="355" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A355" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58414,7 +58414,7 @@
       </c>
       <c r="F355"/>
     </row>
-    <row r="356" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A356" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58432,7 +58432,7 @@
       </c>
       <c r="F356"/>
     </row>
-    <row r="357" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A357" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58450,7 +58450,7 @@
       </c>
       <c r="F357"/>
     </row>
-    <row r="358" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A358" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58468,7 +58468,7 @@
       </c>
       <c r="F358"/>
     </row>
-    <row r="359" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58486,7 +58486,7 @@
       </c>
       <c r="F359"/>
     </row>
-    <row r="360" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A360" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58504,7 +58504,7 @@
       </c>
       <c r="F360"/>
     </row>
-    <row r="361" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A361" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58522,7 +58522,7 @@
       </c>
       <c r="F361"/>
     </row>
-    <row r="362" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A362" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58540,7 +58540,7 @@
       </c>
       <c r="F362"/>
     </row>
-    <row r="363" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A363" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58558,7 +58558,7 @@
       </c>
       <c r="F363"/>
     </row>
-    <row r="364" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A364" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58576,7 +58576,7 @@
       </c>
       <c r="F364"/>
     </row>
-    <row r="365" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A365" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58594,7 +58594,7 @@
       </c>
       <c r="F365"/>
     </row>
-    <row r="366" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A366" s="4" t="s">
         <v>1119</v>
       </c>
@@ -58612,7 +58612,7 @@
       </c>
       <c r="F366"/>
     </row>
-    <row r="367" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A367" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58632,7 +58632,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="368" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A368" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58652,7 +58652,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="369" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A369" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58672,7 +58672,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="370" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A370" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58692,7 +58692,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="371" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A371" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58712,7 +58712,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="372" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A372" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58732,7 +58732,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="373" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A373" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58752,7 +58752,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="374" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A374" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58772,7 +58772,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="375" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58792,7 +58792,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="376" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A376" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58812,7 +58812,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="377" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A377" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58832,7 +58832,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="378" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A378" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58852,7 +58852,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="379" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A379" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58872,7 +58872,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="380" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A380" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58892,7 +58892,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="381" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A381" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58910,7 +58910,7 @@
       </c>
       <c r="F381"/>
     </row>
-    <row r="382" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A382" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58928,7 +58928,7 @@
       </c>
       <c r="F382"/>
     </row>
-    <row r="383" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A383" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58946,7 +58946,7 @@
       </c>
       <c r="F383"/>
     </row>
-    <row r="384" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A384" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58964,7 +58964,7 @@
       </c>
       <c r="F384"/>
     </row>
-    <row r="385" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A385" s="4" t="s">
         <v>1120</v>
       </c>
@@ -58982,7 +58982,7 @@
       </c>
       <c r="F385"/>
     </row>
-    <row r="386" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A386" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59000,7 +59000,7 @@
       </c>
       <c r="F386"/>
     </row>
-    <row r="387" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A387" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59018,7 +59018,7 @@
       </c>
       <c r="F387"/>
     </row>
-    <row r="388" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A388" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59036,7 +59036,7 @@
       </c>
       <c r="F388"/>
     </row>
-    <row r="389" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A389" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59054,7 +59054,7 @@
       </c>
       <c r="F389"/>
     </row>
-    <row r="390" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A390" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59072,7 +59072,7 @@
       </c>
       <c r="F390"/>
     </row>
-    <row r="391" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59090,7 +59090,7 @@
       </c>
       <c r="F391"/>
     </row>
-    <row r="392" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A392" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59108,7 +59108,7 @@
       </c>
       <c r="F392"/>
     </row>
-    <row r="393" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A393" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59126,7 +59126,7 @@
       </c>
       <c r="F393"/>
     </row>
-    <row r="394" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59144,7 +59144,7 @@
       </c>
       <c r="F394"/>
     </row>
-    <row r="395" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59162,7 +59162,7 @@
       </c>
       <c r="F395"/>
     </row>
-    <row r="396" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A396" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59180,7 +59180,7 @@
       </c>
       <c r="F396"/>
     </row>
-    <row r="397" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A397" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59198,7 +59198,7 @@
       </c>
       <c r="F397"/>
     </row>
-    <row r="398" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A398" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59216,7 +59216,7 @@
       </c>
       <c r="F398"/>
     </row>
-    <row r="399" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A399" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59234,7 +59234,7 @@
       </c>
       <c r="F399"/>
     </row>
-    <row r="400" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A400" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59252,7 +59252,7 @@
       </c>
       <c r="F400"/>
     </row>
-    <row r="401" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A401" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59270,7 +59270,7 @@
       </c>
       <c r="F401"/>
     </row>
-    <row r="402" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A402" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59288,7 +59288,7 @@
       </c>
       <c r="F402"/>
     </row>
-    <row r="403" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A403" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59414,7 +59414,7 @@
       </c>
       <c r="F409"/>
     </row>
-    <row r="410" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A410" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59432,7 +59432,7 @@
       </c>
       <c r="F410"/>
     </row>
-    <row r="411" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A411" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59450,7 +59450,7 @@
       </c>
       <c r="F411"/>
     </row>
-    <row r="412" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A412" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59468,7 +59468,7 @@
       </c>
       <c r="F412"/>
     </row>
-    <row r="413" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A413" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59486,7 +59486,7 @@
       </c>
       <c r="F413"/>
     </row>
-    <row r="414" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A414" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59504,7 +59504,7 @@
       </c>
       <c r="F414"/>
     </row>
-    <row r="415" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A415" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59522,7 +59522,7 @@
       </c>
       <c r="F415"/>
     </row>
-    <row r="416" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A416" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59540,7 +59540,7 @@
       </c>
       <c r="F416"/>
     </row>
-    <row r="417" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A417" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59558,7 +59558,7 @@
       </c>
       <c r="F417"/>
     </row>
-    <row r="418" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A418" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59576,7 +59576,7 @@
       </c>
       <c r="F418"/>
     </row>
-    <row r="419" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A419" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59594,7 +59594,7 @@
       </c>
       <c r="F419"/>
     </row>
-    <row r="420" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A420" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59612,7 +59612,7 @@
       </c>
       <c r="F420"/>
     </row>
-    <row r="421" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A421" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59630,7 +59630,7 @@
       </c>
       <c r="F421"/>
     </row>
-    <row r="422" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A422" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59648,7 +59648,7 @@
       </c>
       <c r="F422"/>
     </row>
-    <row r="423" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A423" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59666,7 +59666,7 @@
       </c>
       <c r="F423"/>
     </row>
-    <row r="424" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A424" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59684,7 +59684,7 @@
       </c>
       <c r="F424"/>
     </row>
-    <row r="425" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A425" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59702,7 +59702,7 @@
       </c>
       <c r="F425"/>
     </row>
-    <row r="426" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A426" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59720,7 +59720,7 @@
       </c>
       <c r="F426"/>
     </row>
-    <row r="427" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A427" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59738,7 +59738,7 @@
       </c>
       <c r="F427"/>
     </row>
-    <row r="428" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A428" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59756,7 +59756,7 @@
       </c>
       <c r="F428"/>
     </row>
-    <row r="429" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A429" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59774,7 +59774,7 @@
       </c>
       <c r="F429"/>
     </row>
-    <row r="430" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A430" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59792,7 +59792,7 @@
       </c>
       <c r="F430"/>
     </row>
-    <row r="431" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A431" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59810,7 +59810,7 @@
       </c>
       <c r="F431"/>
     </row>
-    <row r="432" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A432" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59828,7 +59828,7 @@
       </c>
       <c r="F432"/>
     </row>
-    <row r="433" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A433" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59846,7 +59846,7 @@
       </c>
       <c r="F433"/>
     </row>
-    <row r="434" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A434" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59864,7 +59864,7 @@
       </c>
       <c r="F434"/>
     </row>
-    <row r="435" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A435" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59882,7 +59882,7 @@
       </c>
       <c r="F435"/>
     </row>
-    <row r="436" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A436" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59900,7 +59900,7 @@
       </c>
       <c r="F436"/>
     </row>
-    <row r="437" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A437" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59918,7 +59918,7 @@
       </c>
       <c r="F437"/>
     </row>
-    <row r="438" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A438" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59936,7 +59936,7 @@
       </c>
       <c r="F438"/>
     </row>
-    <row r="439" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A439" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59954,7 +59954,7 @@
       </c>
       <c r="F439"/>
     </row>
-    <row r="440" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A440" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59972,7 +59972,7 @@
       </c>
       <c r="F440"/>
     </row>
-    <row r="441" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A441" s="4" t="s">
         <v>1120</v>
       </c>
@@ -59990,7 +59990,7 @@
       </c>
       <c r="F441"/>
     </row>
-    <row r="442" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A442" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60008,7 +60008,7 @@
       </c>
       <c r="F442"/>
     </row>
-    <row r="443" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A443" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60026,7 +60026,7 @@
       </c>
       <c r="F443"/>
     </row>
-    <row r="444" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A444" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60044,7 +60044,7 @@
       </c>
       <c r="F444"/>
     </row>
-    <row r="445" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A445" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60062,7 +60062,7 @@
       </c>
       <c r="F445"/>
     </row>
-    <row r="446" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A446" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60080,7 +60080,7 @@
       </c>
       <c r="F446"/>
     </row>
-    <row r="447" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A447" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60098,7 +60098,7 @@
       </c>
       <c r="F447"/>
     </row>
-    <row r="448" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A448" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60116,7 +60116,7 @@
       </c>
       <c r="F448"/>
     </row>
-    <row r="449" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A449" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60134,7 +60134,7 @@
       </c>
       <c r="F449"/>
     </row>
-    <row r="450" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A450" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60152,7 +60152,7 @@
       </c>
       <c r="F450"/>
     </row>
-    <row r="451" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A451" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60170,7 +60170,7 @@
       </c>
       <c r="F451"/>
     </row>
-    <row r="452" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A452" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60188,7 +60188,7 @@
       </c>
       <c r="F452"/>
     </row>
-    <row r="453" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A453" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60206,7 +60206,7 @@
       </c>
       <c r="F453"/>
     </row>
-    <row r="454" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A454" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60224,7 +60224,7 @@
       </c>
       <c r="F454"/>
     </row>
-    <row r="455" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A455" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60242,7 +60242,7 @@
       </c>
       <c r="F455"/>
     </row>
-    <row r="456" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A456" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60260,7 +60260,7 @@
       </c>
       <c r="F456"/>
     </row>
-    <row r="457" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A457" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60278,7 +60278,7 @@
       </c>
       <c r="F457"/>
     </row>
-    <row r="458" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A458" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60296,7 +60296,7 @@
       </c>
       <c r="F458"/>
     </row>
-    <row r="459" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A459" s="4" t="s">
         <v>1120</v>
       </c>
@@ -60314,7 +60314,7 @@
       </c>
       <c r="F459"/>
     </row>
-    <row r="460" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A460" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60334,7 +60334,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="461" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A461" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60354,7 +60354,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="462" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A462" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60374,7 +60374,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="463" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A463" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60394,7 +60394,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="464" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A464" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60414,7 +60414,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="465" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A465" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60434,7 +60434,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="466" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A466" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60454,7 +60454,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="467" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A467" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60474,7 +60474,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="468" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A468" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60494,7 +60494,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="469" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A469" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60514,7 +60514,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="470" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A470" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60534,7 +60534,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="471" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A471" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60554,7 +60554,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="472" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A472" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60574,7 +60574,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="473" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A473" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60594,7 +60594,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="474" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A474" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60612,7 +60612,7 @@
       </c>
       <c r="F474"/>
     </row>
-    <row r="475" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A475" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60630,7 +60630,7 @@
       </c>
       <c r="F475"/>
     </row>
-    <row r="476" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A476" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60648,7 +60648,7 @@
       </c>
       <c r="F476"/>
     </row>
-    <row r="477" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A477" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60666,7 +60666,7 @@
       </c>
       <c r="F477"/>
     </row>
-    <row r="478" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A478" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60684,7 +60684,7 @@
       </c>
       <c r="F478"/>
     </row>
-    <row r="479" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A479" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60702,7 +60702,7 @@
       </c>
       <c r="F479"/>
     </row>
-    <row r="480" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A480" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60720,7 +60720,7 @@
       </c>
       <c r="F480"/>
     </row>
-    <row r="481" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A481" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60738,7 +60738,7 @@
       </c>
       <c r="F481"/>
     </row>
-    <row r="482" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A482" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60756,7 +60756,7 @@
       </c>
       <c r="F482"/>
     </row>
-    <row r="483" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A483" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60774,7 +60774,7 @@
       </c>
       <c r="F483"/>
     </row>
-    <row r="484" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A484" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60792,7 +60792,7 @@
       </c>
       <c r="F484"/>
     </row>
-    <row r="485" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A485" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60810,7 +60810,7 @@
       </c>
       <c r="F485"/>
     </row>
-    <row r="486" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A486" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60828,7 +60828,7 @@
       </c>
       <c r="F486"/>
     </row>
-    <row r="487" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A487" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60846,7 +60846,7 @@
       </c>
       <c r="F487"/>
     </row>
-    <row r="488" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A488" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60864,7 +60864,7 @@
       </c>
       <c r="F488"/>
     </row>
-    <row r="489" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A489" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60882,7 +60882,7 @@
       </c>
       <c r="F489"/>
     </row>
-    <row r="490" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A490" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60900,7 +60900,7 @@
       </c>
       <c r="F490"/>
     </row>
-    <row r="491" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A491" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60918,7 +60918,7 @@
       </c>
       <c r="F491"/>
     </row>
-    <row r="492" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A492" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60936,7 +60936,7 @@
       </c>
       <c r="F492"/>
     </row>
-    <row r="493" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A493" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60954,7 +60954,7 @@
       </c>
       <c r="F493"/>
     </row>
-    <row r="494" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A494" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60972,7 +60972,7 @@
       </c>
       <c r="F494"/>
     </row>
-    <row r="495" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A495" s="4" t="s">
         <v>1121</v>
       </c>
@@ -60990,7 +60990,7 @@
       </c>
       <c r="F495"/>
     </row>
-    <row r="496" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A496" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61116,7 +61116,7 @@
       </c>
       <c r="F502"/>
     </row>
-    <row r="503" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A503" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61134,7 +61134,7 @@
       </c>
       <c r="F503"/>
     </row>
-    <row r="504" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A504" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61152,7 +61152,7 @@
       </c>
       <c r="F504"/>
     </row>
-    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A505" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61170,7 +61170,7 @@
       </c>
       <c r="F505"/>
     </row>
-    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A506" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61188,7 +61188,7 @@
       </c>
       <c r="F506"/>
     </row>
-    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A507" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61206,7 +61206,7 @@
       </c>
       <c r="F507"/>
     </row>
-    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A508" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61224,7 +61224,7 @@
       </c>
       <c r="F508"/>
     </row>
-    <row r="509" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A509" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61242,7 +61242,7 @@
       </c>
       <c r="F509"/>
     </row>
-    <row r="510" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A510" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61260,7 +61260,7 @@
       </c>
       <c r="F510"/>
     </row>
-    <row r="511" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A511" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61278,7 +61278,7 @@
       </c>
       <c r="F511"/>
     </row>
-    <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A512" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61296,7 +61296,7 @@
       </c>
       <c r="F512"/>
     </row>
-    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A513" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61314,7 +61314,7 @@
       </c>
       <c r="F513"/>
     </row>
-    <row r="514" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A514" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61332,7 +61332,7 @@
       </c>
       <c r="F514"/>
     </row>
-    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A515" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61350,7 +61350,7 @@
       </c>
       <c r="F515"/>
     </row>
-    <row r="516" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A516" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61368,7 +61368,7 @@
       </c>
       <c r="F516"/>
     </row>
-    <row r="517" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A517" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61386,7 +61386,7 @@
       </c>
       <c r="F517"/>
     </row>
-    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A518" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61404,7 +61404,7 @@
       </c>
       <c r="F518"/>
     </row>
-    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A519" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61422,7 +61422,7 @@
       </c>
       <c r="F519"/>
     </row>
-    <row r="520" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A520" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61440,7 +61440,7 @@
       </c>
       <c r="F520"/>
     </row>
-    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A521" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61458,7 +61458,7 @@
       </c>
       <c r="F521"/>
     </row>
-    <row r="522" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A522" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61476,7 +61476,7 @@
       </c>
       <c r="F522"/>
     </row>
-    <row r="523" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A523" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61494,7 +61494,7 @@
       </c>
       <c r="F523"/>
     </row>
-    <row r="524" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A524" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61512,7 +61512,7 @@
       </c>
       <c r="F524"/>
     </row>
-    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A525" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61530,7 +61530,7 @@
       </c>
       <c r="F525"/>
     </row>
-    <row r="526" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A526" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61548,7 +61548,7 @@
       </c>
       <c r="F526"/>
     </row>
-    <row r="527" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A527" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61566,7 +61566,7 @@
       </c>
       <c r="F527"/>
     </row>
-    <row r="528" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A528" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61584,7 +61584,7 @@
       </c>
       <c r="F528"/>
     </row>
-    <row r="529" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A529" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61602,7 +61602,7 @@
       </c>
       <c r="F529"/>
     </row>
-    <row r="530" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A530" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61620,7 +61620,7 @@
       </c>
       <c r="F530"/>
     </row>
-    <row r="531" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A531" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61638,7 +61638,7 @@
       </c>
       <c r="F531"/>
     </row>
-    <row r="532" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A532" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61656,7 +61656,7 @@
       </c>
       <c r="F532"/>
     </row>
-    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A533" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61674,7 +61674,7 @@
       </c>
       <c r="F533"/>
     </row>
-    <row r="534" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A534" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61692,7 +61692,7 @@
       </c>
       <c r="F534"/>
     </row>
-    <row r="535" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A535" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61710,7 +61710,7 @@
       </c>
       <c r="F535"/>
     </row>
-    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A536" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61728,7 +61728,7 @@
       </c>
       <c r="F536"/>
     </row>
-    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A537" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61746,7 +61746,7 @@
       </c>
       <c r="F537"/>
     </row>
-    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A538" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61764,7 +61764,7 @@
       </c>
       <c r="F538"/>
     </row>
-    <row r="539" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A539" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61782,7 +61782,7 @@
       </c>
       <c r="F539"/>
     </row>
-    <row r="540" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A540" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61800,7 +61800,7 @@
       </c>
       <c r="F540"/>
     </row>
-    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A541" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61818,7 +61818,7 @@
       </c>
       <c r="F541"/>
     </row>
-    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A542" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61836,7 +61836,7 @@
       </c>
       <c r="F542"/>
     </row>
-    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A543" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61854,7 +61854,7 @@
       </c>
       <c r="F543"/>
     </row>
-    <row r="544" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A544" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61872,7 +61872,7 @@
       </c>
       <c r="F544"/>
     </row>
-    <row r="545" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A545" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61890,7 +61890,7 @@
       </c>
       <c r="F545"/>
     </row>
-    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A546" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61908,7 +61908,7 @@
       </c>
       <c r="F546"/>
     </row>
-    <row r="547" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A547" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61926,7 +61926,7 @@
       </c>
       <c r="F547"/>
     </row>
-    <row r="548" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A548" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61944,7 +61944,7 @@
       </c>
       <c r="F548"/>
     </row>
-    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A549" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61962,7 +61962,7 @@
       </c>
       <c r="F549"/>
     </row>
-    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A550" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61980,7 +61980,7 @@
       </c>
       <c r="F550"/>
     </row>
-    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A551" s="4" t="s">
         <v>1121</v>
       </c>
@@ -61998,7 +61998,7 @@
       </c>
       <c r="F551"/>
     </row>
-    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A552" s="4" t="s">
         <v>1121</v>
       </c>
@@ -62016,7 +62016,7 @@
       </c>
       <c r="F552"/>
     </row>
-    <row r="553" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A553" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62036,7 +62036,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A554" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62056,7 +62056,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A555" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62076,7 +62076,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A556" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62096,7 +62096,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="557" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A557" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62116,7 +62116,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A558" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62136,7 +62136,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="559" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A559" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62156,7 +62156,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A560" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62176,7 +62176,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="561" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A561" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62196,7 +62196,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="562" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A562" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62216,7 +62216,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="563" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A563" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62236,7 +62236,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A564" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62256,7 +62256,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="565" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A565" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62276,7 +62276,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="566" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A566" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62296,7 +62296,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="567" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A567" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62314,7 +62314,7 @@
       </c>
       <c r="F567"/>
     </row>
-    <row r="568" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A568" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62332,7 +62332,7 @@
       </c>
       <c r="F568"/>
     </row>
-    <row r="569" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A569" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62350,7 +62350,7 @@
       </c>
       <c r="F569"/>
     </row>
-    <row r="570" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A570" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62368,7 +62368,7 @@
       </c>
       <c r="F570"/>
     </row>
-    <row r="571" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A571" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62386,7 +62386,7 @@
       </c>
       <c r="F571"/>
     </row>
-    <row r="572" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A572" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62404,7 +62404,7 @@
       </c>
       <c r="F572"/>
     </row>
-    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A573" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62422,7 +62422,7 @@
       </c>
       <c r="F573"/>
     </row>
-    <row r="574" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A574" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62440,7 +62440,7 @@
       </c>
       <c r="F574"/>
     </row>
-    <row r="575" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A575" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62458,7 +62458,7 @@
       </c>
       <c r="F575"/>
     </row>
-    <row r="576" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A576" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62476,7 +62476,7 @@
       </c>
       <c r="F576"/>
     </row>
-    <row r="577" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A577" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62494,7 +62494,7 @@
       </c>
       <c r="F577"/>
     </row>
-    <row r="578" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A578" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62512,7 +62512,7 @@
       </c>
       <c r="F578"/>
     </row>
-    <row r="579" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A579" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62530,7 +62530,7 @@
       </c>
       <c r="F579"/>
     </row>
-    <row r="580" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A580" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62548,7 +62548,7 @@
       </c>
       <c r="F580"/>
     </row>
-    <row r="581" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A581" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62566,7 +62566,7 @@
       </c>
       <c r="F581"/>
     </row>
-    <row r="582" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A582" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62584,7 +62584,7 @@
       </c>
       <c r="F582"/>
     </row>
-    <row r="583" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A583" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62602,7 +62602,7 @@
       </c>
       <c r="F583"/>
     </row>
-    <row r="584" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A584" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62620,7 +62620,7 @@
       </c>
       <c r="F584"/>
     </row>
-    <row r="585" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A585" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62638,7 +62638,7 @@
       </c>
       <c r="F585"/>
     </row>
-    <row r="586" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A586" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62656,7 +62656,7 @@
       </c>
       <c r="F586"/>
     </row>
-    <row r="587" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A587" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62674,7 +62674,7 @@
       </c>
       <c r="F587"/>
     </row>
-    <row r="588" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A588" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62692,7 +62692,7 @@
       </c>
       <c r="F588"/>
     </row>
-    <row r="589" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A589" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62818,7 +62818,7 @@
       </c>
       <c r="F595"/>
     </row>
-    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A596" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62836,7 +62836,7 @@
       </c>
       <c r="F596"/>
     </row>
-    <row r="597" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A597" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62854,7 +62854,7 @@
       </c>
       <c r="F597"/>
     </row>
-    <row r="598" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A598" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62872,7 +62872,7 @@
       </c>
       <c r="F598"/>
     </row>
-    <row r="599" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A599" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62890,7 +62890,7 @@
       </c>
       <c r="F599"/>
     </row>
-    <row r="600" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A600" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62908,7 +62908,7 @@
       </c>
       <c r="F600"/>
     </row>
-    <row r="601" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A601" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62926,7 +62926,7 @@
       </c>
       <c r="F601"/>
     </row>
-    <row r="602" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A602" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62944,7 +62944,7 @@
       </c>
       <c r="F602"/>
     </row>
-    <row r="603" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A603" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62962,7 +62962,7 @@
       </c>
       <c r="F603"/>
     </row>
-    <row r="604" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A604" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62980,7 +62980,7 @@
       </c>
       <c r="F604"/>
     </row>
-    <row r="605" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A605" s="4" t="s">
         <v>1122</v>
       </c>
@@ -62998,7 +62998,7 @@
       </c>
       <c r="F605"/>
     </row>
-    <row r="606" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A606" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63016,7 +63016,7 @@
       </c>
       <c r="F606"/>
     </row>
-    <row r="607" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A607" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63034,7 +63034,7 @@
       </c>
       <c r="F607"/>
     </row>
-    <row r="608" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A608" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63052,7 +63052,7 @@
       </c>
       <c r="F608"/>
     </row>
-    <row r="609" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A609" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63070,7 +63070,7 @@
       </c>
       <c r="F609"/>
     </row>
-    <row r="610" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A610" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63088,7 +63088,7 @@
       </c>
       <c r="F610"/>
     </row>
-    <row r="611" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A611" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63106,7 +63106,7 @@
       </c>
       <c r="F611"/>
     </row>
-    <row r="612" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A612" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63124,7 +63124,7 @@
       </c>
       <c r="F612"/>
     </row>
-    <row r="613" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A613" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63142,7 +63142,7 @@
       </c>
       <c r="F613"/>
     </row>
-    <row r="614" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A614" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63160,7 +63160,7 @@
       </c>
       <c r="F614"/>
     </row>
-    <row r="615" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A615" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63178,7 +63178,7 @@
       </c>
       <c r="F615"/>
     </row>
-    <row r="616" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A616" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63196,7 +63196,7 @@
       </c>
       <c r="F616"/>
     </row>
-    <row r="617" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A617" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63214,7 +63214,7 @@
       </c>
       <c r="F617"/>
     </row>
-    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A618" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63232,7 +63232,7 @@
       </c>
       <c r="F618"/>
     </row>
-    <row r="619" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A619" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63250,7 +63250,7 @@
       </c>
       <c r="F619"/>
     </row>
-    <row r="620" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A620" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63268,7 +63268,7 @@
       </c>
       <c r="F620"/>
     </row>
-    <row r="621" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A621" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63286,7 +63286,7 @@
       </c>
       <c r="F621"/>
     </row>
-    <row r="622" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A622" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63304,7 +63304,7 @@
       </c>
       <c r="F622"/>
     </row>
-    <row r="623" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A623" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63322,7 +63322,7 @@
       </c>
       <c r="F623"/>
     </row>
-    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A624" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63340,7 +63340,7 @@
       </c>
       <c r="F624"/>
     </row>
-    <row r="625" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A625" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63358,7 +63358,7 @@
       </c>
       <c r="F625"/>
     </row>
-    <row r="626" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A626" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63376,7 +63376,7 @@
       </c>
       <c r="F626"/>
     </row>
-    <row r="627" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A627" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63394,7 +63394,7 @@
       </c>
       <c r="F627"/>
     </row>
-    <row r="628" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A628" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63412,7 +63412,7 @@
       </c>
       <c r="F628"/>
     </row>
-    <row r="629" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A629" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63430,7 +63430,7 @@
       </c>
       <c r="F629"/>
     </row>
-    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A630" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63448,7 +63448,7 @@
       </c>
       <c r="F630"/>
     </row>
-    <row r="631" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A631" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63466,7 +63466,7 @@
       </c>
       <c r="F631"/>
     </row>
-    <row r="632" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A632" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63484,7 +63484,7 @@
       </c>
       <c r="F632"/>
     </row>
-    <row r="633" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A633" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63502,7 +63502,7 @@
       </c>
       <c r="F633"/>
     </row>
-    <row r="634" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A634" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63520,7 +63520,7 @@
       </c>
       <c r="F634"/>
     </row>
-    <row r="635" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A635" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63538,7 +63538,7 @@
       </c>
       <c r="F635"/>
     </row>
-    <row r="636" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A636" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63556,7 +63556,7 @@
       </c>
       <c r="F636"/>
     </row>
-    <row r="637" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A637" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63574,7 +63574,7 @@
       </c>
       <c r="F637"/>
     </row>
-    <row r="638" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A638" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63592,7 +63592,7 @@
       </c>
       <c r="F638"/>
     </row>
-    <row r="639" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A639" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63610,7 +63610,7 @@
       </c>
       <c r="F639"/>
     </row>
-    <row r="640" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A640" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63628,7 +63628,7 @@
       </c>
       <c r="F640"/>
     </row>
-    <row r="641" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A641" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63646,7 +63646,7 @@
       </c>
       <c r="F641"/>
     </row>
-    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A642" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63664,7 +63664,7 @@
       </c>
       <c r="F642"/>
     </row>
-    <row r="643" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A643" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63682,7 +63682,7 @@
       </c>
       <c r="F643"/>
     </row>
-    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A644" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63700,7 +63700,7 @@
       </c>
       <c r="F644"/>
     </row>
-    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A645" s="4" t="s">
         <v>1122</v>
       </c>
@@ -63718,7 +63718,7 @@
       </c>
       <c r="F645"/>
     </row>
-    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A646" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63738,7 +63738,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A647" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63758,7 +63758,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="648" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A648" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63778,7 +63778,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="649" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A649" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63795,7 +63795,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A650" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63815,7 +63815,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="651" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A651" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63835,7 +63835,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="652" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A652" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63855,7 +63855,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="653" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A653" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63875,7 +63875,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="654" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A654" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63895,7 +63895,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="655" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A655" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63915,7 +63915,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="656" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A656" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63933,7 +63933,7 @@
       </c>
       <c r="F656"/>
     </row>
-    <row r="657" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A657" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63951,7 +63951,7 @@
       </c>
       <c r="F657"/>
     </row>
-    <row r="658" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A658" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63969,7 +63969,7 @@
       </c>
       <c r="F658"/>
     </row>
-    <row r="659" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A659" s="4" t="s">
         <v>1116</v>
       </c>
@@ -63987,7 +63987,7 @@
       </c>
       <c r="F659"/>
     </row>
-    <row r="660" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A660" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64005,7 +64005,7 @@
       </c>
       <c r="F660"/>
     </row>
-    <row r="661" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A661" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64023,7 +64023,7 @@
       </c>
       <c r="F661"/>
     </row>
-    <row r="662" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A662" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64041,7 +64041,7 @@
       </c>
       <c r="F662"/>
     </row>
-    <row r="663" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A663" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64059,7 +64059,7 @@
       </c>
       <c r="F663"/>
     </row>
-    <row r="664" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A664" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64077,7 +64077,7 @@
       </c>
       <c r="F664"/>
     </row>
-    <row r="665" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A665" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64095,7 +64095,7 @@
       </c>
       <c r="F665"/>
     </row>
-    <row r="666" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A666" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64113,7 +64113,7 @@
       </c>
       <c r="F666"/>
     </row>
-    <row r="667" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A667" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64131,7 +64131,7 @@
       </c>
       <c r="F667"/>
     </row>
-    <row r="668" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A668" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64149,7 +64149,7 @@
       </c>
       <c r="F668"/>
     </row>
-    <row r="669" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A669" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64167,7 +64167,7 @@
       </c>
       <c r="F669"/>
     </row>
-    <row r="670" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A670" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64185,7 +64185,7 @@
       </c>
       <c r="F670"/>
     </row>
-    <row r="671" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A671" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64203,7 +64203,7 @@
       </c>
       <c r="F671"/>
     </row>
-    <row r="672" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A672" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64221,7 +64221,7 @@
       </c>
       <c r="F672"/>
     </row>
-    <row r="673" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A673" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64239,7 +64239,7 @@
       </c>
       <c r="F673"/>
     </row>
-    <row r="674" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A674" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64257,7 +64257,7 @@
       </c>
       <c r="F674"/>
     </row>
-    <row r="675" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A675" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64275,7 +64275,7 @@
       </c>
       <c r="F675"/>
     </row>
-    <row r="676" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A676" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64293,7 +64293,7 @@
       </c>
       <c r="F676"/>
     </row>
-    <row r="677" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A677" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64311,7 +64311,7 @@
       </c>
       <c r="F677"/>
     </row>
-    <row r="678" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A678" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64437,7 +64437,7 @@
       </c>
       <c r="F684"/>
     </row>
-    <row r="685" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A685" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64455,7 +64455,7 @@
       </c>
       <c r="F685"/>
     </row>
-    <row r="686" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A686" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64473,7 +64473,7 @@
       </c>
       <c r="F686"/>
     </row>
-    <row r="687" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A687" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64491,7 +64491,7 @@
       </c>
       <c r="F687"/>
     </row>
-    <row r="688" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A688" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64509,7 +64509,7 @@
       </c>
       <c r="F688"/>
     </row>
-    <row r="689" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A689" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64527,7 +64527,7 @@
       </c>
       <c r="F689"/>
     </row>
-    <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A690" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64545,7 +64545,7 @@
       </c>
       <c r="F690"/>
     </row>
-    <row r="691" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A691" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64563,7 +64563,7 @@
       </c>
       <c r="F691"/>
     </row>
-    <row r="692" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A692" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64581,7 +64581,7 @@
       </c>
       <c r="F692"/>
     </row>
-    <row r="693" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A693" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64599,7 +64599,7 @@
       </c>
       <c r="F693"/>
     </row>
-    <row r="694" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A694" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64617,7 +64617,7 @@
       </c>
       <c r="F694"/>
     </row>
-    <row r="695" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A695" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64635,7 +64635,7 @@
       </c>
       <c r="F695"/>
     </row>
-    <row r="696" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A696" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64653,7 +64653,7 @@
       </c>
       <c r="F696"/>
     </row>
-    <row r="697" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A697" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64671,7 +64671,7 @@
       </c>
       <c r="F697"/>
     </row>
-    <row r="698" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A698" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64689,7 +64689,7 @@
       </c>
       <c r="F698"/>
     </row>
-    <row r="699" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A699" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64707,7 +64707,7 @@
       </c>
       <c r="F699"/>
     </row>
-    <row r="700" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A700" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64725,7 +64725,7 @@
       </c>
       <c r="F700"/>
     </row>
-    <row r="701" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A701" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64743,7 +64743,7 @@
       </c>
       <c r="F701"/>
     </row>
-    <row r="702" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A702" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64761,7 +64761,7 @@
       </c>
       <c r="F702"/>
     </row>
-    <row r="703" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A703" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64779,7 +64779,7 @@
       </c>
       <c r="F703"/>
     </row>
-    <row r="704" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A704" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64797,7 +64797,7 @@
       </c>
       <c r="F704"/>
     </row>
-    <row r="705" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A705" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64815,7 +64815,7 @@
       </c>
       <c r="F705"/>
     </row>
-    <row r="706" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A706" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64833,7 +64833,7 @@
       </c>
       <c r="F706"/>
     </row>
-    <row r="707" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A707" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64851,7 +64851,7 @@
       </c>
       <c r="F707"/>
     </row>
-    <row r="708" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A708" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64869,7 +64869,7 @@
       </c>
       <c r="F708"/>
     </row>
-    <row r="709" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A709" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64887,7 +64887,7 @@
       </c>
       <c r="F709"/>
     </row>
-    <row r="710" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A710" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64905,7 +64905,7 @@
       </c>
       <c r="F710"/>
     </row>
-    <row r="711" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A711" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64923,7 +64923,7 @@
       </c>
       <c r="F711"/>
     </row>
-    <row r="712" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A712" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64941,7 +64941,7 @@
       </c>
       <c r="F712"/>
     </row>
-    <row r="713" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A713" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64959,7 +64959,7 @@
       </c>
       <c r="F713"/>
     </row>
-    <row r="714" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A714" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64977,7 +64977,7 @@
       </c>
       <c r="F714"/>
     </row>
-    <row r="715" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A715" s="4" t="s">
         <v>1116</v>
       </c>
@@ -64995,7 +64995,7 @@
       </c>
       <c r="F715"/>
     </row>
-    <row r="716" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A716" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65013,7 +65013,7 @@
       </c>
       <c r="F716"/>
     </row>
-    <row r="717" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A717" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65031,7 +65031,7 @@
       </c>
       <c r="F717"/>
     </row>
-    <row r="718" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A718" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65049,7 +65049,7 @@
       </c>
       <c r="F718"/>
     </row>
-    <row r="719" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A719" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65067,7 +65067,7 @@
       </c>
       <c r="F719"/>
     </row>
-    <row r="720" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A720" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65085,7 +65085,7 @@
       </c>
       <c r="F720"/>
     </row>
-    <row r="721" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A721" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65103,7 +65103,7 @@
       </c>
       <c r="F721"/>
     </row>
-    <row r="722" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A722" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65121,7 +65121,7 @@
       </c>
       <c r="F722"/>
     </row>
-    <row r="723" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A723" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65139,7 +65139,7 @@
       </c>
       <c r="F723"/>
     </row>
-    <row r="724" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A724" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65157,7 +65157,7 @@
       </c>
       <c r="F724"/>
     </row>
-    <row r="725" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A725" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65175,7 +65175,7 @@
       </c>
       <c r="F725"/>
     </row>
-    <row r="726" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A726" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65193,7 +65193,7 @@
       </c>
       <c r="F726"/>
     </row>
-    <row r="727" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A727" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65211,7 +65211,7 @@
       </c>
       <c r="F727"/>
     </row>
-    <row r="728" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A728" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65229,7 +65229,7 @@
       </c>
       <c r="F728"/>
     </row>
-    <row r="729" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A729" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65247,7 +65247,7 @@
       </c>
       <c r="F729"/>
     </row>
-    <row r="730" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A730" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65265,7 +65265,7 @@
       </c>
       <c r="F730"/>
     </row>
-    <row r="731" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A731" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65283,7 +65283,7 @@
       </c>
       <c r="F731"/>
     </row>
-    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A732" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65301,7 +65301,7 @@
       </c>
       <c r="F732"/>
     </row>
-    <row r="733" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A733" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65319,7 +65319,7 @@
       </c>
       <c r="F733"/>
     </row>
-    <row r="734" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A734" s="4" t="s">
         <v>1116</v>
       </c>
@@ -65337,7 +65337,7 @@
       </c>
       <c r="F734"/>
     </row>
-    <row r="735" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A735" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65357,7 +65357,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="736" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A736" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65377,7 +65377,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="737" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A737" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65397,7 +65397,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="738" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A738" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65417,7 +65417,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="739" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A739" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65437,7 +65437,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="740" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A740" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65457,7 +65457,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="741" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A741" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65477,7 +65477,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="742" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A742" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65497,7 +65497,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="743" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A743" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65517,7 +65517,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="744" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A744" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65537,7 +65537,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="745" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A745" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65557,7 +65557,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="746" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A746" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65577,7 +65577,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="747" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A747" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65595,7 +65595,7 @@
       </c>
       <c r="F747"/>
     </row>
-    <row r="748" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A748" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65613,7 +65613,7 @@
       </c>
       <c r="F748"/>
     </row>
-    <row r="749" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A749" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65631,7 +65631,7 @@
       </c>
       <c r="F749"/>
     </row>
-    <row r="750" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A750" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65649,7 +65649,7 @@
       </c>
       <c r="F750"/>
     </row>
-    <row r="751" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A751" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65667,7 +65667,7 @@
       </c>
       <c r="F751"/>
     </row>
-    <row r="752" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A752" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65685,7 +65685,7 @@
       </c>
       <c r="F752"/>
     </row>
-    <row r="753" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A753" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65703,7 +65703,7 @@
       </c>
       <c r="F753"/>
     </row>
-    <row r="754" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A754" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65721,7 +65721,7 @@
       </c>
       <c r="F754"/>
     </row>
-    <row r="755" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A755" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65739,7 +65739,7 @@
       </c>
       <c r="F755"/>
     </row>
-    <row r="756" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A756" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65757,7 +65757,7 @@
       </c>
       <c r="F756"/>
     </row>
-    <row r="757" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A757" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65775,7 +65775,7 @@
       </c>
       <c r="F757"/>
     </row>
-    <row r="758" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A758" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65793,7 +65793,7 @@
       </c>
       <c r="F758"/>
     </row>
-    <row r="759" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A759" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65811,7 +65811,7 @@
       </c>
       <c r="F759"/>
     </row>
-    <row r="760" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A760" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65829,7 +65829,7 @@
       </c>
       <c r="F760"/>
     </row>
-    <row r="761" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A761" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65847,7 +65847,7 @@
       </c>
       <c r="F761"/>
     </row>
-    <row r="762" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A762" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65865,7 +65865,7 @@
       </c>
       <c r="F762"/>
     </row>
-    <row r="763" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A763" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65883,7 +65883,7 @@
       </c>
       <c r="F763"/>
     </row>
-    <row r="764" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A764" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65901,7 +65901,7 @@
       </c>
       <c r="F764"/>
     </row>
-    <row r="765" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A765" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65919,7 +65919,7 @@
       </c>
       <c r="F765"/>
     </row>
-    <row r="766" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A766" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65937,7 +65937,7 @@
       </c>
       <c r="F766"/>
     </row>
-    <row r="767" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A767" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65955,7 +65955,7 @@
       </c>
       <c r="F767"/>
     </row>
-    <row r="768" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A768" s="4" t="s">
         <v>1117</v>
       </c>
@@ -65973,7 +65973,7 @@
       </c>
       <c r="F768"/>
     </row>
-    <row r="769" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A769" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66099,7 +66099,7 @@
       </c>
       <c r="F775"/>
     </row>
-    <row r="776" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A776" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66117,7 +66117,7 @@
       </c>
       <c r="F776"/>
     </row>
-    <row r="777" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A777" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66135,7 +66135,7 @@
       </c>
       <c r="F777"/>
     </row>
-    <row r="778" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A778" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66153,7 +66153,7 @@
       </c>
       <c r="F778"/>
     </row>
-    <row r="779" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A779" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66171,7 +66171,7 @@
       </c>
       <c r="F779"/>
     </row>
-    <row r="780" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A780" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66189,7 +66189,7 @@
       </c>
       <c r="F780"/>
     </row>
-    <row r="781" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A781" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66207,7 +66207,7 @@
       </c>
       <c r="F781"/>
     </row>
-    <row r="782" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A782" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66225,7 +66225,7 @@
       </c>
       <c r="F782"/>
     </row>
-    <row r="783" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A783" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66243,7 +66243,7 @@
       </c>
       <c r="F783"/>
     </row>
-    <row r="784" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A784" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66261,7 +66261,7 @@
       </c>
       <c r="F784"/>
     </row>
-    <row r="785" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A785" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66279,7 +66279,7 @@
       </c>
       <c r="F785"/>
     </row>
-    <row r="786" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A786" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66297,7 +66297,7 @@
       </c>
       <c r="F786"/>
     </row>
-    <row r="787" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A787" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66315,7 +66315,7 @@
       </c>
       <c r="F787"/>
     </row>
-    <row r="788" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A788" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66333,7 +66333,7 @@
       </c>
       <c r="F788"/>
     </row>
-    <row r="789" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A789" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66351,7 +66351,7 @@
       </c>
       <c r="F789"/>
     </row>
-    <row r="790" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A790" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66369,7 +66369,7 @@
       </c>
       <c r="F790"/>
     </row>
-    <row r="791" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A791" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66387,7 +66387,7 @@
       </c>
       <c r="F791"/>
     </row>
-    <row r="792" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A792" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66405,7 +66405,7 @@
       </c>
       <c r="F792"/>
     </row>
-    <row r="793" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A793" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66423,7 +66423,7 @@
       </c>
       <c r="F793"/>
     </row>
-    <row r="794" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A794" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66441,7 +66441,7 @@
       </c>
       <c r="F794"/>
     </row>
-    <row r="795" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A795" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66459,7 +66459,7 @@
       </c>
       <c r="F795"/>
     </row>
-    <row r="796" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A796" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66477,7 +66477,7 @@
       </c>
       <c r="F796"/>
     </row>
-    <row r="797" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A797" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66495,7 +66495,7 @@
       </c>
       <c r="F797"/>
     </row>
-    <row r="798" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A798" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66513,7 +66513,7 @@
       </c>
       <c r="F798"/>
     </row>
-    <row r="799" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A799" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66531,7 +66531,7 @@
       </c>
       <c r="F799"/>
     </row>
-    <row r="800" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A800" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66549,7 +66549,7 @@
       </c>
       <c r="F800"/>
     </row>
-    <row r="801" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A801" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66567,7 +66567,7 @@
       </c>
       <c r="F801"/>
     </row>
-    <row r="802" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A802" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66585,7 +66585,7 @@
       </c>
       <c r="F802"/>
     </row>
-    <row r="803" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A803" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66603,7 +66603,7 @@
       </c>
       <c r="F803"/>
     </row>
-    <row r="804" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A804" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66621,7 +66621,7 @@
       </c>
       <c r="F804"/>
     </row>
-    <row r="805" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A805" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66639,7 +66639,7 @@
       </c>
       <c r="F805"/>
     </row>
-    <row r="806" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A806" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66657,7 +66657,7 @@
       </c>
       <c r="F806"/>
     </row>
-    <row r="807" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A807" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66675,7 +66675,7 @@
       </c>
       <c r="F807"/>
     </row>
-    <row r="808" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A808" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66693,7 +66693,7 @@
       </c>
       <c r="F808"/>
     </row>
-    <row r="809" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A809" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66711,7 +66711,7 @@
       </c>
       <c r="F809"/>
     </row>
-    <row r="810" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A810" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66729,7 +66729,7 @@
       </c>
       <c r="F810"/>
     </row>
-    <row r="811" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A811" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66747,7 +66747,7 @@
       </c>
       <c r="F811"/>
     </row>
-    <row r="812" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A812" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66765,7 +66765,7 @@
       </c>
       <c r="F812"/>
     </row>
-    <row r="813" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A813" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66783,7 +66783,7 @@
       </c>
       <c r="F813"/>
     </row>
-    <row r="814" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A814" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66801,7 +66801,7 @@
       </c>
       <c r="F814"/>
     </row>
-    <row r="815" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A815" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66819,7 +66819,7 @@
       </c>
       <c r="F815"/>
     </row>
-    <row r="816" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A816" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66837,7 +66837,7 @@
       </c>
       <c r="F816"/>
     </row>
-    <row r="817" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A817" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66855,7 +66855,7 @@
       </c>
       <c r="F817"/>
     </row>
-    <row r="818" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A818" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66873,7 +66873,7 @@
       </c>
       <c r="F818"/>
     </row>
-    <row r="819" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A819" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66891,7 +66891,7 @@
       </c>
       <c r="F819"/>
     </row>
-    <row r="820" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A820" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66909,7 +66909,7 @@
       </c>
       <c r="F820"/>
     </row>
-    <row r="821" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A821" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66927,7 +66927,7 @@
       </c>
       <c r="F821"/>
     </row>
-    <row r="822" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A822" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66945,7 +66945,7 @@
       </c>
       <c r="F822"/>
     </row>
-    <row r="823" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A823" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66963,7 +66963,7 @@
       </c>
       <c r="F823"/>
     </row>
-    <row r="824" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A824" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66981,7 +66981,7 @@
       </c>
       <c r="F824"/>
     </row>
-    <row r="825" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A825" s="4" t="s">
         <v>1117</v>
       </c>
@@ -66999,7 +66999,7 @@
       </c>
       <c r="F825"/>
     </row>
-    <row r="826" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A826" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67019,7 +67019,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="827" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A827" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67039,7 +67039,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="828" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A828" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67059,7 +67059,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="829" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A829" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67079,7 +67079,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="830" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A830" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67099,7 +67099,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="831" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A831" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67119,7 +67119,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="832" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A832" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67139,7 +67139,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="833" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A833" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67159,7 +67159,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="834" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A834" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67179,7 +67179,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="835" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A835" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67199,7 +67199,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="836" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A836" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67219,7 +67219,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="837" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A837" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67239,7 +67239,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="838" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A838" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67257,7 +67257,7 @@
       </c>
       <c r="F838"/>
     </row>
-    <row r="839" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A839" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67275,7 +67275,7 @@
       </c>
       <c r="F839"/>
     </row>
-    <row r="840" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A840" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67293,7 +67293,7 @@
       </c>
       <c r="F840"/>
     </row>
-    <row r="841" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A841" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67311,7 +67311,7 @@
       </c>
       <c r="F841"/>
     </row>
-    <row r="842" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A842" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67329,7 +67329,7 @@
       </c>
       <c r="F842"/>
     </row>
-    <row r="843" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A843" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67347,7 +67347,7 @@
       </c>
       <c r="F843"/>
     </row>
-    <row r="844" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A844" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67365,7 +67365,7 @@
       </c>
       <c r="F844"/>
     </row>
-    <row r="845" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A845" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67383,7 +67383,7 @@
       </c>
       <c r="F845"/>
     </row>
-    <row r="846" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A846" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67401,7 +67401,7 @@
       </c>
       <c r="F846"/>
     </row>
-    <row r="847" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A847" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67419,7 +67419,7 @@
       </c>
       <c r="F847"/>
     </row>
-    <row r="848" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A848" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67437,7 +67437,7 @@
       </c>
       <c r="F848"/>
     </row>
-    <row r="849" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A849" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67455,7 +67455,7 @@
       </c>
       <c r="F849"/>
     </row>
-    <row r="850" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A850" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67473,7 +67473,7 @@
       </c>
       <c r="F850"/>
     </row>
-    <row r="851" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A851" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67491,7 +67491,7 @@
       </c>
       <c r="F851"/>
     </row>
-    <row r="852" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A852" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67509,7 +67509,7 @@
       </c>
       <c r="F852"/>
     </row>
-    <row r="853" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A853" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67527,7 +67527,7 @@
       </c>
       <c r="F853"/>
     </row>
-    <row r="854" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A854" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67545,7 +67545,7 @@
       </c>
       <c r="F854"/>
     </row>
-    <row r="855" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A855" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67563,7 +67563,7 @@
       </c>
       <c r="F855"/>
     </row>
-    <row r="856" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A856" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67581,7 +67581,7 @@
       </c>
       <c r="F856"/>
     </row>
-    <row r="857" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A857" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67599,7 +67599,7 @@
       </c>
       <c r="F857"/>
     </row>
-    <row r="858" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A858" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67617,7 +67617,7 @@
       </c>
       <c r="F858"/>
     </row>
-    <row r="859" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A859" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67635,7 +67635,7 @@
       </c>
       <c r="F859"/>
     </row>
-    <row r="860" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A860" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67761,7 +67761,7 @@
       </c>
       <c r="F866"/>
     </row>
-    <row r="867" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A867" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67779,7 +67779,7 @@
       </c>
       <c r="F867"/>
     </row>
-    <row r="868" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A868" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67797,7 +67797,7 @@
       </c>
       <c r="F868"/>
     </row>
-    <row r="869" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A869" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67815,7 +67815,7 @@
       </c>
       <c r="F869"/>
     </row>
-    <row r="870" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A870" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67833,7 +67833,7 @@
       </c>
       <c r="F870"/>
     </row>
-    <row r="871" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A871" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67851,7 +67851,7 @@
       </c>
       <c r="F871"/>
     </row>
-    <row r="872" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A872" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67869,7 +67869,7 @@
       </c>
       <c r="F872"/>
     </row>
-    <row r="873" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A873" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67887,7 +67887,7 @@
       </c>
       <c r="F873"/>
     </row>
-    <row r="874" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A874" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67905,7 +67905,7 @@
       </c>
       <c r="F874"/>
     </row>
-    <row r="875" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A875" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67923,7 +67923,7 @@
       </c>
       <c r="F875"/>
     </row>
-    <row r="876" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A876" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67941,7 +67941,7 @@
       </c>
       <c r="F876"/>
     </row>
-    <row r="877" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A877" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67959,7 +67959,7 @@
       </c>
       <c r="F877"/>
     </row>
-    <row r="878" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A878" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67977,7 +67977,7 @@
       </c>
       <c r="F878"/>
     </row>
-    <row r="879" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A879" s="4" t="s">
         <v>1112</v>
       </c>
@@ -67995,7 +67995,7 @@
       </c>
       <c r="F879"/>
     </row>
-    <row r="880" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A880" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68013,7 +68013,7 @@
       </c>
       <c r="F880"/>
     </row>
-    <row r="881" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A881" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68031,7 +68031,7 @@
       </c>
       <c r="F881"/>
     </row>
-    <row r="882" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A882" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68049,7 +68049,7 @@
       </c>
       <c r="F882"/>
     </row>
-    <row r="883" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A883" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68067,7 +68067,7 @@
       </c>
       <c r="F883"/>
     </row>
-    <row r="884" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A884" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68085,7 +68085,7 @@
       </c>
       <c r="F884"/>
     </row>
-    <row r="885" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A885" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68103,7 +68103,7 @@
       </c>
       <c r="F885"/>
     </row>
-    <row r="886" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A886" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68121,7 +68121,7 @@
       </c>
       <c r="F886"/>
     </row>
-    <row r="887" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A887" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68139,7 +68139,7 @@
       </c>
       <c r="F887"/>
     </row>
-    <row r="888" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A888" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68157,7 +68157,7 @@
       </c>
       <c r="F888"/>
     </row>
-    <row r="889" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A889" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68175,7 +68175,7 @@
       </c>
       <c r="F889"/>
     </row>
-    <row r="890" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A890" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68193,7 +68193,7 @@
       </c>
       <c r="F890"/>
     </row>
-    <row r="891" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A891" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68211,7 +68211,7 @@
       </c>
       <c r="F891"/>
     </row>
-    <row r="892" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A892" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68229,7 +68229,7 @@
       </c>
       <c r="F892"/>
     </row>
-    <row r="893" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A893" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68247,7 +68247,7 @@
       </c>
       <c r="F893"/>
     </row>
-    <row r="894" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A894" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68265,7 +68265,7 @@
       </c>
       <c r="F894"/>
     </row>
-    <row r="895" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A895" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68283,7 +68283,7 @@
       </c>
       <c r="F895"/>
     </row>
-    <row r="896" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A896" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68301,7 +68301,7 @@
       </c>
       <c r="F896"/>
     </row>
-    <row r="897" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A897" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68319,7 +68319,7 @@
       </c>
       <c r="F897"/>
     </row>
-    <row r="898" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A898" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68337,7 +68337,7 @@
       </c>
       <c r="F898"/>
     </row>
-    <row r="899" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A899" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68355,7 +68355,7 @@
       </c>
       <c r="F899"/>
     </row>
-    <row r="900" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A900" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68373,7 +68373,7 @@
       </c>
       <c r="F900"/>
     </row>
-    <row r="901" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A901" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68391,7 +68391,7 @@
       </c>
       <c r="F901"/>
     </row>
-    <row r="902" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A902" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68409,7 +68409,7 @@
       </c>
       <c r="F902"/>
     </row>
-    <row r="903" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A903" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68427,7 +68427,7 @@
       </c>
       <c r="F903"/>
     </row>
-    <row r="904" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A904" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68445,7 +68445,7 @@
       </c>
       <c r="F904"/>
     </row>
-    <row r="905" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A905" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68463,7 +68463,7 @@
       </c>
       <c r="F905"/>
     </row>
-    <row r="906" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A906" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68481,7 +68481,7 @@
       </c>
       <c r="F906"/>
     </row>
-    <row r="907" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A907" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68499,7 +68499,7 @@
       </c>
       <c r="F907"/>
     </row>
-    <row r="908" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A908" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68517,7 +68517,7 @@
       </c>
       <c r="F908"/>
     </row>
-    <row r="909" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A909" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68535,7 +68535,7 @@
       </c>
       <c r="F909"/>
     </row>
-    <row r="910" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A910" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68553,7 +68553,7 @@
       </c>
       <c r="F910"/>
     </row>
-    <row r="911" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A911" s="4" t="s">
         <v>1112</v>
       </c>
@@ -68571,7 +68571,7 @@
       </c>
       <c r="F911"/>
     </row>
-    <row r="912" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A912" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68591,7 +68591,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="913" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A913" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68611,7 +68611,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="914" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A914" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68631,7 +68631,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="915" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A915" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68651,7 +68651,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="916" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A916" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68671,7 +68671,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="917" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A917" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68691,7 +68691,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="918" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A918" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68711,7 +68711,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="919" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A919" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68731,7 +68731,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="920" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A920" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68751,7 +68751,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="921" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A921" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68771,7 +68771,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="922" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A922" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68789,7 +68789,7 @@
       </c>
       <c r="F922"/>
     </row>
-    <row r="923" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A923" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68807,7 +68807,7 @@
       </c>
       <c r="F923"/>
     </row>
-    <row r="924" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A924" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68825,7 +68825,7 @@
       </c>
       <c r="F924"/>
     </row>
-    <row r="925" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A925" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68843,7 +68843,7 @@
       </c>
       <c r="F925"/>
     </row>
-    <row r="926" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A926" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68861,7 +68861,7 @@
       </c>
       <c r="F926"/>
     </row>
-    <row r="927" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A927" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68879,7 +68879,7 @@
       </c>
       <c r="F927"/>
     </row>
-    <row r="928" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A928" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68897,7 +68897,7 @@
       </c>
       <c r="F928"/>
     </row>
-    <row r="929" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A929" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68915,7 +68915,7 @@
       </c>
       <c r="F929"/>
     </row>
-    <row r="930" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A930" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68933,7 +68933,7 @@
       </c>
       <c r="F930"/>
     </row>
-    <row r="931" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A931" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68951,7 +68951,7 @@
       </c>
       <c r="F931"/>
     </row>
-    <row r="932" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A932" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68969,7 +68969,7 @@
       </c>
       <c r="F932"/>
     </row>
-    <row r="933" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A933" s="4" t="s">
         <v>1113</v>
       </c>
@@ -68987,7 +68987,7 @@
       </c>
       <c r="F933"/>
     </row>
-    <row r="934" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A934" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69005,7 +69005,7 @@
       </c>
       <c r="F934"/>
     </row>
-    <row r="935" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A935" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69023,7 +69023,7 @@
       </c>
       <c r="F935"/>
     </row>
-    <row r="936" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A936" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69041,7 +69041,7 @@
       </c>
       <c r="F936"/>
     </row>
-    <row r="937" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A937" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69059,7 +69059,7 @@
       </c>
       <c r="F937"/>
     </row>
-    <row r="938" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A938" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69077,7 +69077,7 @@
       </c>
       <c r="F938"/>
     </row>
-    <row r="939" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A939" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69095,7 +69095,7 @@
       </c>
       <c r="F939"/>
     </row>
-    <row r="940" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A940" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69113,7 +69113,7 @@
       </c>
       <c r="F940"/>
     </row>
-    <row r="941" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A941" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69131,7 +69131,7 @@
       </c>
       <c r="F941"/>
     </row>
-    <row r="942" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A942" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69149,7 +69149,7 @@
       </c>
       <c r="F942"/>
     </row>
-    <row r="943" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A943" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69167,7 +69167,7 @@
       </c>
       <c r="F943"/>
     </row>
-    <row r="944" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A944" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69293,7 +69293,7 @@
       </c>
       <c r="F950"/>
     </row>
-    <row r="951" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A951" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69311,7 +69311,7 @@
       </c>
       <c r="F951"/>
     </row>
-    <row r="952" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A952" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69329,7 +69329,7 @@
       </c>
       <c r="F952"/>
     </row>
-    <row r="953" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A953" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69347,7 +69347,7 @@
       </c>
       <c r="F953"/>
     </row>
-    <row r="954" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A954" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69365,7 +69365,7 @@
       </c>
       <c r="F954"/>
     </row>
-    <row r="955" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A955" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69383,7 +69383,7 @@
       </c>
       <c r="F955"/>
     </row>
-    <row r="956" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A956" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69401,7 +69401,7 @@
       </c>
       <c r="F956"/>
     </row>
-    <row r="957" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A957" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69419,7 +69419,7 @@
       </c>
       <c r="F957"/>
     </row>
-    <row r="958" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A958" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69437,7 +69437,7 @@
       </c>
       <c r="F958"/>
     </row>
-    <row r="959" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A959" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69455,7 +69455,7 @@
       </c>
       <c r="F959"/>
     </row>
-    <row r="960" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A960" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69473,7 +69473,7 @@
       </c>
       <c r="F960"/>
     </row>
-    <row r="961" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A961" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69491,7 +69491,7 @@
       </c>
       <c r="F961"/>
     </row>
-    <row r="962" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A962" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69509,7 +69509,7 @@
       </c>
       <c r="F962"/>
     </row>
-    <row r="963" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A963" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69527,7 +69527,7 @@
       </c>
       <c r="F963"/>
     </row>
-    <row r="964" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A964" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69545,7 +69545,7 @@
       </c>
       <c r="F964"/>
     </row>
-    <row r="965" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A965" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69563,7 +69563,7 @@
       </c>
       <c r="F965"/>
     </row>
-    <row r="966" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A966" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69581,7 +69581,7 @@
       </c>
       <c r="F966"/>
     </row>
-    <row r="967" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A967" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69599,7 +69599,7 @@
       </c>
       <c r="F967"/>
     </row>
-    <row r="968" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A968" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69617,7 +69617,7 @@
       </c>
       <c r="F968"/>
     </row>
-    <row r="969" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A969" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69635,7 +69635,7 @@
       </c>
       <c r="F969"/>
     </row>
-    <row r="970" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A970" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69653,7 +69653,7 @@
       </c>
       <c r="F970"/>
     </row>
-    <row r="971" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A971" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69671,7 +69671,7 @@
       </c>
       <c r="F971"/>
     </row>
-    <row r="972" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A972" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69689,7 +69689,7 @@
       </c>
       <c r="F972"/>
     </row>
-    <row r="973" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A973" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69707,7 +69707,7 @@
       </c>
       <c r="F973"/>
     </row>
-    <row r="974" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A974" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69725,7 +69725,7 @@
       </c>
       <c r="F974"/>
     </row>
-    <row r="975" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A975" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69743,7 +69743,7 @@
       </c>
       <c r="F975"/>
     </row>
-    <row r="976" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A976" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69761,7 +69761,7 @@
       </c>
       <c r="F976"/>
     </row>
-    <row r="977" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A977" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69779,7 +69779,7 @@
       </c>
       <c r="F977"/>
     </row>
-    <row r="978" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A978" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69797,7 +69797,7 @@
       </c>
       <c r="F978"/>
     </row>
-    <row r="979" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A979" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69815,7 +69815,7 @@
       </c>
       <c r="F979"/>
     </row>
-    <row r="980" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A980" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69833,7 +69833,7 @@
       </c>
       <c r="F980"/>
     </row>
-    <row r="981" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A981" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69851,7 +69851,7 @@
       </c>
       <c r="F981"/>
     </row>
-    <row r="982" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A982" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69869,7 +69869,7 @@
       </c>
       <c r="F982"/>
     </row>
-    <row r="983" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A983" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69887,7 +69887,7 @@
       </c>
       <c r="F983"/>
     </row>
-    <row r="984" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A984" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69905,7 +69905,7 @@
       </c>
       <c r="F984"/>
     </row>
-    <row r="985" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A985" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69923,7 +69923,7 @@
       </c>
       <c r="F985"/>
     </row>
-    <row r="986" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A986" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69941,7 +69941,7 @@
       </c>
       <c r="F986"/>
     </row>
-    <row r="987" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A987" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69959,7 +69959,7 @@
       </c>
       <c r="F987"/>
     </row>
-    <row r="988" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A988" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69977,7 +69977,7 @@
       </c>
       <c r="F988"/>
     </row>
-    <row r="989" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A989" s="4" t="s">
         <v>1113</v>
       </c>
@@ -69995,7 +69995,7 @@
       </c>
       <c r="F989"/>
     </row>
-    <row r="990" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A990" s="4" t="s">
         <v>1113</v>
       </c>
@@ -70013,7 +70013,7 @@
       </c>
       <c r="F990"/>
     </row>
-    <row r="991" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A991" s="4" t="s">
         <v>1113</v>
       </c>
@@ -70031,7 +70031,7 @@
       </c>
       <c r="F991"/>
     </row>
-    <row r="992" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A992" s="4" t="s">
         <v>1113</v>
       </c>
@@ -70049,7 +70049,7 @@
       </c>
       <c r="F992"/>
     </row>
-    <row r="993" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A993" s="4" t="s">
         <v>1113</v>
       </c>
@@ -70067,7 +70067,7 @@
       </c>
       <c r="F993"/>
     </row>
-    <row r="994" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A994" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70087,7 +70087,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="995" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A995" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70107,7 +70107,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="996" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A996" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70127,7 +70127,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="997" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A997" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70147,7 +70147,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="998" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A998" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70167,7 +70167,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="999" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A999" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70187,7 +70187,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1000" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1000" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70207,7 +70207,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1001" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1001" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1001" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70227,7 +70227,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1002" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1002" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A1002" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70247,7 +70247,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1003" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1003" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1003" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70265,7 +70265,7 @@
       </c>
       <c r="F1003"/>
     </row>
-    <row r="1004" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1004" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1004" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70283,7 +70283,7 @@
       </c>
       <c r="F1004"/>
     </row>
-    <row r="1005" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1005" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1005" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70301,7 +70301,7 @@
       </c>
       <c r="F1005"/>
     </row>
-    <row r="1006" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1006" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1006" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70319,7 +70319,7 @@
       </c>
       <c r="F1006"/>
     </row>
-    <row r="1007" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1007" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1007" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70337,7 +70337,7 @@
       </c>
       <c r="F1007"/>
     </row>
-    <row r="1008" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1008" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1008" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70355,7 +70355,7 @@
       </c>
       <c r="F1008"/>
     </row>
-    <row r="1009" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1009" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1009" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70373,7 +70373,7 @@
       </c>
       <c r="F1009"/>
     </row>
-    <row r="1010" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1010" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1010" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70391,7 +70391,7 @@
       </c>
       <c r="F1010"/>
     </row>
-    <row r="1011" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1011" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1011" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70409,7 +70409,7 @@
       </c>
       <c r="F1011"/>
     </row>
-    <row r="1012" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1012" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1012" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70427,7 +70427,7 @@
       </c>
       <c r="F1012"/>
     </row>
-    <row r="1013" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1013" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1013" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70445,7 +70445,7 @@
       </c>
       <c r="F1013"/>
     </row>
-    <row r="1014" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1014" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1014" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70463,7 +70463,7 @@
       </c>
       <c r="F1014"/>
     </row>
-    <row r="1015" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1015" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1015" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70481,7 +70481,7 @@
       </c>
       <c r="F1015"/>
     </row>
-    <row r="1016" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1016" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1016" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70499,7 +70499,7 @@
       </c>
       <c r="F1016"/>
     </row>
-    <row r="1017" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1017" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1017" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70517,7 +70517,7 @@
       </c>
       <c r="F1017"/>
     </row>
-    <row r="1018" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1018" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1018" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70535,7 +70535,7 @@
       </c>
       <c r="F1018"/>
     </row>
-    <row r="1019" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1019" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1019" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70553,7 +70553,7 @@
       </c>
       <c r="F1019"/>
     </row>
-    <row r="1020" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1020" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1020" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70571,7 +70571,7 @@
       </c>
       <c r="F1020"/>
     </row>
-    <row r="1021" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1021" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1021" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70589,7 +70589,7 @@
       </c>
       <c r="F1021"/>
     </row>
-    <row r="1022" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1022" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1022" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70607,7 +70607,7 @@
       </c>
       <c r="F1022"/>
     </row>
-    <row r="1023" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1023" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1023" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70625,7 +70625,7 @@
       </c>
       <c r="F1023"/>
     </row>
-    <row r="1024" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1024" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1024" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70643,7 +70643,7 @@
       </c>
       <c r="F1024"/>
     </row>
-    <row r="1025" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1025" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1025" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70769,7 +70769,7 @@
       </c>
       <c r="F1031"/>
     </row>
-    <row r="1032" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1032" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1032" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70787,7 +70787,7 @@
       </c>
       <c r="F1032"/>
     </row>
-    <row r="1033" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1033" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1033" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70805,7 +70805,7 @@
       </c>
       <c r="F1033"/>
     </row>
-    <row r="1034" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1034" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1034" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70823,7 +70823,7 @@
       </c>
       <c r="F1034"/>
     </row>
-    <row r="1035" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1035" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1035" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70841,7 +70841,7 @@
       </c>
       <c r="F1035"/>
     </row>
-    <row r="1036" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1036" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1036" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70859,7 +70859,7 @@
       </c>
       <c r="F1036"/>
     </row>
-    <row r="1037" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1037" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1037" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70877,7 +70877,7 @@
       </c>
       <c r="F1037"/>
     </row>
-    <row r="1038" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1038" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1038" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70895,7 +70895,7 @@
       </c>
       <c r="F1038"/>
     </row>
-    <row r="1039" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1039" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1039" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70913,7 +70913,7 @@
       </c>
       <c r="F1039"/>
     </row>
-    <row r="1040" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1040" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1040" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70931,7 +70931,7 @@
       </c>
       <c r="F1040"/>
     </row>
-    <row r="1041" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1041" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1041" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70949,7 +70949,7 @@
       </c>
       <c r="F1041"/>
     </row>
-    <row r="1042" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1042" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1042" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70967,7 +70967,7 @@
       </c>
       <c r="F1042"/>
     </row>
-    <row r="1043" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1043" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1043" s="4" t="s">
         <v>1114</v>
       </c>
@@ -70985,7 +70985,7 @@
       </c>
       <c r="F1043"/>
     </row>
-    <row r="1044" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1044" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1044" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71003,7 +71003,7 @@
       </c>
       <c r="F1044"/>
     </row>
-    <row r="1045" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1045" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1045" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71021,7 +71021,7 @@
       </c>
       <c r="F1045"/>
     </row>
-    <row r="1046" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1046" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1046" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71039,7 +71039,7 @@
       </c>
       <c r="F1046"/>
     </row>
-    <row r="1047" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1047" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1047" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71057,7 +71057,7 @@
       </c>
       <c r="F1047"/>
     </row>
-    <row r="1048" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1048" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1048" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71075,7 +71075,7 @@
       </c>
       <c r="F1048"/>
     </row>
-    <row r="1049" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1049" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1049" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71093,7 +71093,7 @@
       </c>
       <c r="F1049"/>
     </row>
-    <row r="1050" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1050" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1050" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71111,7 +71111,7 @@
       </c>
       <c r="F1050"/>
     </row>
-    <row r="1051" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1051" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1051" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71129,7 +71129,7 @@
       </c>
       <c r="F1051"/>
     </row>
-    <row r="1052" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1052" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1052" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71147,7 +71147,7 @@
       </c>
       <c r="F1052"/>
     </row>
-    <row r="1053" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1053" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1053" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71165,7 +71165,7 @@
       </c>
       <c r="F1053"/>
     </row>
-    <row r="1054" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1054" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1054" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71183,7 +71183,7 @@
       </c>
       <c r="F1054"/>
     </row>
-    <row r="1055" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1055" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1055" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71201,7 +71201,7 @@
       </c>
       <c r="F1055"/>
     </row>
-    <row r="1056" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1056" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1056" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71219,7 +71219,7 @@
       </c>
       <c r="F1056"/>
     </row>
-    <row r="1057" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1057" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1057" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71237,7 +71237,7 @@
       </c>
       <c r="F1057"/>
     </row>
-    <row r="1058" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1058" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1058" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71255,7 +71255,7 @@
       </c>
       <c r="F1058"/>
     </row>
-    <row r="1059" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1059" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1059" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71273,7 +71273,7 @@
       </c>
       <c r="F1059"/>
     </row>
-    <row r="1060" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1060" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1060" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71291,7 +71291,7 @@
       </c>
       <c r="F1060"/>
     </row>
-    <row r="1061" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1061" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A1061" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71309,7 +71309,7 @@
       </c>
       <c r="F1061"/>
     </row>
-    <row r="1062" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1062" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1062" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71327,7 +71327,7 @@
       </c>
       <c r="F1062"/>
     </row>
-    <row r="1063" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1063" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1063" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71345,7 +71345,7 @@
       </c>
       <c r="F1063"/>
     </row>
-    <row r="1064" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1064" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1064" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71363,7 +71363,7 @@
       </c>
       <c r="F1064"/>
     </row>
-    <row r="1065" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1065" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1065" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71381,7 +71381,7 @@
       </c>
       <c r="F1065"/>
     </row>
-    <row r="1066" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1066" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1066" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71399,7 +71399,7 @@
       </c>
       <c r="F1066"/>
     </row>
-    <row r="1067" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1067" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1067" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71417,7 +71417,7 @@
       </c>
       <c r="F1067"/>
     </row>
-    <row r="1068" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1068" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1068" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71435,7 +71435,7 @@
       </c>
       <c r="F1068"/>
     </row>
-    <row r="1069" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1069" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1069" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71453,7 +71453,7 @@
       </c>
       <c r="F1069"/>
     </row>
-    <row r="1070" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1070" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1070" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71471,7 +71471,7 @@
       </c>
       <c r="F1070"/>
     </row>
-    <row r="1071" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1071" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1071" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71489,7 +71489,7 @@
       </c>
       <c r="F1071"/>
     </row>
-    <row r="1072" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1072" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1072" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71507,7 +71507,7 @@
       </c>
       <c r="F1072"/>
     </row>
-    <row r="1073" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1073" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1073" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71525,7 +71525,7 @@
       </c>
       <c r="F1073"/>
     </row>
-    <row r="1074" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1074" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1074" s="4" t="s">
         <v>1114</v>
       </c>
@@ -71543,7 +71543,7 @@
       </c>
       <c r="F1074"/>
     </row>
-    <row r="1075" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1075" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1075" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71563,7 +71563,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1076" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1076" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1076" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71583,7 +71583,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="1077" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1077" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1077" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71603,7 +71603,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1078" spans="1:6" ht="58" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1078" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A1078" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71623,7 +71623,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1079" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1079" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1079" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71643,7 +71643,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1080" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1080" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1080" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71663,7 +71663,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1081" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1081" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1081" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71683,7 +71683,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1082" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1082" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1082" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71703,7 +71703,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1083" spans="1:6" ht="101.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1083" spans="1:6" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A1083" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71723,7 +71723,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="1084" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1084" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1084" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71741,7 +71741,7 @@
       </c>
       <c r="F1084"/>
     </row>
-    <row r="1085" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1085" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1085" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71759,7 +71759,7 @@
       </c>
       <c r="F1085"/>
     </row>
-    <row r="1086" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1086" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1086" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71777,7 +71777,7 @@
       </c>
       <c r="F1086"/>
     </row>
-    <row r="1087" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1087" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1087" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71795,7 +71795,7 @@
       </c>
       <c r="F1087"/>
     </row>
-    <row r="1088" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1088" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1088" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71813,7 +71813,7 @@
       </c>
       <c r="F1088"/>
     </row>
-    <row r="1089" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1089" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1089" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71831,7 +71831,7 @@
       </c>
       <c r="F1089"/>
     </row>
-    <row r="1090" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1090" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1090" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71849,7 +71849,7 @@
       </c>
       <c r="F1090"/>
     </row>
-    <row r="1091" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1091" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1091" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71867,7 +71867,7 @@
       </c>
       <c r="F1091"/>
     </row>
-    <row r="1092" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1092" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1092" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71885,7 +71885,7 @@
       </c>
       <c r="F1092"/>
     </row>
-    <row r="1093" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1093" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1093" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71903,7 +71903,7 @@
       </c>
       <c r="F1093"/>
     </row>
-    <row r="1094" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1094" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1094" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71921,7 +71921,7 @@
       </c>
       <c r="F1094"/>
     </row>
-    <row r="1095" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1095" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1095" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71939,7 +71939,7 @@
       </c>
       <c r="F1095"/>
     </row>
-    <row r="1096" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1096" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1096" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71957,7 +71957,7 @@
       </c>
       <c r="F1096"/>
     </row>
-    <row r="1097" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1097" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1097" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71975,7 +71975,7 @@
       </c>
       <c r="F1097"/>
     </row>
-    <row r="1098" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1098" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1098" s="4" t="s">
         <v>1115</v>
       </c>
@@ -71993,7 +71993,7 @@
       </c>
       <c r="F1098"/>
     </row>
-    <row r="1099" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1099" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1099" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72011,7 +72011,7 @@
       </c>
       <c r="F1099"/>
     </row>
-    <row r="1100" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1100" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72029,7 +72029,7 @@
       </c>
       <c r="F1100"/>
     </row>
-    <row r="1101" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1101" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72047,7 +72047,7 @@
       </c>
       <c r="F1101"/>
     </row>
-    <row r="1102" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1102" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72065,7 +72065,7 @@
       </c>
       <c r="F1102"/>
     </row>
-    <row r="1103" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1103" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72083,7 +72083,7 @@
       </c>
       <c r="F1103"/>
     </row>
-    <row r="1104" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1104" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72101,7 +72101,7 @@
       </c>
       <c r="F1104"/>
     </row>
-    <row r="1105" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1105" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72119,7 +72119,7 @@
       </c>
       <c r="F1105"/>
     </row>
-    <row r="1106" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1106" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72245,7 +72245,7 @@
       </c>
       <c r="F1112"/>
     </row>
-    <row r="1113" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1113" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72263,7 +72263,7 @@
       </c>
       <c r="F1113"/>
     </row>
-    <row r="1114" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1114" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72281,7 +72281,7 @@
       </c>
       <c r="F1114"/>
     </row>
-    <row r="1115" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1115" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72299,7 +72299,7 @@
       </c>
       <c r="F1115"/>
     </row>
-    <row r="1116" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1116" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72317,7 +72317,7 @@
       </c>
       <c r="F1116"/>
     </row>
-    <row r="1117" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1117" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72335,7 +72335,7 @@
       </c>
       <c r="F1117"/>
     </row>
-    <row r="1118" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1118" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1118" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72353,7 +72353,7 @@
       </c>
       <c r="F1118"/>
     </row>
-    <row r="1119" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1119" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1119" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72371,7 +72371,7 @@
       </c>
       <c r="F1119"/>
     </row>
-    <row r="1120" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1120" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72389,7 +72389,7 @@
       </c>
       <c r="F1120"/>
     </row>
-    <row r="1121" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1121" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1121" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72407,7 +72407,7 @@
       </c>
       <c r="F1121"/>
     </row>
-    <row r="1122" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1122" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1122" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72425,7 +72425,7 @@
       </c>
       <c r="F1122"/>
     </row>
-    <row r="1123" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1123" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1123" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72443,7 +72443,7 @@
       </c>
       <c r="F1123"/>
     </row>
-    <row r="1124" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1124" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72461,7 +72461,7 @@
       </c>
       <c r="F1124"/>
     </row>
-    <row r="1125" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1125" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72479,7 +72479,7 @@
       </c>
       <c r="F1125"/>
     </row>
-    <row r="1126" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1126" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72497,7 +72497,7 @@
       </c>
       <c r="F1126"/>
     </row>
-    <row r="1127" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1127" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72515,7 +72515,7 @@
       </c>
       <c r="F1127"/>
     </row>
-    <row r="1128" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1128" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72533,7 +72533,7 @@
       </c>
       <c r="F1128"/>
     </row>
-    <row r="1129" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1129" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72551,7 +72551,7 @@
       </c>
       <c r="F1129"/>
     </row>
-    <row r="1130" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1130" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1130" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72569,7 +72569,7 @@
       </c>
       <c r="F1130"/>
     </row>
-    <row r="1131" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1131" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72587,7 +72587,7 @@
       </c>
       <c r="F1131"/>
     </row>
-    <row r="1132" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1132" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72605,7 +72605,7 @@
       </c>
       <c r="F1132"/>
     </row>
-    <row r="1133" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1133" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72623,7 +72623,7 @@
       </c>
       <c r="F1133"/>
     </row>
-    <row r="1134" spans="1:6" ht="43.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1134" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1134" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72641,7 +72641,7 @@
       </c>
       <c r="F1134"/>
     </row>
-    <row r="1135" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1135" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72659,7 +72659,7 @@
       </c>
       <c r="F1135"/>
     </row>
-    <row r="1136" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1136" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72677,7 +72677,7 @@
       </c>
       <c r="F1136"/>
     </row>
-    <row r="1137" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1137" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1137" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72695,7 +72695,7 @@
       </c>
       <c r="F1137"/>
     </row>
-    <row r="1138" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1138" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72713,7 +72713,7 @@
       </c>
       <c r="F1138"/>
     </row>
-    <row r="1139" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1139" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1139" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72731,7 +72731,7 @@
       </c>
       <c r="F1139"/>
     </row>
-    <row r="1140" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1140" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1140" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72749,7 +72749,7 @@
       </c>
       <c r="F1140"/>
     </row>
-    <row r="1141" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1141" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72767,7 +72767,7 @@
       </c>
       <c r="F1141"/>
     </row>
-    <row r="1142" spans="1:6" ht="72.5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1142" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A1142" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72785,7 +72785,7 @@
       </c>
       <c r="F1142"/>
     </row>
-    <row r="1143" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1143" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72803,7 +72803,7 @@
       </c>
       <c r="F1143"/>
     </row>
-    <row r="1144" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1144" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72821,7 +72821,7 @@
       </c>
       <c r="F1144"/>
     </row>
-    <row r="1145" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1145" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72839,7 +72839,7 @@
       </c>
       <c r="F1145"/>
     </row>
-    <row r="1146" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1146" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72857,7 +72857,7 @@
       </c>
       <c r="F1146"/>
     </row>
-    <row r="1147" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1147" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72875,7 +72875,7 @@
       </c>
       <c r="F1147"/>
     </row>
-    <row r="1148" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1148" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72893,7 +72893,7 @@
       </c>
       <c r="F1148"/>
     </row>
-    <row r="1149" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1149" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72911,7 +72911,7 @@
       </c>
       <c r="F1149"/>
     </row>
-    <row r="1150" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1150" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1150" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72929,7 +72929,7 @@
       </c>
       <c r="F1150"/>
     </row>
-    <row r="1151" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1151" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72947,7 +72947,7 @@
       </c>
       <c r="F1151"/>
     </row>
-    <row r="1152" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1152" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72965,7 +72965,7 @@
       </c>
       <c r="F1152"/>
     </row>
-    <row r="1153" spans="1:6" ht="29" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1153" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A1153" s="4" t="s">
         <v>1115</v>
       </c>
@@ -72983,7 +72983,7 @@
       </c>
       <c r="F1153"/>
     </row>
-    <row r="1154" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1154" s="4" t="s">
         <v>1115</v>
       </c>
@@ -73001,7 +73001,7 @@
       </c>
       <c r="F1154"/>
     </row>
-    <row r="1155" spans="1:6" hidden="1" x14ac:dyDescent="0.35">
+    <row r="1155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1155" s="4" t="s">
         <v>1115</v>
       </c>
@@ -73020,13 +73020,7 @@
       <c r="F1155"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1155" xr:uid="{7E885E9E-B9D0-4AB2-985A-25954D52BD4C}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="12.6 Duplicate Processing"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:I1155" xr:uid="{7E885E9E-B9D0-4AB2-985A-25954D52BD4C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/VISA_CHECK.xlsx
+++ b/VISA_CHECK.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JulianaRodriguezBelt\Downloads\DEFENSE_VIEWER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E0DDC7-EE61-4A22-8F5A-A0D9880626DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C5864E-8921-4092-ADAA-043AF654314A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="941" firstSheet="2" activeTab="6" xr2:uid="{65CF5D28-24F6-4E6D-B37B-A691AC3C8BFA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="941" firstSheet="2" activeTab="6" xr2:uid="{65CF5D28-24F6-4E6D-B37B-A691AC3C8BFA}"/>
   </bookViews>
   <sheets>
     <sheet name="MCC" sheetId="11" state="hidden" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18298" uniqueCount="1313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18299" uniqueCount="1314">
   <si>
     <t>country_code</t>
   </si>
@@ -4376,6 +4376,9 @@
   </si>
   <si>
     <t>Cardholder must attempted to resolve with Merchant</t>
+  </si>
+  <si>
+    <t>Transaction Type</t>
   </si>
 </sst>
 </file>
@@ -51926,7 +51929,9 @@
       <c r="E1" s="23" t="s">
         <v>1074</v>
       </c>
-      <c r="F1" s="24"/>
+      <c r="F1" s="23" t="s">
+        <v>1313</v>
+      </c>
     </row>
     <row r="2" spans="1:6" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
